--- a/前缀.xlsx
+++ b/前缀.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lazy\Desktop\Research-on-the-Identification-Mechanism-of-Altmetrics-Data-for-Sina-Weibo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0700B3-7FFC-4AB8-B2B2-B01E68CD2CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9303601-8073-4167-9D86-E1AC12777F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1668,10 +1668,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://??/article/??/fulltext;https://??/article/??/abstract</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://???.springeropen.com/counter/pdf/??.pdf;https://link.springer.com/content/pdf/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6299,6 +6295,10 @@
   </si>
   <si>
     <t>https://www.aminer.cn/pub/;https://www.aminer.org/pub/;https://aminer.cn/pub/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://??/article/??/fulltext;https://??/article/??/abstract;https://??/article/view/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6713,10 +6713,10 @@
         <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="C2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>202</v>
@@ -6727,10 +6727,10 @@
         <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>203</v>
@@ -6756,7 +6756,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="C5" t="s">
         <v>195</v>
@@ -6786,12 +6786,12 @@
         <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>322</v>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="C8" t="s">
         <v>133</v>
@@ -6811,7 +6811,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -6822,7 +6822,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C10" t="s">
         <v>217</v>
@@ -6888,10 +6888,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
+        <v>420</v>
+      </c>
+      <c r="C16" t="s">
         <v>421</v>
-      </c>
-      <c r="C16" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -6965,7 +6965,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C23" t="s">
         <v>228</v>
@@ -6987,7 +6987,7 @@
         <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C25" t="s">
         <v>135</v>
@@ -7056,7 +7056,7 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7097,7 +7097,7 @@
         <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="C35" t="s">
         <v>65</v>
@@ -7108,7 +7108,7 @@
         <v>223</v>
       </c>
       <c r="B36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -7119,10 +7119,10 @@
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="C37" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -7160,32 +7160,32 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B41" t="s">
         <v>441</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>442</v>
-      </c>
-      <c r="C41" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B42" t="s">
         <v>444</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>445</v>
-      </c>
-      <c r="C42" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B43" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>229</v>
       </c>
       <c r="B48" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C48" t="s">
         <v>230</v>
@@ -7284,10 +7284,10 @@
         <v>243</v>
       </c>
       <c r="B52" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C52" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -7328,10 +7328,10 @@
         <v>247</v>
       </c>
       <c r="B56" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C56" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -7383,7 +7383,7 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C61" t="s">
         <v>210</v>
@@ -7394,10 +7394,10 @@
         <v>192</v>
       </c>
       <c r="B62" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C62" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7405,7 +7405,7 @@
         <v>193</v>
       </c>
       <c r="B63" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C63" t="s">
         <v>194</v>
@@ -7449,10 +7449,10 @@
         <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C67" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -7496,7 +7496,7 @@
         <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7515,18 +7515,18 @@
         <v>250</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>431</v>
+      </c>
+      <c r="B74" t="s">
         <v>432</v>
-      </c>
-      <c r="B74" t="s">
-        <v>433</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B75" t="s">
         <v>448</v>
-      </c>
-      <c r="B75" t="s">
-        <v>449</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7545,32 +7545,32 @@
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B76" t="s">
+        <v>541</v>
+      </c>
+      <c r="C76" t="s">
         <v>434</v>
-      </c>
-      <c r="B76" t="s">
-        <v>542</v>
-      </c>
-      <c r="C76" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C77" t="s">
         <v>429</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1554</v>
-      </c>
-      <c r="C77" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B78" t="s">
         <v>427</v>
-      </c>
-      <c r="B78" t="s">
-        <v>428</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7625,10 +7625,10 @@
         <v>265</v>
       </c>
       <c r="B83" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C83" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7691,7 +7691,7 @@
         <v>291</v>
       </c>
       <c r="B89" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7812,10 +7812,10 @@
         <v>319</v>
       </c>
       <c r="B100" t="s">
+        <v>544</v>
+      </c>
+      <c r="C100" t="s">
         <v>545</v>
-      </c>
-      <c r="C100" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7848,7 +7848,7 @@
         <v>325</v>
       </c>
       <c r="C103" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7889,10 +7889,10 @@
         <v>337</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C107" t="s">
         <v>548</v>
-      </c>
-      <c r="C107" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7900,7 +7900,7 @@
         <v>338</v>
       </c>
       <c r="B108" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -7977,7 +7977,7 @@
         <v>356</v>
       </c>
       <c r="B115" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C115" t="s">
         <v>355</v>
@@ -8032,10 +8032,10 @@
         <v>369</v>
       </c>
       <c r="B120" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C120" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8054,10 +8054,10 @@
         <v>373</v>
       </c>
       <c r="B122" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C122" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8106,13 +8106,13 @@
     </row>
     <row r="127" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B127" t="s">
         <v>436</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>437</v>
-      </c>
-      <c r="C127" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8197,10 +8197,10 @@
         <v>406</v>
       </c>
       <c r="B135" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C135" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8208,10 +8208,10 @@
         <v>407</v>
       </c>
       <c r="B136" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C136" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8227,24 +8227,24 @@
     </row>
     <row r="138" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B138" t="s">
         <v>453</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>454</v>
-      </c>
-      <c r="C138" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B139" t="s">
         <v>456</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>457</v>
-      </c>
-      <c r="C139" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8260,65 +8260,65 @@
     </row>
     <row r="141" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B141" t="s">
+        <v>554</v>
+      </c>
+      <c r="C141" t="s">
         <v>459</v>
-      </c>
-      <c r="B141" t="s">
-        <v>555</v>
-      </c>
-      <c r="C141" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B142" t="s">
         <v>462</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>463</v>
-      </c>
-      <c r="C142" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B143" t="s">
         <v>465</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
         <v>466</v>
-      </c>
-      <c r="C143" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B144" t="s">
+        <v>469</v>
+      </c>
+      <c r="C144" t="s">
         <v>468</v>
-      </c>
-      <c r="B144" t="s">
-        <v>470</v>
-      </c>
-      <c r="C144" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B145" t="s">
+        <v>472</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="B145" t="s">
-        <v>473</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B146" t="s">
         <v>474</v>
-      </c>
-      <c r="B146" t="s">
-        <v>475</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -8326,43 +8326,43 @@
     </row>
     <row r="147" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C147" t="s">
         <v>476</v>
-      </c>
-      <c r="B147" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C147" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B148" t="s">
         <v>478</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>479</v>
-      </c>
-      <c r="C148" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B149" t="s">
         <v>481</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>482</v>
-      </c>
-      <c r="C149" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B150" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -8370,32 +8370,32 @@
     </row>
     <row r="151" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B151" t="s">
         <v>485</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>486</v>
-      </c>
-      <c r="C151" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B152" t="s">
         <v>488</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>489</v>
-      </c>
-      <c r="C152" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B153" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -8403,32 +8403,32 @@
     </row>
     <row r="154" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B154" t="s">
+        <v>493</v>
+      </c>
+      <c r="C154" t="s">
         <v>492</v>
-      </c>
-      <c r="B154" t="s">
-        <v>494</v>
-      </c>
-      <c r="C154" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B155" t="s">
         <v>495</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" t="s">
         <v>496</v>
-      </c>
-      <c r="C155" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B156" t="s">
         <v>498</v>
-      </c>
-      <c r="B156" t="s">
-        <v>499</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -8436,43 +8436,43 @@
     </row>
     <row r="157" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B157" t="s">
         <v>500</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>501</v>
-      </c>
-      <c r="C157" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B158" t="s">
         <v>503</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C158" t="s">
         <v>504</v>
-      </c>
-      <c r="C158" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B159" t="s">
+        <v>507</v>
+      </c>
+      <c r="C159" t="s">
         <v>506</v>
-      </c>
-      <c r="B159" t="s">
-        <v>508</v>
-      </c>
-      <c r="C159" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B160" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C160" s="7">
         <v>0</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="161" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B161" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C161" s="7">
         <v>0</v>
@@ -8491,21 +8491,21 @@
     </row>
     <row r="162" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B162" t="s">
+        <v>559</v>
+      </c>
+      <c r="C162" t="s">
         <v>511</v>
-      </c>
-      <c r="B162" t="s">
-        <v>560</v>
-      </c>
-      <c r="C162" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B163" t="s">
         <v>513</v>
-      </c>
-      <c r="B163" t="s">
-        <v>514</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -8513,76 +8513,76 @@
     </row>
     <row r="164" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="B164" t="s">
         <v>515</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C164" t="s">
         <v>516</v>
-      </c>
-      <c r="C164" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B165" t="s">
+        <v>519</v>
+      </c>
+      <c r="C165" t="s">
         <v>518</v>
-      </c>
-      <c r="B165" t="s">
-        <v>520</v>
-      </c>
-      <c r="C165" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B166" t="s">
         <v>521</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>522</v>
-      </c>
-      <c r="C166" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B167" t="s">
         <v>524</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C167" t="s">
         <v>525</v>
-      </c>
-      <c r="C167" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="B168" t="s">
+        <v>528</v>
+      </c>
+      <c r="C168" t="s">
         <v>527</v>
-      </c>
-      <c r="B168" t="s">
-        <v>529</v>
-      </c>
-      <c r="C168" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="B169" t="s">
+        <v>531</v>
+      </c>
+      <c r="C169" t="s">
         <v>530</v>
-      </c>
-      <c r="B169" t="s">
-        <v>532</v>
-      </c>
-      <c r="C169" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="B170" t="s">
         <v>533</v>
-      </c>
-      <c r="B170" t="s">
-        <v>534</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -8590,10 +8590,10 @@
     </row>
     <row r="171" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B171" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -8601,21 +8601,21 @@
     </row>
     <row r="172" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="B172" t="s">
         <v>562</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C172" t="s">
         <v>563</v>
-      </c>
-      <c r="C172" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="B173" t="s">
         <v>565</v>
-      </c>
-      <c r="B173" t="s">
-        <v>566</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -8623,43 +8623,43 @@
     </row>
     <row r="174" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="B174" t="s">
+        <v>568</v>
+      </c>
+      <c r="C174" t="s">
         <v>567</v>
-      </c>
-      <c r="B174" t="s">
-        <v>569</v>
-      </c>
-      <c r="C174" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="B175" t="s">
+        <v>571</v>
+      </c>
+      <c r="C175" t="s">
         <v>570</v>
-      </c>
-      <c r="B175" t="s">
-        <v>572</v>
-      </c>
-      <c r="C175" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="B176" t="s">
         <v>573</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C176" t="s">
         <v>574</v>
-      </c>
-      <c r="C176" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="B177" t="s">
         <v>576</v>
-      </c>
-      <c r="B177" t="s">
-        <v>577</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -8667,10 +8667,10 @@
     </row>
     <row r="178" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B178" t="s">
         <v>578</v>
-      </c>
-      <c r="B178" t="s">
-        <v>579</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -8678,10 +8678,10 @@
     </row>
     <row r="179" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="B179" t="s">
         <v>580</v>
-      </c>
-      <c r="B179" t="s">
-        <v>581</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="180" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B180" t="s">
         <v>582</v>
-      </c>
-      <c r="B180" t="s">
-        <v>583</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -8700,21 +8700,21 @@
     </row>
     <row r="181" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="B181" t="s">
         <v>584</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>585</v>
-      </c>
-      <c r="C181" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="B182" t="s">
         <v>587</v>
-      </c>
-      <c r="B182" t="s">
-        <v>588</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -8722,21 +8722,21 @@
     </row>
     <row r="183" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="B183" t="s">
         <v>589</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>590</v>
-      </c>
-      <c r="C183" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B184" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -8745,82 +8745,82 @@
     </row>
     <row r="185" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="B185" t="s">
+        <v>597</v>
+      </c>
+      <c r="C185" t="s">
         <v>596</v>
-      </c>
-      <c r="B185" t="s">
-        <v>598</v>
-      </c>
-      <c r="C185" t="s">
-        <v>597</v>
       </c>
       <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="B186" t="s">
         <v>600</v>
       </c>
-      <c r="B186" t="s">
+      <c r="C186" t="s">
         <v>601</v>
-      </c>
-      <c r="C186" t="s">
-        <v>602</v>
       </c>
       <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C187" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B188" t="s">
+        <v>606</v>
+      </c>
+      <c r="C188" t="s">
         <v>607</v>
-      </c>
-      <c r="C188" t="s">
-        <v>608</v>
       </c>
       <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="B189" t="s">
         <v>609</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>610</v>
-      </c>
-      <c r="C189" t="s">
-        <v>611</v>
       </c>
       <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B190" t="s">
         <v>612</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>613</v>
-      </c>
-      <c r="C190" t="s">
-        <v>614</v>
       </c>
       <c r="D190" s="1"/>
     </row>
     <row r="191" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="B191" t="s">
         <v>615</v>
-      </c>
-      <c r="B191" t="s">
-        <v>616</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -8829,22 +8829,22 @@
     </row>
     <row r="192" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B192" t="s">
         <v>617</v>
       </c>
-      <c r="B192" t="s">
+      <c r="C192" t="s">
         <v>618</v>
-      </c>
-      <c r="C192" t="s">
-        <v>619</v>
       </c>
       <c r="D192" s="1"/>
     </row>
     <row r="193" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B193" t="s">
         <v>620</v>
-      </c>
-      <c r="B193" t="s">
-        <v>621</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -8853,34 +8853,34 @@
     </row>
     <row r="194" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="B194" t="s">
         <v>622</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>623</v>
-      </c>
-      <c r="C194" t="s">
-        <v>624</v>
       </c>
       <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="B195" t="s">
         <v>625</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>626</v>
-      </c>
-      <c r="C195" t="s">
-        <v>627</v>
       </c>
       <c r="D195" s="1"/>
     </row>
     <row r="196" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="B196" t="s">
         <v>628</v>
-      </c>
-      <c r="B196" t="s">
-        <v>629</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -8889,10 +8889,10 @@
     </row>
     <row r="197" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B197" t="s">
         <v>630</v>
-      </c>
-      <c r="B197" t="s">
-        <v>631</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8901,10 +8901,10 @@
     </row>
     <row r="198" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B198" t="s">
         <v>635</v>
-      </c>
-      <c r="B198" t="s">
-        <v>636</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8913,22 +8913,22 @@
     </row>
     <row r="199" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B199" t="s">
         <v>637</v>
       </c>
-      <c r="B199" t="s">
+      <c r="C199" t="s">
         <v>638</v>
-      </c>
-      <c r="C199" t="s">
-        <v>639</v>
       </c>
       <c r="D199" s="1"/>
     </row>
     <row r="200" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B200" t="s">
         <v>640</v>
-      </c>
-      <c r="B200" t="s">
-        <v>641</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="201" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B201" t="s">
         <v>642</v>
-      </c>
-      <c r="B201" t="s">
-        <v>643</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -8949,34 +8949,34 @@
     </row>
     <row r="202" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B202" t="s">
+        <v>645</v>
+      </c>
+      <c r="C202" t="s">
         <v>644</v>
-      </c>
-      <c r="B202" t="s">
-        <v>646</v>
-      </c>
-      <c r="C202" t="s">
-        <v>645</v>
       </c>
       <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="B203" t="s">
+        <v>648</v>
+      </c>
+      <c r="C203" t="s">
         <v>647</v>
-      </c>
-      <c r="B203" t="s">
-        <v>649</v>
-      </c>
-      <c r="C203" t="s">
-        <v>648</v>
       </c>
       <c r="D203" s="1"/>
     </row>
     <row r="204" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="B204" t="s">
         <v>650</v>
-      </c>
-      <c r="B204" t="s">
-        <v>651</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -8985,10 +8985,10 @@
     </row>
     <row r="205" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B205" t="s">
         <v>652</v>
-      </c>
-      <c r="B205" t="s">
-        <v>653</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="206" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="B206" t="s">
         <v>654</v>
-      </c>
-      <c r="B206" t="s">
-        <v>655</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -9009,10 +9009,10 @@
     </row>
     <row r="207" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B207" t="s">
         <v>656</v>
-      </c>
-      <c r="B207" t="s">
-        <v>657</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -9021,10 +9021,10 @@
     </row>
     <row r="208" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="B208" t="s">
         <v>658</v>
-      </c>
-      <c r="B208" t="s">
-        <v>659</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -9033,58 +9033,58 @@
     </row>
     <row r="209" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="B209" t="s">
+        <v>661</v>
+      </c>
+      <c r="C209" t="s">
         <v>660</v>
-      </c>
-      <c r="B209" t="s">
-        <v>662</v>
-      </c>
-      <c r="C209" t="s">
-        <v>661</v>
       </c>
       <c r="D209" s="1"/>
     </row>
     <row r="210" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="B210" t="s">
         <v>663</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>664</v>
-      </c>
-      <c r="C210" t="s">
-        <v>665</v>
       </c>
       <c r="D210" s="1"/>
     </row>
     <row r="211" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="B211" t="s">
         <v>666</v>
       </c>
-      <c r="B211" t="s">
+      <c r="C211" t="s">
         <v>667</v>
-      </c>
-      <c r="C211" t="s">
-        <v>668</v>
       </c>
       <c r="D211" s="1"/>
     </row>
     <row r="212" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="B212" t="s">
+        <v>670</v>
+      </c>
+      <c r="C212" t="s">
         <v>669</v>
-      </c>
-      <c r="B212" t="s">
-        <v>671</v>
-      </c>
-      <c r="C212" t="s">
-        <v>670</v>
       </c>
       <c r="D212" s="1"/>
     </row>
     <row r="213" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B213" t="s">
         <v>672</v>
-      </c>
-      <c r="B213" t="s">
-        <v>673</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -9093,34 +9093,34 @@
     </row>
     <row r="214" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="B214" t="s">
+        <v>675</v>
+      </c>
+      <c r="C214" t="s">
         <v>674</v>
-      </c>
-      <c r="B214" t="s">
-        <v>676</v>
-      </c>
-      <c r="C214" t="s">
-        <v>675</v>
       </c>
       <c r="D214" s="1"/>
     </row>
     <row r="215" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="B215" t="s">
         <v>677</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
         <v>678</v>
-      </c>
-      <c r="C215" t="s">
-        <v>679</v>
       </c>
       <c r="D215" s="1"/>
     </row>
     <row r="216" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="B216" t="s">
         <v>680</v>
-      </c>
-      <c r="B216" t="s">
-        <v>681</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -9129,58 +9129,58 @@
     </row>
     <row r="217" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="B217" t="s">
+        <v>683</v>
+      </c>
+      <c r="C217" t="s">
         <v>682</v>
-      </c>
-      <c r="B217" t="s">
-        <v>684</v>
-      </c>
-      <c r="C217" t="s">
-        <v>683</v>
       </c>
       <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="B218" t="s">
+        <v>686</v>
+      </c>
+      <c r="C218" t="s">
         <v>685</v>
-      </c>
-      <c r="B218" t="s">
-        <v>687</v>
-      </c>
-      <c r="C218" t="s">
-        <v>686</v>
       </c>
       <c r="D218" s="1"/>
     </row>
     <row r="219" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="B219" t="s">
         <v>688</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>689</v>
-      </c>
-      <c r="C219" t="s">
-        <v>690</v>
       </c>
       <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B220" t="s">
         <v>691</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>692</v>
-      </c>
-      <c r="C220" t="s">
-        <v>693</v>
       </c>
       <c r="D220" s="1"/>
     </row>
     <row r="221" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B221" t="s">
         <v>694</v>
-      </c>
-      <c r="B221" t="s">
-        <v>695</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -9189,58 +9189,58 @@
     </row>
     <row r="222" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B222" t="s">
         <v>696</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>697</v>
-      </c>
-      <c r="C222" t="s">
-        <v>698</v>
       </c>
       <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="B223" t="s">
         <v>699</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>700</v>
-      </c>
-      <c r="C223" t="s">
-        <v>701</v>
       </c>
       <c r="D223" s="1"/>
     </row>
     <row r="224" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="B224" t="s">
+        <v>703</v>
+      </c>
+      <c r="C224" t="s">
         <v>702</v>
-      </c>
-      <c r="B224" t="s">
-        <v>704</v>
-      </c>
-      <c r="C224" t="s">
-        <v>703</v>
       </c>
       <c r="D224" s="1"/>
     </row>
     <row r="225" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="B225" t="s">
+        <v>706</v>
+      </c>
+      <c r="C225" t="s">
         <v>705</v>
-      </c>
-      <c r="B225" t="s">
-        <v>707</v>
-      </c>
-      <c r="C225" t="s">
-        <v>706</v>
       </c>
       <c r="D225" s="1"/>
     </row>
     <row r="226" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B226" t="s">
         <v>708</v>
-      </c>
-      <c r="B226" t="s">
-        <v>709</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -9249,58 +9249,58 @@
     </row>
     <row r="227" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B227" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C227" t="s">
         <v>1538</v>
-      </c>
-      <c r="C227" t="s">
-        <v>1539</v>
       </c>
       <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B228" t="s">
         <v>711</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
         <v>712</v>
-      </c>
-      <c r="C228" t="s">
-        <v>713</v>
       </c>
       <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B229" t="s">
         <v>714</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>715</v>
-      </c>
-      <c r="C229" t="s">
-        <v>716</v>
       </c>
       <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="B230" t="s">
         <v>717</v>
       </c>
-      <c r="B230" t="s">
+      <c r="C230" t="s">
         <v>718</v>
-      </c>
-      <c r="C230" t="s">
-        <v>719</v>
       </c>
       <c r="D230" s="1"/>
     </row>
     <row r="231" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="B231" t="s">
         <v>720</v>
-      </c>
-      <c r="B231" t="s">
-        <v>721</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -9309,22 +9309,22 @@
     </row>
     <row r="232" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="B232" t="s">
+        <v>723</v>
+      </c>
+      <c r="C232" t="s">
         <v>722</v>
-      </c>
-      <c r="B232" t="s">
-        <v>724</v>
-      </c>
-      <c r="C232" t="s">
-        <v>723</v>
       </c>
       <c r="D232" s="1"/>
     </row>
     <row r="233" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B233" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -9333,46 +9333,46 @@
     </row>
     <row r="234" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="B234" t="s">
         <v>726</v>
       </c>
-      <c r="B234" t="s">
+      <c r="C234" t="s">
         <v>727</v>
-      </c>
-      <c r="C234" t="s">
-        <v>728</v>
       </c>
       <c r="D234" s="1"/>
     </row>
     <row r="235" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="B235" t="s">
+        <v>730</v>
+      </c>
+      <c r="C235" t="s">
         <v>729</v>
-      </c>
-      <c r="B235" t="s">
-        <v>731</v>
-      </c>
-      <c r="C235" t="s">
-        <v>730</v>
       </c>
       <c r="D235" s="1"/>
     </row>
     <row r="236" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="B236" t="s">
         <v>732</v>
       </c>
-      <c r="B236" t="s">
+      <c r="C236" t="s">
         <v>733</v>
-      </c>
-      <c r="C236" t="s">
-        <v>734</v>
       </c>
       <c r="D236" s="1"/>
     </row>
     <row r="237" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="B237" t="s">
         <v>735</v>
-      </c>
-      <c r="B237" t="s">
-        <v>736</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="238" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B238" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9393,10 +9393,10 @@
     </row>
     <row r="239" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B239" t="s">
         <v>739</v>
-      </c>
-      <c r="B239" t="s">
-        <v>740</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -9405,34 +9405,34 @@
     </row>
     <row r="240" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="B240" t="s">
         <v>741</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" t="s">
         <v>742</v>
-      </c>
-      <c r="C240" t="s">
-        <v>743</v>
       </c>
       <c r="D240" s="1"/>
     </row>
     <row r="241" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="B241" t="s">
         <v>744</v>
       </c>
-      <c r="B241" t="s">
+      <c r="C241" t="s">
         <v>745</v>
-      </c>
-      <c r="C241" t="s">
-        <v>746</v>
       </c>
       <c r="D241" s="1"/>
     </row>
     <row r="242" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B242" t="s">
         <v>747</v>
-      </c>
-      <c r="B242" t="s">
-        <v>748</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -9441,10 +9441,10 @@
     </row>
     <row r="243" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="B243" t="s">
         <v>749</v>
-      </c>
-      <c r="B243" t="s">
-        <v>750</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -9453,10 +9453,10 @@
     </row>
     <row r="244" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
+        <v>750</v>
+      </c>
+      <c r="B244" t="s">
         <v>751</v>
-      </c>
-      <c r="B244" t="s">
-        <v>752</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -9465,10 +9465,10 @@
     </row>
     <row r="245" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="B245" t="s">
         <v>753</v>
-      </c>
-      <c r="B245" t="s">
-        <v>754</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -9477,10 +9477,10 @@
     </row>
     <row r="246" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="B246" t="s">
         <v>755</v>
-      </c>
-      <c r="B246" t="s">
-        <v>756</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9489,10 +9489,10 @@
     </row>
     <row r="247" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="B247" t="s">
         <v>757</v>
-      </c>
-      <c r="B247" t="s">
-        <v>758</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -9501,34 +9501,34 @@
     </row>
     <row r="248" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="B248" t="s">
         <v>759</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" t="s">
         <v>760</v>
-      </c>
-      <c r="C248" t="s">
-        <v>761</v>
       </c>
       <c r="D248" s="1"/>
     </row>
     <row r="249" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="B249" t="s">
         <v>762</v>
       </c>
-      <c r="B249" t="s">
+      <c r="C249" t="s">
         <v>763</v>
-      </c>
-      <c r="C249" t="s">
-        <v>764</v>
       </c>
       <c r="D249" s="1"/>
     </row>
     <row r="250" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="B250" t="s">
         <v>765</v>
-      </c>
-      <c r="B250" t="s">
-        <v>766</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -9537,34 +9537,34 @@
     </row>
     <row r="251" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="B251" t="s">
+        <v>768</v>
+      </c>
+      <c r="C251" t="s">
         <v>767</v>
-      </c>
-      <c r="B251" t="s">
-        <v>769</v>
-      </c>
-      <c r="C251" t="s">
-        <v>768</v>
       </c>
       <c r="D251" s="1"/>
     </row>
     <row r="252" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="B252" t="s">
         <v>770</v>
       </c>
-      <c r="B252" t="s">
+      <c r="C252" t="s">
         <v>771</v>
-      </c>
-      <c r="C252" t="s">
-        <v>772</v>
       </c>
       <c r="D252" s="1"/>
     </row>
     <row r="253" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="B253" t="s">
         <v>773</v>
-      </c>
-      <c r="B253" t="s">
-        <v>774</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="254" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
+        <v>774</v>
+      </c>
+      <c r="B254" t="s">
         <v>775</v>
-      </c>
-      <c r="B254" t="s">
-        <v>776</v>
       </c>
       <c r="C254" t="s">
         <v>381</v>
@@ -9585,10 +9585,10 @@
     </row>
     <row r="255" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="B255" t="s">
         <v>777</v>
-      </c>
-      <c r="B255" t="s">
-        <v>778</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -9597,34 +9597,34 @@
     </row>
     <row r="256" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="B256" t="s">
         <v>779</v>
       </c>
-      <c r="B256" t="s">
-        <v>780</v>
-      </c>
       <c r="C256" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D256" s="1"/>
     </row>
     <row r="257" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B257" t="s">
+        <v>782</v>
+      </c>
+      <c r="C257" t="s">
         <v>783</v>
-      </c>
-      <c r="C257" t="s">
-        <v>784</v>
       </c>
       <c r="D257" s="1"/>
     </row>
     <row r="258" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="B258" t="s">
         <v>785</v>
-      </c>
-      <c r="B258" t="s">
-        <v>786</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -9633,10 +9633,10 @@
     </row>
     <row r="259" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="B259" t="s">
         <v>787</v>
-      </c>
-      <c r="B259" t="s">
-        <v>788</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -9645,22 +9645,22 @@
     </row>
     <row r="260" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="B260" t="s">
         <v>789</v>
       </c>
-      <c r="B260" t="s">
+      <c r="C260" t="s">
         <v>790</v>
-      </c>
-      <c r="C260" t="s">
-        <v>791</v>
       </c>
       <c r="D260" s="1"/>
     </row>
     <row r="261" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="B261" t="s">
         <v>792</v>
-      </c>
-      <c r="B261" t="s">
-        <v>793</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -9669,22 +9669,22 @@
     </row>
     <row r="262" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="B262" t="s">
         <v>794</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C262" t="s">
         <v>795</v>
-      </c>
-      <c r="C262" t="s">
-        <v>796</v>
       </c>
       <c r="D262" s="1"/>
     </row>
     <row r="263" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="B263" t="s">
         <v>797</v>
-      </c>
-      <c r="B263" t="s">
-        <v>798</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -9693,10 +9693,10 @@
     </row>
     <row r="264" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -9705,10 +9705,10 @@
     </row>
     <row r="265" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="B265" t="s">
         <v>800</v>
-      </c>
-      <c r="B265" t="s">
-        <v>801</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -9717,10 +9717,10 @@
     </row>
     <row r="266" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B266" t="s">
         <v>802</v>
-      </c>
-      <c r="B266" t="s">
-        <v>803</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -9729,34 +9729,34 @@
     </row>
     <row r="267" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B267" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C267" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D267" s="1"/>
     </row>
     <row r="268" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B268" t="s">
         <v>805</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C268" t="s">
         <v>806</v>
-      </c>
-      <c r="C268" t="s">
-        <v>807</v>
       </c>
       <c r="D268" s="1"/>
     </row>
     <row r="269" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="B269" t="s">
         <v>808</v>
-      </c>
-      <c r="B269" t="s">
-        <v>809</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -9765,22 +9765,22 @@
     </row>
     <row r="270" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B270" t="s">
         <v>810</v>
       </c>
-      <c r="B270" t="s">
+      <c r="C270" t="s">
         <v>811</v>
-      </c>
-      <c r="C270" t="s">
-        <v>812</v>
       </c>
       <c r="D270" s="1"/>
     </row>
     <row r="271" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="B271" t="s">
         <v>813</v>
-      </c>
-      <c r="B271" t="s">
-        <v>814</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -9789,22 +9789,22 @@
     </row>
     <row r="272" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="B272" t="s">
         <v>815</v>
       </c>
-      <c r="B272" t="s">
+      <c r="C272" t="s">
         <v>816</v>
-      </c>
-      <c r="C272" t="s">
-        <v>817</v>
       </c>
       <c r="D272" s="1"/>
     </row>
     <row r="273" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B273" t="s">
         <v>818</v>
-      </c>
-      <c r="B273" t="s">
-        <v>819</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -9813,82 +9813,82 @@
     </row>
     <row r="274" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="B274" t="s">
+        <v>821</v>
+      </c>
+      <c r="C274" t="s">
         <v>820</v>
-      </c>
-      <c r="B274" t="s">
-        <v>822</v>
-      </c>
-      <c r="C274" t="s">
-        <v>821</v>
       </c>
       <c r="D274" s="1"/>
     </row>
     <row r="275" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
+        <v>822</v>
+      </c>
+      <c r="B275" t="s">
         <v>823</v>
       </c>
-      <c r="B275" t="s">
+      <c r="C275" t="s">
         <v>824</v>
-      </c>
-      <c r="C275" t="s">
-        <v>825</v>
       </c>
       <c r="D275" s="1"/>
     </row>
     <row r="276" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B276" t="s">
+        <v>827</v>
+      </c>
+      <c r="C276" t="s">
         <v>826</v>
-      </c>
-      <c r="B276" t="s">
-        <v>828</v>
-      </c>
-      <c r="C276" t="s">
-        <v>827</v>
       </c>
       <c r="D276" s="1"/>
     </row>
     <row r="277" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="B277" t="s">
+        <v>830</v>
+      </c>
+      <c r="C277" t="s">
         <v>829</v>
-      </c>
-      <c r="B277" t="s">
-        <v>831</v>
-      </c>
-      <c r="C277" t="s">
-        <v>830</v>
       </c>
       <c r="D277" s="1"/>
     </row>
     <row r="278" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="B278" t="s">
         <v>832</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>833</v>
-      </c>
-      <c r="C278" t="s">
-        <v>834</v>
       </c>
       <c r="D278" s="1"/>
     </row>
     <row r="279" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="B279" t="s">
         <v>835</v>
       </c>
-      <c r="B279" t="s">
+      <c r="C279" t="s">
         <v>836</v>
-      </c>
-      <c r="C279" t="s">
-        <v>837</v>
       </c>
       <c r="D279" s="1"/>
     </row>
     <row r="280" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="B280" t="s">
         <v>838</v>
-      </c>
-      <c r="B280" t="s">
-        <v>839</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -9897,10 +9897,10 @@
     </row>
     <row r="281" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B281" t="s">
         <v>840</v>
-      </c>
-      <c r="B281" t="s">
-        <v>841</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -9909,22 +9909,22 @@
     </row>
     <row r="282" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B282" t="s">
+        <v>843</v>
+      </c>
+      <c r="C282" t="s">
         <v>842</v>
-      </c>
-      <c r="B282" t="s">
-        <v>844</v>
-      </c>
-      <c r="C282" t="s">
-        <v>843</v>
       </c>
       <c r="D282" s="1"/>
     </row>
     <row r="283" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="B283" t="s">
         <v>845</v>
-      </c>
-      <c r="B283" t="s">
-        <v>846</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="284" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B284" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -9945,34 +9945,34 @@
     </row>
     <row r="285" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="B285" t="s">
         <v>848</v>
       </c>
-      <c r="B285" t="s">
+      <c r="C285" t="s">
         <v>849</v>
-      </c>
-      <c r="C285" t="s">
-        <v>850</v>
       </c>
       <c r="D285" s="1"/>
     </row>
     <row r="286" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="B286" t="s">
         <v>851</v>
       </c>
-      <c r="B286" t="s">
+      <c r="C286" t="s">
         <v>852</v>
-      </c>
-      <c r="C286" t="s">
-        <v>853</v>
       </c>
       <c r="D286" s="1"/>
     </row>
     <row r="287" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="B287" t="s">
         <v>854</v>
-      </c>
-      <c r="B287" t="s">
-        <v>855</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -9981,10 +9981,10 @@
     </row>
     <row r="288" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B288" t="s">
         <v>856</v>
-      </c>
-      <c r="B288" t="s">
-        <v>857</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -9993,58 +9993,58 @@
     </row>
     <row r="289" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="B289" t="s">
         <v>858</v>
       </c>
-      <c r="B289" t="s">
+      <c r="C289" t="s">
         <v>859</v>
-      </c>
-      <c r="C289" t="s">
-        <v>860</v>
       </c>
       <c r="D289" s="1"/>
     </row>
     <row r="290" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="B290" t="s">
         <v>861</v>
       </c>
-      <c r="B290" t="s">
+      <c r="C290" t="s">
         <v>862</v>
-      </c>
-      <c r="C290" t="s">
-        <v>863</v>
       </c>
       <c r="D290" s="1"/>
     </row>
     <row r="291" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="B291" t="s">
         <v>864</v>
       </c>
-      <c r="B291" t="s">
+      <c r="C291" t="s">
         <v>865</v>
-      </c>
-      <c r="C291" t="s">
-        <v>866</v>
       </c>
       <c r="D291" s="1"/>
     </row>
     <row r="292" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B292" t="s">
         <v>867</v>
       </c>
-      <c r="B292" t="s">
+      <c r="C292" t="s">
         <v>868</v>
-      </c>
-      <c r="C292" t="s">
-        <v>869</v>
       </c>
       <c r="D292" s="1"/>
     </row>
     <row r="293" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B293" t="s">
         <v>870</v>
-      </c>
-      <c r="B293" t="s">
-        <v>871</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -10053,82 +10053,82 @@
     </row>
     <row r="294" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B294" t="s">
+        <v>873</v>
+      </c>
+      <c r="C294" t="s">
         <v>874</v>
-      </c>
-      <c r="C294" t="s">
-        <v>875</v>
       </c>
       <c r="D294" s="1"/>
     </row>
     <row r="295" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="B295" t="s">
         <v>876</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" t="s">
         <v>877</v>
-      </c>
-      <c r="C295" t="s">
-        <v>878</v>
       </c>
       <c r="D295" s="1"/>
     </row>
     <row r="296" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="B296" t="s">
         <v>879</v>
       </c>
-      <c r="B296" t="s">
+      <c r="C296" t="s">
         <v>880</v>
-      </c>
-      <c r="C296" t="s">
-        <v>881</v>
       </c>
       <c r="D296" s="1"/>
     </row>
     <row r="297" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297" t="s">
         <v>882</v>
-      </c>
-      <c r="B297">
-        <v>0</v>
-      </c>
-      <c r="C297" t="s">
-        <v>883</v>
       </c>
       <c r="D297" s="1"/>
     </row>
     <row r="298" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="B298" t="s">
+        <v>885</v>
+      </c>
+      <c r="C298" t="s">
         <v>884</v>
-      </c>
-      <c r="B298" t="s">
-        <v>886</v>
-      </c>
-      <c r="C298" t="s">
-        <v>885</v>
       </c>
       <c r="D298" s="1"/>
     </row>
     <row r="299" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="B299" t="s">
         <v>887</v>
       </c>
-      <c r="B299" t="s">
+      <c r="C299" t="s">
         <v>888</v>
-      </c>
-      <c r="C299" t="s">
-        <v>889</v>
       </c>
       <c r="D299" s="1"/>
     </row>
     <row r="300" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="B300" t="s">
         <v>890</v>
-      </c>
-      <c r="B300" t="s">
-        <v>891</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -10137,34 +10137,34 @@
     </row>
     <row r="301" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="B301" t="s">
         <v>892</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" t="s">
         <v>893</v>
-      </c>
-      <c r="C301" t="s">
-        <v>894</v>
       </c>
       <c r="D301" s="1"/>
     </row>
     <row r="302" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="B302" t="s">
         <v>895</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>896</v>
-      </c>
-      <c r="C302" t="s">
-        <v>897</v>
       </c>
       <c r="D302" s="1"/>
     </row>
     <row r="303" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="B303" t="s">
         <v>898</v>
-      </c>
-      <c r="B303" t="s">
-        <v>899</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -10173,22 +10173,22 @@
     </row>
     <row r="304" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="B304" t="s">
+        <v>901</v>
+      </c>
+      <c r="C304" t="s">
         <v>900</v>
-      </c>
-      <c r="B304" t="s">
-        <v>902</v>
-      </c>
-      <c r="C304" t="s">
-        <v>901</v>
       </c>
       <c r="D304" s="1"/>
     </row>
     <row r="305" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
+        <v>902</v>
+      </c>
+      <c r="B305" t="s">
         <v>903</v>
-      </c>
-      <c r="B305" t="s">
-        <v>904</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -10197,10 +10197,10 @@
     </row>
     <row r="306" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="B306" t="s">
         <v>905</v>
-      </c>
-      <c r="B306" t="s">
-        <v>906</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -10209,22 +10209,22 @@
     </row>
     <row r="307" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="B307" t="s">
+        <v>909</v>
+      </c>
+      <c r="C307" t="s">
         <v>907</v>
-      </c>
-      <c r="B307" t="s">
-        <v>910</v>
-      </c>
-      <c r="C307" t="s">
-        <v>908</v>
       </c>
       <c r="D307" s="1"/>
     </row>
     <row r="308" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="8" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B308" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -10233,10 +10233,10 @@
     </row>
     <row r="309" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="8" t="s">
+        <v>911</v>
+      </c>
+      <c r="B309" t="s">
         <v>912</v>
-      </c>
-      <c r="B309" t="s">
-        <v>913</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -10245,10 +10245,10 @@
     </row>
     <row r="310" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="B310" t="s">
         <v>914</v>
-      </c>
-      <c r="B310" t="s">
-        <v>915</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -10257,10 +10257,10 @@
     </row>
     <row r="311" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="8" t="s">
+        <v>915</v>
+      </c>
+      <c r="B311" t="s">
         <v>916</v>
-      </c>
-      <c r="B311" t="s">
-        <v>917</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -10269,10 +10269,10 @@
     </row>
     <row r="312" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B312" t="s">
         <v>918</v>
-      </c>
-      <c r="B312" t="s">
-        <v>919</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -10281,10 +10281,10 @@
     </row>
     <row r="313" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="B313" t="s">
         <v>920</v>
-      </c>
-      <c r="B313" t="s">
-        <v>921</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -10293,10 +10293,10 @@
     </row>
     <row r="314" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B314" t="s">
         <v>922</v>
-      </c>
-      <c r="B314" t="s">
-        <v>923</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -10305,10 +10305,10 @@
     </row>
     <row r="315" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="B315" t="s">
         <v>924</v>
-      </c>
-      <c r="B315" t="s">
-        <v>925</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -10317,10 +10317,10 @@
     </row>
     <row r="316" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
+        <v>925</v>
+      </c>
+      <c r="B316" t="s">
         <v>926</v>
-      </c>
-      <c r="B316" t="s">
-        <v>927</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -10329,10 +10329,10 @@
     </row>
     <row r="317" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="B317" t="s">
         <v>928</v>
-      </c>
-      <c r="B317" t="s">
-        <v>929</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -10341,10 +10341,10 @@
     </row>
     <row r="318" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="B318" t="s">
         <v>930</v>
-      </c>
-      <c r="B318" t="s">
-        <v>931</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="319" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="B319" t="s">
         <v>932</v>
-      </c>
-      <c r="B319" t="s">
-        <v>933</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="320" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="8" t="s">
+        <v>933</v>
+      </c>
+      <c r="B320" t="s">
         <v>934</v>
-      </c>
-      <c r="B320" t="s">
-        <v>935</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -10377,10 +10377,10 @@
     </row>
     <row r="321" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="8" t="s">
+        <v>935</v>
+      </c>
+      <c r="B321" t="s">
         <v>936</v>
-      </c>
-      <c r="B321" t="s">
-        <v>937</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -10389,10 +10389,10 @@
     </row>
     <row r="322" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="B322" t="s">
         <v>938</v>
-      </c>
-      <c r="B322" t="s">
-        <v>939</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -10401,10 +10401,10 @@
     </row>
     <row r="323" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="B323" t="s">
         <v>940</v>
-      </c>
-      <c r="B323" t="s">
-        <v>941</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -10413,10 +10413,10 @@
     </row>
     <row r="324" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B324" t="s">
         <v>942</v>
-      </c>
-      <c r="B324" t="s">
-        <v>943</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="325" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="B325" t="s">
         <v>944</v>
-      </c>
-      <c r="B325" t="s">
-        <v>945</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -10437,10 +10437,10 @@
     </row>
     <row r="326" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="B326" t="s">
         <v>946</v>
-      </c>
-      <c r="B326" t="s">
-        <v>947</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -10449,10 +10449,10 @@
     </row>
     <row r="327" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="B327" t="s">
         <v>948</v>
-      </c>
-      <c r="B327" t="s">
-        <v>949</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -10461,10 +10461,10 @@
     </row>
     <row r="328" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="B328" t="s">
         <v>950</v>
-      </c>
-      <c r="B328" t="s">
-        <v>951</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -10473,142 +10473,142 @@
     </row>
     <row r="329" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="B329" t="s">
+        <v>953</v>
+      </c>
+      <c r="C329" t="s">
         <v>952</v>
-      </c>
-      <c r="B329" t="s">
-        <v>954</v>
-      </c>
-      <c r="C329" t="s">
-        <v>953</v>
       </c>
       <c r="D329" s="1"/>
     </row>
     <row r="330" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="B330" t="s">
         <v>955</v>
       </c>
-      <c r="B330" t="s">
+      <c r="C330" t="s">
         <v>956</v>
-      </c>
-      <c r="C330" t="s">
-        <v>957</v>
       </c>
       <c r="D330" s="1"/>
     </row>
     <row r="331" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="B331" t="s">
         <v>958</v>
       </c>
-      <c r="B331" t="s">
+      <c r="C331" t="s">
         <v>959</v>
-      </c>
-      <c r="C331" t="s">
-        <v>960</v>
       </c>
       <c r="D331" s="1"/>
     </row>
     <row r="332" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B332" t="s">
+        <v>960</v>
+      </c>
+      <c r="C332" t="s">
         <v>961</v>
-      </c>
-      <c r="C332" t="s">
-        <v>962</v>
       </c>
       <c r="D332" s="1"/>
     </row>
     <row r="333" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="B333" t="s">
+        <v>965</v>
+      </c>
+      <c r="C333" t="s">
         <v>964</v>
-      </c>
-      <c r="B333" t="s">
-        <v>966</v>
-      </c>
-      <c r="C333" t="s">
-        <v>965</v>
       </c>
       <c r="D333" s="1"/>
     </row>
     <row r="334" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="B334" t="s">
+        <v>968</v>
+      </c>
+      <c r="C334" t="s">
         <v>967</v>
-      </c>
-      <c r="B334" t="s">
-        <v>969</v>
-      </c>
-      <c r="C334" t="s">
-        <v>968</v>
       </c>
       <c r="D334" s="1"/>
     </row>
     <row r="335" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335" t="s">
         <v>970</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-      <c r="C335" t="s">
-        <v>971</v>
       </c>
       <c r="D335" s="1"/>
     </row>
     <row r="336" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="B336" t="s">
+        <v>973</v>
+      </c>
+      <c r="C336" t="s">
         <v>972</v>
-      </c>
-      <c r="B336" t="s">
-        <v>974</v>
-      </c>
-      <c r="C336" t="s">
-        <v>973</v>
       </c>
       <c r="D336" s="1"/>
     </row>
     <row r="337" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="B337" t="s">
         <v>975</v>
       </c>
-      <c r="B337" t="s">
+      <c r="C337" t="s">
         <v>976</v>
-      </c>
-      <c r="C337" t="s">
-        <v>977</v>
       </c>
       <c r="D337" s="1"/>
     </row>
     <row r="338" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="B338" t="s">
+        <v>979</v>
+      </c>
+      <c r="C338" t="s">
         <v>978</v>
-      </c>
-      <c r="B338" t="s">
-        <v>980</v>
-      </c>
-      <c r="C338" t="s">
-        <v>979</v>
       </c>
       <c r="D338" s="1"/>
     </row>
     <row r="339" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="B339" t="s">
+        <v>982</v>
+      </c>
+      <c r="C339" t="s">
         <v>981</v>
-      </c>
-      <c r="B339" t="s">
-        <v>983</v>
-      </c>
-      <c r="C339" t="s">
-        <v>982</v>
       </c>
       <c r="D339" s="1"/>
     </row>
     <row r="340" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="B340" t="s">
         <v>984</v>
-      </c>
-      <c r="B340" t="s">
-        <v>985</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -10617,10 +10617,10 @@
     </row>
     <row r="341" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="B341" t="s">
         <v>986</v>
-      </c>
-      <c r="B341" t="s">
-        <v>987</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -10629,130 +10629,130 @@
     </row>
     <row r="342" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="B342" t="s">
         <v>988</v>
       </c>
-      <c r="B342" t="s">
+      <c r="C342" t="s">
         <v>989</v>
-      </c>
-      <c r="C342" t="s">
-        <v>990</v>
       </c>
       <c r="D342" s="1"/>
     </row>
     <row r="343" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B343" t="s">
         <v>991</v>
       </c>
-      <c r="B343" t="s">
+      <c r="C343" t="s">
         <v>992</v>
-      </c>
-      <c r="C343" t="s">
-        <v>993</v>
       </c>
       <c r="D343" s="1"/>
     </row>
     <row r="344" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="B344" t="s">
+        <v>995</v>
+      </c>
+      <c r="C344" t="s">
         <v>994</v>
-      </c>
-      <c r="B344" t="s">
-        <v>996</v>
-      </c>
-      <c r="C344" t="s">
-        <v>995</v>
       </c>
       <c r="D344" s="1"/>
     </row>
     <row r="345" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="B345" t="s">
+        <v>998</v>
+      </c>
+      <c r="C345" t="s">
         <v>997</v>
-      </c>
-      <c r="B345" t="s">
-        <v>999</v>
-      </c>
-      <c r="C345" t="s">
-        <v>998</v>
       </c>
       <c r="D345" s="1"/>
     </row>
     <row r="346" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="B346" t="s">
         <v>1000</v>
       </c>
-      <c r="B346" t="s">
+      <c r="C346" t="s">
         <v>1001</v>
-      </c>
-      <c r="C346" t="s">
-        <v>1002</v>
       </c>
       <c r="D346" s="1"/>
     </row>
     <row r="347" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B347" t="s">
         <v>1003</v>
       </c>
-      <c r="B347" t="s">
+      <c r="C347" t="s">
         <v>1004</v>
-      </c>
-      <c r="C347" t="s">
-        <v>1005</v>
       </c>
       <c r="D347" s="1"/>
     </row>
     <row r="348" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B348" t="s">
         <v>1006</v>
       </c>
-      <c r="B348" t="s">
+      <c r="C348" t="s">
         <v>1007</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1008</v>
       </c>
       <c r="D348" s="1"/>
     </row>
     <row r="349" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B349" t="s">
         <v>1009</v>
       </c>
-      <c r="B349" t="s">
+      <c r="C349" t="s">
         <v>1010</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1011</v>
       </c>
       <c r="D349" s="1"/>
     </row>
     <row r="350" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C350" t="s">
         <v>1012</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1013</v>
       </c>
       <c r="D350" s="1"/>
     </row>
     <row r="351" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C351" t="s">
         <v>1015</v>
-      </c>
-      <c r="B351" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1016</v>
       </c>
       <c r="D351" s="1"/>
     </row>
     <row r="352" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B352" t="s">
         <v>1018</v>
-      </c>
-      <c r="B352" t="s">
-        <v>1019</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -10761,10 +10761,10 @@
     </row>
     <row r="353" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B353" t="s">
         <v>1021</v>
-      </c>
-      <c r="B353" t="s">
-        <v>1022</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -10773,10 +10773,10 @@
     </row>
     <row r="354" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B354" t="s">
         <v>1023</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1024</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -10785,10 +10785,10 @@
     </row>
     <row r="355" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B355" t="s">
         <v>1025</v>
-      </c>
-      <c r="B355" t="s">
-        <v>1026</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -10797,22 +10797,22 @@
     </row>
     <row r="356" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B356" t="s">
         <v>1027</v>
       </c>
-      <c r="B356" t="s">
+      <c r="C356" t="s">
         <v>1028</v>
-      </c>
-      <c r="C356" t="s">
-        <v>1029</v>
       </c>
       <c r="D356" s="1"/>
     </row>
     <row r="357" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B357" t="s">
         <v>1030</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1031</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="358" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B358" t="s">
         <v>1032</v>
-      </c>
-      <c r="B358" t="s">
-        <v>1033</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -10833,10 +10833,10 @@
     </row>
     <row r="359" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B359" t="s">
         <v>1034</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1035</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -10845,31 +10845,31 @@
     </row>
     <row r="360" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C360" t="s">
         <v>1036</v>
-      </c>
-      <c r="B360" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C360" t="s">
-        <v>1037</v>
       </c>
       <c r="D360" s="1"/>
     </row>
     <row r="361" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C361" t="s">
         <v>1039</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C361" t="s">
-        <v>1040</v>
       </c>
       <c r="D361" s="1"/>
     </row>
     <row r="362" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -10881,10 +10881,10 @@
     </row>
     <row r="363" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B363" t="s">
         <v>1043</v>
-      </c>
-      <c r="B363" t="s">
-        <v>1044</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -10893,142 +10893,142 @@
     </row>
     <row r="364" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B364" t="s">
         <v>1045</v>
       </c>
-      <c r="B364" t="s">
+      <c r="C364" t="s">
         <v>1046</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1047</v>
       </c>
       <c r="D364" s="1"/>
     </row>
     <row r="365" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B365" t="s">
         <v>1048</v>
       </c>
-      <c r="B365" t="s">
+      <c r="C365" t="s">
         <v>1049</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1050</v>
       </c>
       <c r="D365" s="1"/>
     </row>
     <row r="366" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B366" t="s">
         <v>1051</v>
       </c>
-      <c r="B366" t="s">
+      <c r="C366" t="s">
         <v>1052</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1053</v>
       </c>
       <c r="D366" s="1"/>
     </row>
     <row r="367" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B367" t="s">
         <v>1054</v>
       </c>
-      <c r="B367" t="s">
+      <c r="C367" t="s">
         <v>1055</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1056</v>
       </c>
       <c r="D367" s="1"/>
     </row>
     <row r="368" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B368" t="s">
         <v>1057</v>
       </c>
-      <c r="B368" t="s">
+      <c r="C368" t="s">
         <v>1058</v>
-      </c>
-      <c r="C368" t="s">
-        <v>1059</v>
       </c>
       <c r="D368" s="1"/>
     </row>
     <row r="369" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B369" t="s">
         <v>1060</v>
       </c>
-      <c r="B369" t="s">
+      <c r="C369" t="s">
         <v>1061</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1062</v>
       </c>
       <c r="D369" s="1"/>
     </row>
     <row r="370" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C370" t="s">
         <v>1063</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C370" t="s">
-        <v>1064</v>
       </c>
       <c r="D370" s="1"/>
     </row>
     <row r="371" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="8" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B371" t="s">
         <v>1066</v>
       </c>
-      <c r="B371" t="s">
+      <c r="C371" t="s">
         <v>1067</v>
-      </c>
-      <c r="C371" t="s">
-        <v>1068</v>
       </c>
       <c r="D371" s="1"/>
     </row>
     <row r="372" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="8" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B372" t="s">
         <v>1069</v>
       </c>
-      <c r="B372" t="s">
+      <c r="C372" t="s">
         <v>1070</v>
-      </c>
-      <c r="C372" t="s">
-        <v>1071</v>
       </c>
       <c r="D372" s="1"/>
     </row>
     <row r="373" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B373" t="s">
         <v>1072</v>
       </c>
-      <c r="B373" t="s">
+      <c r="C373" t="s">
         <v>1073</v>
-      </c>
-      <c r="C373" t="s">
-        <v>1074</v>
       </c>
       <c r="D373" s="1"/>
     </row>
     <row r="374" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="8" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B374" t="s">
         <v>1075</v>
       </c>
-      <c r="B374" t="s">
+      <c r="C374" t="s">
         <v>1076</v>
-      </c>
-      <c r="C374" t="s">
-        <v>1077</v>
       </c>
       <c r="D374" s="1"/>
     </row>
     <row r="375" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B375" t="s">
         <v>1078</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1079</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -11037,22 +11037,22 @@
     </row>
     <row r="376" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B376" t="s">
         <v>1080</v>
       </c>
-      <c r="B376" t="s">
+      <c r="C376" t="s">
         <v>1081</v>
-      </c>
-      <c r="C376" t="s">
-        <v>1082</v>
       </c>
       <c r="D376" s="1"/>
     </row>
     <row r="377" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B377" t="s">
         <v>1083</v>
-      </c>
-      <c r="B377" t="s">
-        <v>1084</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -11061,10 +11061,10 @@
     </row>
     <row r="378" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B378" t="s">
         <v>1085</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1086</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -11073,22 +11073,22 @@
     </row>
     <row r="379" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B379" t="s">
         <v>1087</v>
       </c>
-      <c r="B379" t="s">
+      <c r="C379" t="s">
         <v>1088</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1089</v>
       </c>
       <c r="D379" s="1"/>
     </row>
     <row r="380" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B380" t="s">
         <v>1090</v>
-      </c>
-      <c r="B380" t="s">
-        <v>1091</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -11097,22 +11097,22 @@
     </row>
     <row r="381" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="8" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381" t="s">
         <v>1092</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1093</v>
       </c>
       <c r="D381" s="1"/>
     </row>
     <row r="382" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="8" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B382" t="s">
         <v>1094</v>
-      </c>
-      <c r="B382" t="s">
-        <v>1095</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -11121,43 +11121,43 @@
     </row>
     <row r="383" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="8" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B383" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C383" t="s">
         <v>1098</v>
-      </c>
-      <c r="C383" t="s">
-        <v>1099</v>
       </c>
       <c r="D383" s="1"/>
     </row>
     <row r="384" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="8" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B384">
         <v>0</v>
       </c>
       <c r="C384" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D384" s="1"/>
     </row>
     <row r="385" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385" t="s">
         <v>1101</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385" t="s">
-        <v>1102</v>
       </c>
       <c r="D385" s="1"/>
     </row>
     <row r="386" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="8" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -11169,22 +11169,22 @@
     </row>
     <row r="387" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B387" t="s">
         <v>1104</v>
       </c>
-      <c r="B387" t="s">
+      <c r="C387" t="s">
         <v>1105</v>
-      </c>
-      <c r="C387" t="s">
-        <v>1106</v>
       </c>
       <c r="D387" s="1"/>
     </row>
     <row r="388" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B388" t="s">
         <v>1107</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1108</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -11193,70 +11193,70 @@
     </row>
     <row r="389" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389" t="s">
         <v>1109</v>
-      </c>
-      <c r="B389">
-        <v>0</v>
-      </c>
-      <c r="C389" t="s">
-        <v>1110</v>
       </c>
       <c r="D389" s="1"/>
     </row>
     <row r="390" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B390" t="s">
         <v>1111</v>
       </c>
-      <c r="B390" t="s">
+      <c r="C390" t="s">
         <v>1112</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1113</v>
       </c>
       <c r="D390" s="1"/>
     </row>
     <row r="391" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="8" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391" t="s">
         <v>1114</v>
-      </c>
-      <c r="B391">
-        <v>0</v>
-      </c>
-      <c r="C391" t="s">
-        <v>1115</v>
       </c>
       <c r="D391" s="1"/>
     </row>
     <row r="392" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="8" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B392" t="s">
         <v>1116</v>
       </c>
-      <c r="B392" t="s">
+      <c r="C392" t="s">
         <v>1117</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1118</v>
       </c>
       <c r="D392" s="1"/>
     </row>
     <row r="393" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="8" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B393" t="s">
         <v>1119</v>
       </c>
-      <c r="B393" t="s">
+      <c r="C393" t="s">
         <v>1120</v>
-      </c>
-      <c r="C393" t="s">
-        <v>1121</v>
       </c>
       <c r="D393" s="1"/>
     </row>
     <row r="394" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B394" t="s">
         <v>1122</v>
-      </c>
-      <c r="B394" t="s">
-        <v>1123</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -11265,46 +11265,46 @@
     </row>
     <row r="395" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B395" t="s">
         <v>1124</v>
       </c>
-      <c r="B395" t="s">
+      <c r="C395" t="s">
         <v>1125</v>
-      </c>
-      <c r="C395" t="s">
-        <v>1126</v>
       </c>
       <c r="D395" s="1"/>
     </row>
     <row r="396" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="8" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B396" t="s">
         <v>1127</v>
       </c>
-      <c r="B396" t="s">
+      <c r="C396" t="s">
         <v>1128</v>
-      </c>
-      <c r="C396" t="s">
-        <v>1129</v>
       </c>
       <c r="D396" s="1"/>
     </row>
     <row r="397" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C397" t="s">
         <v>1130</v>
-      </c>
-      <c r="B397" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C397" t="s">
-        <v>1131</v>
       </c>
       <c r="D397" s="1"/>
     </row>
     <row r="398" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B398" t="s">
         <v>1133</v>
-      </c>
-      <c r="B398" t="s">
-        <v>1134</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -11313,10 +11313,10 @@
     </row>
     <row r="399" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="8" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B399" t="s">
         <v>1135</v>
-      </c>
-      <c r="B399" t="s">
-        <v>1136</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -11325,34 +11325,34 @@
     </row>
     <row r="400" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="8" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C400" t="s">
         <v>1137</v>
-      </c>
-      <c r="B400" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C400" t="s">
-        <v>1138</v>
       </c>
       <c r="D400" s="1"/>
     </row>
     <row r="401" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="8" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B401" t="s">
         <v>1140</v>
       </c>
-      <c r="B401" t="s">
+      <c r="C401" t="s">
         <v>1141</v>
-      </c>
-      <c r="C401" t="s">
-        <v>1142</v>
       </c>
       <c r="D401" s="1"/>
     </row>
     <row r="402" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B402" t="s">
         <v>1143</v>
-      </c>
-      <c r="B402" t="s">
-        <v>1144</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -11361,94 +11361,94 @@
     </row>
     <row r="403" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="8" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B403" t="s">
         <v>1145</v>
       </c>
-      <c r="B403" t="s">
+      <c r="C403" t="s">
         <v>1146</v>
-      </c>
-      <c r="C403" t="s">
-        <v>1147</v>
       </c>
       <c r="D403" s="1"/>
     </row>
     <row r="404" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="8" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B404" t="s">
         <v>1148</v>
       </c>
-      <c r="B404" t="s">
+      <c r="C404" t="s">
         <v>1149</v>
-      </c>
-      <c r="C404" t="s">
-        <v>1150</v>
       </c>
       <c r="D404" s="1"/>
     </row>
     <row r="405" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B405" t="s">
         <v>1151</v>
       </c>
-      <c r="B405" t="s">
+      <c r="C405" t="s">
         <v>1152</v>
-      </c>
-      <c r="C405" t="s">
-        <v>1153</v>
       </c>
       <c r="D405" s="1"/>
     </row>
     <row r="406" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="8" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B406" t="s">
         <v>1154</v>
       </c>
-      <c r="B406" t="s">
+      <c r="C406" t="s">
         <v>1155</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1156</v>
       </c>
       <c r="D406" s="1"/>
     </row>
     <row r="407" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="8" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C407" t="s">
         <v>1157</v>
-      </c>
-      <c r="B407" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C407" t="s">
-        <v>1158</v>
       </c>
       <c r="D407" s="1"/>
     </row>
     <row r="408" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="8" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B408" t="s">
         <v>1160</v>
       </c>
-      <c r="B408" t="s">
+      <c r="C408" t="s">
         <v>1161</v>
-      </c>
-      <c r="C408" t="s">
-        <v>1162</v>
       </c>
       <c r="D408" s="1"/>
     </row>
     <row r="409" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="8" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B409" t="s">
         <v>1163</v>
       </c>
-      <c r="B409" t="s">
+      <c r="C409" t="s">
         <v>1164</v>
-      </c>
-      <c r="C409" t="s">
-        <v>1165</v>
       </c>
       <c r="D409" s="1"/>
     </row>
     <row r="410" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="8" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B410" t="s">
         <v>1166</v>
-      </c>
-      <c r="B410" t="s">
-        <v>1167</v>
       </c>
       <c r="C410" t="s">
         <v>381</v>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="411" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="8" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B411" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C411" t="s">
         <v>381</v>
@@ -11469,82 +11469,82 @@
     </row>
     <row r="412" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="8" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C412" t="s">
         <v>1169</v>
-      </c>
-      <c r="B412" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C412" t="s">
-        <v>1170</v>
       </c>
       <c r="D412" s="1"/>
     </row>
     <row r="413" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C413" t="s">
         <v>1172</v>
-      </c>
-      <c r="B413" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C413" t="s">
-        <v>1173</v>
       </c>
       <c r="D413" s="1"/>
     </row>
     <row r="414" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B414" t="s">
         <v>1175</v>
       </c>
-      <c r="B414" t="s">
+      <c r="C414" t="s">
         <v>1176</v>
-      </c>
-      <c r="C414" t="s">
-        <v>1177</v>
       </c>
       <c r="D414" s="1"/>
     </row>
     <row r="415" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B415" t="s">
         <v>1178</v>
       </c>
-      <c r="B415" t="s">
+      <c r="C415" t="s">
         <v>1179</v>
-      </c>
-      <c r="C415" t="s">
-        <v>1180</v>
       </c>
       <c r="D415" s="1"/>
     </row>
     <row r="416" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B416" t="s">
         <v>1181</v>
       </c>
-      <c r="B416" t="s">
+      <c r="C416" t="s">
         <v>1182</v>
-      </c>
-      <c r="C416" t="s">
-        <v>1183</v>
       </c>
       <c r="D416" s="1"/>
     </row>
     <row r="417" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B417" t="s">
         <v>1184</v>
       </c>
-      <c r="B417" t="s">
+      <c r="C417" t="s">
         <v>1185</v>
-      </c>
-      <c r="C417" t="s">
-        <v>1186</v>
       </c>
       <c r="D417" s="1"/>
     </row>
     <row r="418" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B418" t="s">
         <v>1187</v>
-      </c>
-      <c r="B418" t="s">
-        <v>1188</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="419" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B419" t="s">
         <v>1189</v>
-      </c>
-      <c r="B419" t="s">
-        <v>1190</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -11565,10 +11565,10 @@
     </row>
     <row r="420" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B420" t="s">
         <v>1191</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1192</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -11577,82 +11577,82 @@
     </row>
     <row r="421" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C421" t="s">
         <v>1193</v>
-      </c>
-      <c r="B421" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C421" t="s">
-        <v>1194</v>
       </c>
       <c r="D421" s="1"/>
     </row>
     <row r="422" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="8" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C422" t="s">
         <v>1195</v>
-      </c>
-      <c r="B422" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C422" t="s">
-        <v>1196</v>
       </c>
       <c r="D422" s="1"/>
     </row>
     <row r="423" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="8" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B423" t="s">
         <v>1197</v>
       </c>
-      <c r="B423" t="s">
+      <c r="C423" t="s">
         <v>1198</v>
-      </c>
-      <c r="C423" t="s">
-        <v>1199</v>
       </c>
       <c r="D423" s="1"/>
     </row>
     <row r="424" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B424" t="s">
         <v>1200</v>
       </c>
-      <c r="B424" t="s">
+      <c r="C424" t="s">
         <v>1201</v>
-      </c>
-      <c r="C424" t="s">
-        <v>1202</v>
       </c>
       <c r="D424" s="1"/>
     </row>
     <row r="425" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="8" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B425" t="s">
         <v>1203</v>
       </c>
-      <c r="B425" t="s">
+      <c r="C425" t="s">
         <v>1204</v>
-      </c>
-      <c r="C425" t="s">
-        <v>1205</v>
       </c>
       <c r="D425" s="1"/>
     </row>
     <row r="426" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B426" t="s">
         <v>1206</v>
       </c>
-      <c r="B426" t="s">
+      <c r="C426" t="s">
         <v>1207</v>
-      </c>
-      <c r="C426" t="s">
-        <v>1208</v>
       </c>
       <c r="D426" s="1"/>
     </row>
     <row r="427" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B427" t="s">
         <v>1209</v>
-      </c>
-      <c r="B427" t="s">
-        <v>1210</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -11661,10 +11661,10 @@
     </row>
     <row r="428" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="8" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B428" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C428">
         <v>0</v>
@@ -11673,82 +11673,82 @@
     </row>
     <row r="429" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B429" t="s">
         <v>1212</v>
       </c>
-      <c r="B429" t="s">
+      <c r="C429" t="s">
         <v>1213</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1214</v>
       </c>
       <c r="D429" s="1"/>
     </row>
     <row r="430" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B430" t="s">
         <v>1215</v>
       </c>
-      <c r="B430" t="s">
+      <c r="C430" t="s">
         <v>1216</v>
-      </c>
-      <c r="C430" t="s">
-        <v>1217</v>
       </c>
       <c r="D430" s="1"/>
     </row>
     <row r="431" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C431" t="s">
         <v>1218</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C431" t="s">
-        <v>1219</v>
       </c>
       <c r="D431" s="1"/>
     </row>
     <row r="432" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B432" t="s">
         <v>1221</v>
       </c>
-      <c r="B432" t="s">
+      <c r="C432" t="s">
         <v>1222</v>
-      </c>
-      <c r="C432" t="s">
-        <v>1223</v>
       </c>
       <c r="D432" s="1"/>
     </row>
     <row r="433" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C433" t="s">
         <v>1224</v>
-      </c>
-      <c r="B433" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C433" t="s">
-        <v>1225</v>
       </c>
       <c r="D433" s="1"/>
     </row>
     <row r="434" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B434" t="s">
         <v>1227</v>
       </c>
-      <c r="B434" t="s">
+      <c r="C434" t="s">
         <v>1228</v>
-      </c>
-      <c r="C434" t="s">
-        <v>1229</v>
       </c>
       <c r="D434" s="1"/>
     </row>
     <row r="435" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B435" t="s">
         <v>1230</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1231</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="436" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="8" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B436" t="s">
         <v>1232</v>
-      </c>
-      <c r="B436" t="s">
-        <v>1233</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -11769,10 +11769,10 @@
     </row>
     <row r="437" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="8" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B437" t="s">
         <v>1234</v>
-      </c>
-      <c r="B437" t="s">
-        <v>1235</v>
       </c>
       <c r="C437">
         <v>0</v>
@@ -11781,22 +11781,22 @@
     </row>
     <row r="438" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B438" t="s">
         <v>1236</v>
       </c>
-      <c r="B438" t="s">
+      <c r="C438" t="s">
         <v>1237</v>
-      </c>
-      <c r="C438" t="s">
-        <v>1238</v>
       </c>
       <c r="D438" s="1"/>
     </row>
     <row r="439" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B439" t="s">
         <v>1239</v>
-      </c>
-      <c r="B439" t="s">
-        <v>1240</v>
       </c>
       <c r="C439">
         <v>0</v>
@@ -11805,34 +11805,34 @@
     </row>
     <row r="440" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B440" t="s">
         <v>1241</v>
       </c>
-      <c r="B440" t="s">
+      <c r="C440" s="1" t="s">
         <v>1242</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>1243</v>
       </c>
       <c r="D440" s="1"/>
     </row>
     <row r="441" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B441" t="s">
         <v>1244</v>
       </c>
-      <c r="B441" t="s">
+      <c r="C441" t="s">
         <v>1245</v>
-      </c>
-      <c r="C441" t="s">
-        <v>1246</v>
       </c>
       <c r="D441" s="1"/>
     </row>
     <row r="442" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B442" t="s">
         <v>1247</v>
-      </c>
-      <c r="B442" t="s">
-        <v>1248</v>
       </c>
       <c r="C442">
         <v>0</v>
@@ -11841,70 +11841,70 @@
     </row>
     <row r="443" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B443" t="s">
         <v>1249</v>
       </c>
-      <c r="B443" t="s">
+      <c r="C443" t="s">
         <v>1250</v>
-      </c>
-      <c r="C443" t="s">
-        <v>1251</v>
       </c>
       <c r="D443" s="1"/>
     </row>
     <row r="444" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B444" t="s">
         <v>1252</v>
       </c>
-      <c r="B444" t="s">
+      <c r="C444" t="s">
         <v>1253</v>
-      </c>
-      <c r="C444" t="s">
-        <v>1254</v>
       </c>
       <c r="D444" s="1"/>
     </row>
     <row r="445" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B445" t="s">
         <v>1255</v>
       </c>
-      <c r="B445" t="s">
+      <c r="C445" t="s">
         <v>1256</v>
-      </c>
-      <c r="C445" t="s">
-        <v>1257</v>
       </c>
       <c r="D445" s="1"/>
     </row>
     <row r="446" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="8" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B446" t="s">
         <v>1258</v>
       </c>
-      <c r="B446" t="s">
+      <c r="C446" t="s">
         <v>1259</v>
-      </c>
-      <c r="C446" t="s">
-        <v>1260</v>
       </c>
       <c r="D446" s="1"/>
     </row>
     <row r="447" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C447" t="s">
         <v>1261</v>
-      </c>
-      <c r="B447" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C447" t="s">
-        <v>1262</v>
       </c>
       <c r="D447" s="1"/>
     </row>
     <row r="448" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B448" t="s">
         <v>1264</v>
-      </c>
-      <c r="B448" t="s">
-        <v>1265</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -11913,10 +11913,10 @@
     </row>
     <row r="449" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B449" t="s">
         <v>1266</v>
-      </c>
-      <c r="B449" t="s">
-        <v>1267</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -11925,10 +11925,10 @@
     </row>
     <row r="450" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B450" t="s">
         <v>1268</v>
-      </c>
-      <c r="B450" t="s">
-        <v>1269</v>
       </c>
       <c r="C450">
         <v>0</v>
@@ -11937,166 +11937,166 @@
     </row>
     <row r="451" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C451" t="s">
         <v>1270</v>
-      </c>
-      <c r="B451" t="s">
-        <v>1535</v>
-      </c>
-      <c r="C451" t="s">
-        <v>1271</v>
       </c>
       <c r="D451" s="1"/>
     </row>
     <row r="452" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C452" t="s">
         <v>1272</v>
-      </c>
-      <c r="B452" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C452" t="s">
-        <v>1273</v>
       </c>
       <c r="D452" s="1"/>
     </row>
     <row r="453" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C453" t="s">
         <v>1275</v>
-      </c>
-      <c r="B453" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C453" t="s">
-        <v>1276</v>
       </c>
       <c r="D453" s="1"/>
     </row>
     <row r="454" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C454" t="s">
         <v>1278</v>
-      </c>
-      <c r="B454" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C454" t="s">
-        <v>1279</v>
       </c>
       <c r="D454" s="1"/>
     </row>
     <row r="455" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B455" t="s">
         <v>1281</v>
       </c>
-      <c r="B455" t="s">
+      <c r="C455" t="s">
         <v>1282</v>
-      </c>
-      <c r="C455" t="s">
-        <v>1283</v>
       </c>
       <c r="D455" s="1"/>
     </row>
     <row r="456" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B456" t="s">
         <v>1284</v>
       </c>
-      <c r="B456" t="s">
+      <c r="C456" t="s">
         <v>1285</v>
-      </c>
-      <c r="C456" t="s">
-        <v>1286</v>
       </c>
       <c r="D456" s="1"/>
     </row>
     <row r="457" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B457" t="s">
         <v>1287</v>
       </c>
-      <c r="B457" t="s">
+      <c r="C457" t="s">
         <v>1288</v>
-      </c>
-      <c r="C457" t="s">
-        <v>1289</v>
       </c>
       <c r="D457" s="1"/>
     </row>
     <row r="458" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B458" t="s">
         <v>1290</v>
       </c>
-      <c r="B458" t="s">
+      <c r="C458" t="s">
         <v>1291</v>
-      </c>
-      <c r="C458" t="s">
-        <v>1292</v>
       </c>
       <c r="D458" s="1"/>
     </row>
     <row r="459" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B459" t="s">
         <v>1293</v>
       </c>
-      <c r="B459" t="s">
+      <c r="C459" t="s">
         <v>1294</v>
-      </c>
-      <c r="C459" t="s">
-        <v>1295</v>
       </c>
       <c r="D459" s="1"/>
     </row>
     <row r="460" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B460" t="s">
         <v>1296</v>
       </c>
-      <c r="B460" t="s">
+      <c r="C460" t="s">
         <v>1297</v>
-      </c>
-      <c r="C460" t="s">
-        <v>1298</v>
       </c>
       <c r="D460" s="1"/>
     </row>
     <row r="461" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="8" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B461" t="s">
         <v>1299</v>
       </c>
-      <c r="B461" t="s">
+      <c r="C461" t="s">
         <v>1300</v>
-      </c>
-      <c r="C461" t="s">
-        <v>1301</v>
       </c>
       <c r="D461" s="1"/>
     </row>
     <row r="462" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="8" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C462" t="s">
         <v>1302</v>
-      </c>
-      <c r="B462" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1303</v>
       </c>
       <c r="D462" s="1"/>
     </row>
     <row r="463" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B463" t="s">
         <v>1305</v>
       </c>
-      <c r="B463" t="s">
+      <c r="C463" t="s">
         <v>1306</v>
-      </c>
-      <c r="C463" t="s">
-        <v>1307</v>
       </c>
       <c r="D463" s="1"/>
     </row>
     <row r="464" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="8" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B464" t="s">
         <v>1308</v>
-      </c>
-      <c r="B464" t="s">
-        <v>1309</v>
       </c>
       <c r="C464">
         <v>0</v>
@@ -12105,10 +12105,10 @@
     </row>
     <row r="465" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="8" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B465" t="s">
         <v>1310</v>
-      </c>
-      <c r="B465" t="s">
-        <v>1311</v>
       </c>
       <c r="C465" t="s">
         <v>381</v>
@@ -12117,10 +12117,10 @@
     </row>
     <row r="466" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B466" t="s">
         <v>1312</v>
-      </c>
-      <c r="B466" t="s">
-        <v>1313</v>
       </c>
       <c r="C466">
         <v>0</v>
@@ -12129,118 +12129,118 @@
     </row>
     <row r="467" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B467" t="s">
         <v>1314</v>
       </c>
-      <c r="B467" t="s">
+      <c r="C467" t="s">
         <v>1315</v>
-      </c>
-      <c r="C467" t="s">
-        <v>1316</v>
       </c>
       <c r="D467" s="1"/>
     </row>
     <row r="468" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B468" t="s">
         <v>1317</v>
       </c>
-      <c r="B468" t="s">
+      <c r="C468" t="s">
         <v>1318</v>
-      </c>
-      <c r="C468" t="s">
-        <v>1319</v>
       </c>
       <c r="D468" s="1"/>
     </row>
     <row r="469" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B469" t="s">
         <v>1320</v>
       </c>
-      <c r="B469" t="s">
+      <c r="C469" t="s">
         <v>1321</v>
-      </c>
-      <c r="C469" t="s">
-        <v>1322</v>
       </c>
       <c r="D469" s="1"/>
     </row>
     <row r="470" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B470" t="s">
         <v>1323</v>
       </c>
-      <c r="B470" t="s">
+      <c r="C470" t="s">
         <v>1324</v>
-      </c>
-      <c r="C470" t="s">
-        <v>1325</v>
       </c>
       <c r="D470" s="1"/>
     </row>
     <row r="471" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B471" t="s">
         <v>1326</v>
       </c>
-      <c r="B471" t="s">
+      <c r="C471" t="s">
         <v>1327</v>
-      </c>
-      <c r="C471" t="s">
-        <v>1328</v>
       </c>
       <c r="D471" s="1"/>
     </row>
     <row r="472" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="8" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B472" t="s">
         <v>1329</v>
       </c>
-      <c r="B472" t="s">
+      <c r="C472" t="s">
         <v>1330</v>
-      </c>
-      <c r="C472" t="s">
-        <v>1331</v>
       </c>
       <c r="D472" s="1"/>
     </row>
     <row r="473" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="8" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B473" t="s">
         <v>1332</v>
       </c>
-      <c r="B473" t="s">
+      <c r="C473" t="s">
         <v>1333</v>
-      </c>
-      <c r="C473" t="s">
-        <v>1334</v>
       </c>
       <c r="D473" s="1"/>
     </row>
     <row r="474" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B474" t="s">
         <v>1335</v>
       </c>
-      <c r="B474" t="s">
+      <c r="C474" t="s">
         <v>1336</v>
-      </c>
-      <c r="C474" t="s">
-        <v>1337</v>
       </c>
       <c r="D474" s="1"/>
     </row>
     <row r="475" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="8" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B475" t="s">
         <v>1338</v>
       </c>
-      <c r="B475" t="s">
+      <c r="C475" t="s">
         <v>1339</v>
-      </c>
-      <c r="C475" t="s">
-        <v>1340</v>
       </c>
       <c r="D475" s="1"/>
     </row>
     <row r="476" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="8" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B476" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C476">
         <v>0</v>
@@ -12249,10 +12249,10 @@
     </row>
     <row r="477" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="8" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B477" t="s">
         <v>1343</v>
-      </c>
-      <c r="B477" t="s">
-        <v>1344</v>
       </c>
       <c r="C477">
         <v>0</v>
@@ -12261,34 +12261,34 @@
     </row>
     <row r="478" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B478" t="s">
         <v>1345</v>
       </c>
-      <c r="B478" t="s">
+      <c r="C478" t="s">
         <v>1346</v>
-      </c>
-      <c r="C478" t="s">
-        <v>1347</v>
       </c>
       <c r="D478" s="1"/>
     </row>
     <row r="479" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="8" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C479" t="s">
         <v>1348</v>
-      </c>
-      <c r="B479" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C479" t="s">
-        <v>1349</v>
       </c>
       <c r="D479" s="1"/>
     </row>
     <row r="480" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="8" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B480" t="s">
         <v>1351</v>
-      </c>
-      <c r="B480" t="s">
-        <v>1352</v>
       </c>
       <c r="C480" s="7">
         <v>0</v>
@@ -12297,142 +12297,142 @@
     </row>
     <row r="481" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="8" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C481" t="s">
         <v>1353</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C481" t="s">
-        <v>1354</v>
       </c>
       <c r="D481" s="1"/>
     </row>
     <row r="482" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="8" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B482" t="s">
         <v>1356</v>
       </c>
-      <c r="B482" t="s">
+      <c r="C482" t="s">
         <v>1357</v>
-      </c>
-      <c r="C482" t="s">
-        <v>1358</v>
       </c>
       <c r="D482" s="1"/>
     </row>
     <row r="483" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="8" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B483" t="s">
         <v>1359</v>
       </c>
-      <c r="B483" t="s">
+      <c r="C483" t="s">
         <v>1360</v>
-      </c>
-      <c r="C483" t="s">
-        <v>1361</v>
       </c>
       <c r="D483" s="1"/>
     </row>
     <row r="484" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="8" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C484" t="s">
         <v>1362</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C484" t="s">
-        <v>1363</v>
       </c>
       <c r="D484" s="1"/>
     </row>
     <row r="485" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="8" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B485" t="s">
         <v>1364</v>
       </c>
-      <c r="B485" t="s">
+      <c r="C485" t="s">
         <v>1365</v>
-      </c>
-      <c r="C485" t="s">
-        <v>1366</v>
       </c>
       <c r="D485" s="1"/>
     </row>
     <row r="486" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B486" t="s">
         <v>1367</v>
       </c>
-      <c r="B486" t="s">
+      <c r="C486" t="s">
         <v>1368</v>
-      </c>
-      <c r="C486" t="s">
-        <v>1369</v>
       </c>
       <c r="D486" s="1"/>
     </row>
     <row r="487" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="8" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B487" t="s">
+        <v>683</v>
+      </c>
+      <c r="C487" t="s">
         <v>1370</v>
-      </c>
-      <c r="B487" t="s">
-        <v>684</v>
-      </c>
-      <c r="C487" t="s">
-        <v>1371</v>
       </c>
       <c r="D487" s="1"/>
     </row>
     <row r="488" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="8" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B488" t="s">
         <v>1372</v>
       </c>
-      <c r="B488" t="s">
+      <c r="C488" t="s">
         <v>1373</v>
-      </c>
-      <c r="C488" t="s">
-        <v>1374</v>
       </c>
       <c r="D488" s="1"/>
     </row>
     <row r="489" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B489" t="s">
         <v>1375</v>
       </c>
-      <c r="B489" t="s">
+      <c r="C489" t="s">
         <v>1376</v>
-      </c>
-      <c r="C489" t="s">
-        <v>1377</v>
       </c>
       <c r="D489" s="1"/>
     </row>
     <row r="490" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="8" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B490" t="s">
         <v>1378</v>
       </c>
-      <c r="B490" t="s">
+      <c r="C490" t="s">
         <v>1379</v>
-      </c>
-      <c r="C490" t="s">
-        <v>1380</v>
       </c>
       <c r="D490" s="1"/>
     </row>
     <row r="491" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="8" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B491" t="s">
         <v>1381</v>
       </c>
-      <c r="B491" t="s">
+      <c r="C491" t="s">
         <v>1382</v>
-      </c>
-      <c r="C491" t="s">
-        <v>1383</v>
       </c>
       <c r="D491" s="1"/>
     </row>
     <row r="492" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="8" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B492" t="s">
         <v>1384</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1385</v>
       </c>
       <c r="C492">
         <v>0</v>
@@ -12441,22 +12441,22 @@
     </row>
     <row r="493" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="8" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B493" t="s">
         <v>1386</v>
       </c>
-      <c r="B493" t="s">
+      <c r="C493" t="s">
         <v>1387</v>
-      </c>
-      <c r="C493" t="s">
-        <v>1388</v>
       </c>
       <c r="D493" s="1"/>
     </row>
     <row r="494" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="8" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B494" t="s">
         <v>1389</v>
-      </c>
-      <c r="B494" t="s">
-        <v>1390</v>
       </c>
       <c r="C494">
         <v>0</v>
@@ -12465,58 +12465,58 @@
     </row>
     <row r="495" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="8" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B495" t="s">
         <v>1391</v>
       </c>
-      <c r="B495" t="s">
+      <c r="C495" t="s">
         <v>1392</v>
-      </c>
-      <c r="C495" t="s">
-        <v>1393</v>
       </c>
       <c r="D495" s="1"/>
     </row>
     <row r="496" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="8" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B496" t="s">
         <v>1394</v>
       </c>
-      <c r="B496" t="s">
+      <c r="C496" t="s">
         <v>1395</v>
-      </c>
-      <c r="C496" t="s">
-        <v>1396</v>
       </c>
       <c r="D496" s="1"/>
     </row>
     <row r="497" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="8" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B497">
+        <v>0</v>
+      </c>
+      <c r="C497" t="s">
         <v>1397</v>
-      </c>
-      <c r="B497">
-        <v>0</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1398</v>
       </c>
       <c r="D497" s="1"/>
     </row>
     <row r="498" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B498" t="s">
         <v>1399</v>
       </c>
-      <c r="B498" t="s">
+      <c r="C498" t="s">
         <v>1400</v>
-      </c>
-      <c r="C498" t="s">
-        <v>1401</v>
       </c>
       <c r="D498" s="1"/>
     </row>
     <row r="499" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="8" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B499" t="s">
         <v>1402</v>
-      </c>
-      <c r="B499" t="s">
-        <v>1403</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -12525,10 +12525,10 @@
     </row>
     <row r="500" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="8" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B500" t="s">
         <v>1404</v>
-      </c>
-      <c r="B500" t="s">
-        <v>1405</v>
       </c>
       <c r="C500">
         <v>0</v>
@@ -12537,34 +12537,34 @@
     </row>
     <row r="501" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C501" t="s">
         <v>1406</v>
-      </c>
-      <c r="B501" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C501" t="s">
-        <v>1407</v>
       </c>
       <c r="D501" s="1"/>
     </row>
     <row r="502" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="8" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C502" t="s">
         <v>1409</v>
-      </c>
-      <c r="B502" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C502" t="s">
-        <v>1410</v>
       </c>
       <c r="D502" s="1"/>
     </row>
     <row r="503" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B503" t="s">
         <v>1412</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1413</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -12573,10 +12573,10 @@
     </row>
     <row r="504" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B504" t="s">
         <v>1414</v>
-      </c>
-      <c r="B504" t="s">
-        <v>1415</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -12585,10 +12585,10 @@
     </row>
     <row r="505" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="8" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B505" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C505">
         <v>0</v>
@@ -12597,22 +12597,22 @@
     </row>
     <row r="506" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="8" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B506" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C506" t="s">
         <v>1419</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1420</v>
       </c>
       <c r="D506" s="1"/>
     </row>
     <row r="507" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="8" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B507" t="s">
         <v>1421</v>
-      </c>
-      <c r="B507" t="s">
-        <v>1422</v>
       </c>
       <c r="C507">
         <v>0</v>
@@ -12621,202 +12621,202 @@
     </row>
     <row r="508" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="8" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B508" t="s">
         <v>1423</v>
       </c>
-      <c r="B508" t="s">
+      <c r="C508" t="s">
         <v>1424</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1425</v>
       </c>
       <c r="D508" s="1"/>
     </row>
     <row r="509" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C509" t="s">
         <v>1426</v>
-      </c>
-      <c r="B509" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1427</v>
       </c>
       <c r="D509" s="1"/>
     </row>
     <row r="510" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B510" t="s">
         <v>1429</v>
       </c>
-      <c r="B510" t="s">
+      <c r="C510" t="s">
         <v>1430</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1431</v>
       </c>
       <c r="D510" s="1"/>
     </row>
     <row r="511" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B511" t="s">
         <v>1432</v>
       </c>
-      <c r="B511" t="s">
+      <c r="C511" t="s">
         <v>1433</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1434</v>
       </c>
       <c r="D511" s="1"/>
     </row>
     <row r="512" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="8" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B512" t="s">
         <v>1435</v>
       </c>
-      <c r="B512" t="s">
+      <c r="C512" t="s">
         <v>1436</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1437</v>
       </c>
       <c r="D512" s="1"/>
     </row>
     <row r="513" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="8" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B513" t="s">
         <v>1438</v>
       </c>
-      <c r="B513" t="s">
+      <c r="C513" t="s">
         <v>1439</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1440</v>
       </c>
       <c r="D513" s="1"/>
     </row>
     <row r="514" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B514" t="s">
         <v>1441</v>
       </c>
-      <c r="B514" t="s">
+      <c r="C514" t="s">
         <v>1442</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1443</v>
       </c>
       <c r="D514" s="1"/>
     </row>
     <row r="515" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="8" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B515" t="s">
         <v>1444</v>
       </c>
-      <c r="B515" t="s">
+      <c r="C515" t="s">
         <v>1445</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1446</v>
       </c>
       <c r="D515" s="1"/>
     </row>
     <row r="516" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B516" t="s">
         <v>1447</v>
       </c>
-      <c r="B516" t="s">
+      <c r="C516" t="s">
         <v>1448</v>
-      </c>
-      <c r="C516" t="s">
-        <v>1449</v>
       </c>
       <c r="D516" s="1"/>
     </row>
     <row r="517" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="8" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C517" t="s">
         <v>1450</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1452</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1451</v>
       </c>
       <c r="D517" s="1"/>
     </row>
     <row r="518" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B518" t="s">
         <v>1453</v>
       </c>
-      <c r="B518" t="s">
+      <c r="C518" t="s">
         <v>1454</v>
-      </c>
-      <c r="C518" t="s">
-        <v>1455</v>
       </c>
       <c r="D518" s="1"/>
     </row>
     <row r="519" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B519" t="s">
         <v>1456</v>
       </c>
-      <c r="B519" t="s">
+      <c r="C519" t="s">
         <v>1457</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1458</v>
       </c>
       <c r="D519" s="1"/>
     </row>
     <row r="520" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B520" t="s">
         <v>1459</v>
       </c>
-      <c r="B520" t="s">
+      <c r="C520" t="s">
         <v>1460</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1461</v>
       </c>
       <c r="D520" s="1"/>
     </row>
     <row r="521" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B521" t="s">
         <v>1462</v>
       </c>
-      <c r="B521" t="s">
+      <c r="C521" t="s">
         <v>1463</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1464</v>
       </c>
       <c r="D521" s="1"/>
     </row>
     <row r="522" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="8" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B522" t="s">
         <v>1465</v>
       </c>
-      <c r="B522" t="s">
+      <c r="C522" t="s">
         <v>1466</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1467</v>
       </c>
       <c r="D522" s="1"/>
     </row>
     <row r="523" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="8" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B523" t="s">
         <v>1468</v>
       </c>
-      <c r="B523" t="s">
+      <c r="C523" t="s">
         <v>1469</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1470</v>
       </c>
       <c r="D523" s="1"/>
     </row>
     <row r="524" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="8" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B524" t="s">
         <v>1471</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1472</v>
       </c>
       <c r="C524">
         <v>0</v>
@@ -12825,10 +12825,10 @@
     </row>
     <row r="525" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="8" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B525" t="s">
         <v>1473</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1474</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -12837,10 +12837,10 @@
     </row>
     <row r="526" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="8" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B526" t="s">
         <v>1475</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1476</v>
       </c>
       <c r="C526">
         <v>0</v>
@@ -12849,34 +12849,34 @@
     </row>
     <row r="527" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="8" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B527" s="7">
+        <v>0</v>
+      </c>
+      <c r="C527" t="s">
         <v>1477</v>
-      </c>
-      <c r="B527" s="7">
-        <v>0</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1478</v>
       </c>
       <c r="D527" s="1"/>
     </row>
     <row r="528" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="8" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C528" t="s">
         <v>1479</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1481</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1480</v>
       </c>
       <c r="D528" s="1"/>
     </row>
     <row r="529" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="8" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B529" t="s">
         <v>1482</v>
-      </c>
-      <c r="B529" t="s">
-        <v>1483</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -12885,10 +12885,10 @@
     </row>
     <row r="530" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="8" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B530" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C530">
         <v>0</v>
@@ -12897,82 +12897,82 @@
     </row>
     <row r="531" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="8" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B531" t="s">
         <v>1486</v>
       </c>
-      <c r="B531" t="s">
+      <c r="C531" t="s">
         <v>1487</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1488</v>
       </c>
       <c r="D531" s="1"/>
     </row>
     <row r="532" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="8" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+      <c r="C532" t="s">
         <v>1489</v>
-      </c>
-      <c r="B532">
-        <v>0</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1490</v>
       </c>
       <c r="D532" s="1"/>
     </row>
     <row r="533" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C533" t="s">
         <v>1491</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1493</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1492</v>
       </c>
       <c r="D533" s="1"/>
     </row>
     <row r="534" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B534" t="s">
         <v>1494</v>
       </c>
-      <c r="B534" t="s">
+      <c r="C534" t="s">
         <v>1495</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1496</v>
       </c>
       <c r="D534" s="1"/>
     </row>
     <row r="535" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="8" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C535" t="s">
         <v>1497</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1498</v>
       </c>
       <c r="D535" s="1"/>
     </row>
     <row r="536" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="8" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C536" t="s">
         <v>1500</v>
-      </c>
-      <c r="B536" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1501</v>
       </c>
       <c r="D536" s="1"/>
     </row>
     <row r="537" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="8" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B537" t="s">
         <v>1503</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1504</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -12981,10 +12981,10 @@
     </row>
     <row r="538" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="8" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B538" t="s">
         <v>1505</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1506</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -12993,10 +12993,10 @@
     </row>
     <row r="539" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="8" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B539" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C539">
         <v>0</v>
@@ -13005,34 +13005,34 @@
     </row>
     <row r="540" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="8" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B540" t="s">
         <v>1508</v>
       </c>
-      <c r="B540" t="s">
+      <c r="C540" t="s">
         <v>1509</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1510</v>
       </c>
       <c r="D540" s="1"/>
     </row>
     <row r="541" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="8" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+      <c r="C541" t="s">
         <v>1511</v>
-      </c>
-      <c r="B541">
-        <v>0</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1512</v>
       </c>
       <c r="D541" s="1"/>
     </row>
     <row r="542" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="8" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B542" t="s">
         <v>1513</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1514</v>
       </c>
       <c r="C542">
         <v>0</v>
@@ -13041,22 +13041,22 @@
     </row>
     <row r="543" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="8" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B543" t="s">
         <v>1515</v>
       </c>
-      <c r="B543" t="s">
+      <c r="C543" t="s">
         <v>1516</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1517</v>
       </c>
       <c r="D543" s="1"/>
     </row>
     <row r="544" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B544" t="s">
         <v>1518</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1519</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -13065,10 +13065,10 @@
     </row>
     <row r="545" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="8" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B545" t="s">
         <v>1520</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1521</v>
       </c>
       <c r="C545">
         <v>0</v>
@@ -13077,22 +13077,22 @@
     </row>
     <row r="546" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="8" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B546" t="s">
         <v>1522</v>
       </c>
-      <c r="B546" t="s">
+      <c r="C546" t="s">
         <v>1523</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1524</v>
       </c>
       <c r="D546" s="1"/>
     </row>
     <row r="547" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="8" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B547" t="s">
         <v>1525</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1526</v>
       </c>
       <c r="C547">
         <v>0</v>
@@ -13101,10 +13101,10 @@
     </row>
     <row r="548" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="8" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B548" t="s">
         <v>1527</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1528</v>
       </c>
       <c r="C548">
         <v>0</v>
@@ -13113,10 +13113,10 @@
     </row>
     <row r="549" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B549" t="s">
         <v>1529</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1530</v>
       </c>
       <c r="C549">
         <v>0</v>
@@ -13125,10 +13125,10 @@
     </row>
     <row r="550" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="8" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B550" t="s">
         <v>1547</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1548</v>
       </c>
       <c r="C550">
         <v>0</v>
@@ -13137,10 +13137,10 @@
     </row>
     <row r="551" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="8" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B551" t="s">
         <v>1550</v>
-      </c>
-      <c r="B551" t="s">
-        <v>1551</v>
       </c>
       <c r="C551">
         <v>0</v>
@@ -13149,10 +13149,10 @@
     </row>
     <row r="552" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="8" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B552" t="s">
         <v>1552</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1553</v>
       </c>
       <c r="C552">
         <v>0</v>
@@ -13161,10 +13161,10 @@
     </row>
     <row r="553" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="8" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B553" t="s">
         <v>1579</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1580</v>
       </c>
       <c r="C553">
         <v>0</v>
@@ -13198,7 +13198,7 @@
         <v>10</v>
       </c>
       <c r="B556" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C556" s="1">
         <v>0</v>
@@ -13220,7 +13220,7 @@
         <v>185</v>
       </c>
       <c r="B558" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="C558" t="s">
         <v>186</v>
@@ -13251,13 +13251,13 @@
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C561" t="s">
         <v>1565</v>
-      </c>
-      <c r="B561" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1566</v>
       </c>
       <c r="E561" s="1"/>
     </row>
@@ -13266,7 +13266,7 @@
         <v>163</v>
       </c>
       <c r="B562" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="C562" t="s">
         <v>184</v>
@@ -13309,10 +13309,10 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B566" t="s">
         <v>439</v>
-      </c>
-      <c r="B566" t="s">
-        <v>440</v>
       </c>
       <c r="C566">
         <v>0</v>
@@ -13345,7 +13345,7 @@
         <v>104</v>
       </c>
       <c r="B569" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C569">
         <v>0</v>
@@ -13389,7 +13389,7 @@
         <v>102</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C573" t="s">
         <v>138</v>
@@ -13408,13 +13408,13 @@
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B575" t="s">
         <v>450</v>
       </c>
-      <c r="B575" t="s">
+      <c r="C575" t="s">
         <v>451</v>
-      </c>
-      <c r="C575" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
@@ -13433,7 +13433,7 @@
         <v>149</v>
       </c>
       <c r="B577" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C577">
         <v>0</v>
@@ -13466,10 +13466,10 @@
         <v>157</v>
       </c>
       <c r="B580" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="C580" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -13485,13 +13485,13 @@
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B582" t="s">
+        <v>425</v>
+      </c>
+      <c r="C582" t="s">
         <v>424</v>
-      </c>
-      <c r="B582" t="s">
-        <v>426</v>
-      </c>
-      <c r="C582" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -13510,10 +13510,10 @@
         <v>98</v>
       </c>
       <c r="B584" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="C584" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
@@ -13575,8 +13575,8 @@
       <c r="A590" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B590" s="9" t="s">
-        <v>1581</v>
+      <c r="B590" t="s">
+        <v>1580</v>
       </c>
       <c r="C590" t="s">
         <v>120</v>
@@ -13587,10 +13587,10 @@
         <v>166</v>
       </c>
       <c r="B591" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C591" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="E591" s="1"/>
     </row>
@@ -13631,8 +13631,8 @@
       <c r="A595" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B595" s="9" t="s">
-        <v>1582</v>
+      <c r="B595" t="s">
+        <v>1581</v>
       </c>
       <c r="C595" t="s">
         <v>268</v>
@@ -13708,10 +13708,10 @@
     </row>
     <row r="602" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B602" t="s">
         <v>1577</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1578</v>
       </c>
       <c r="D602" s="1"/>
     </row>
@@ -13739,21 +13739,21 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B605" t="s">
+        <v>594</v>
+      </c>
+      <c r="C605" t="s">
         <v>593</v>
-      </c>
-      <c r="B605" t="s">
-        <v>595</v>
-      </c>
-      <c r="C605" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B606" t="s">
         <v>632</v>
-      </c>
-      <c r="B606" t="s">
-        <v>633</v>
       </c>
       <c r="C606">
         <v>0</v>
@@ -13761,10 +13761,10 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1531</v>
-      </c>
-      <c r="B607" t="s">
-        <v>419</v>
+        <v>1530</v>
+      </c>
+      <c r="B607" s="9" t="s">
+        <v>1582</v>
       </c>
       <c r="C607" t="s">
         <v>204</v>
@@ -13781,8 +13781,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{5A58CD41-CC61-4D83-8620-3795E86571BA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/前缀.xlsx
+++ b/前缀.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lazy\Desktop\Research-on-the-Identification-Mechanism-of-Altmetrics-Data-for-Sina-Weibo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9303601-8073-4167-9D86-E1AC12777F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F998900-D0AD-4E08-A090-F7D503EE24D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$607</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$596</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="1583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="1592">
   <si>
     <t>https://www.tandfonline.com/doi/full/</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -566,10 +566,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNKI</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>万方</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -586,10 +582,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SCIRP 美国科研出版社</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>American Chemical Society/ACS Publications</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -610,10 +602,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>香港科技大学图书馆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://repository.hkust.edu.hk/ir/Record/;https://lbezone.hkust.edu.hk/bib/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1222,10 +1210,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HIGHER EDUCATION PRESS/高等教育出版社前沿期刊</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://journal.hep.com.cn/???/EN/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3251,10 +3235,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://samajournals.co.za/??article/view/3975</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HARVARD LAW SCHOOL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3411,10 +3391,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.opticsjournal.net/Articles/??/Abstract;https://www.opticsjournal.net/Articles/??/FullText;https://researching.cn/articles/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.opticsjournal.net/Articles/GetArticlePDF/;https://www.researching.cn/ArticlePdf/??.pdf</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4823,14 +4799,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://cjcp.ustc.edu.cn/hxwlxb/article/doi/;https://www.cpsjournals.cn/en/article/doi/;https://wulixb.iphy.ac.cn/en/article/doi/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://cjcp.ustc.edu.cn/hxwlxb/article/exportPdf?id=;https://cjcp.ustc.edu.cn/hxwlxb/article/checkArticlePdf?id=;https://www.cpsjournals.cn/eoa-data/cjcp/??/PDF/.pdf;https://wulixb.iphy.ac.cn/article/checkArticlePdf?id=</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CHINESE CHEMICAL SOC</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6299,6 +6267,110 @@
   </si>
   <si>
     <t>https://??/article/??/fulltext;https://??/article/??/abstract;https://??/article/view/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCIRP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>THE HONG KONG UNIVERSITY OF SCIENCE AND TECHNOLOGY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNKI/中国知网</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://samajournals.co.za/??article/view/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.ccspublishing.org.cn/article/doi/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CHINESE JOURNAL OF INORGANIC CHEMISTRY/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无机化学学报</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.ccspublishing.org.cn/article/checkArticlePdf?articleId=;http://www.ccspublishing.org.cn/article/exportPdf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cjcp.ustc.edu.cn/hxwlxb/article/doi/;https://www.cpsjournals.cn/en/article/doi/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wulixb.iphy.ac.cn/en/article/doi/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ACTA PHYSICA SINICA/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物理学报</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cjcp.ustc.edu.cn/hxwlxb/article/exportPdf?id=;https://cjcp.ustc.edu.cn/hxwlxb/article/checkArticlePdf?id=;https://www.cpsjournals.cn/eoa-data/cjcp/??/PDF/.pdf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wulixb.iphy.ac.cn/article/checkArticlePdf?id=</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CHINESE JOURNAL OF LASERS-ZHONGGUO JIGUANG/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中国激光</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.opticsjournal.net/Articles/??/Abstract</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://opg.optica.org/prj/fulltext.cfm?uri=prj;https://opg.optica.org/col/abstract.cfm?uri=col</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://opg.optica.org/col/viewmedia.cfm?uri=prj;https://opg.optica.org/col/viewmedia.cfm?uri=col</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIGHER EDUCATION PRESS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6306,7 +6378,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6358,6 +6430,13 @@
       <color rgb="FF000000"/>
       <name val="Source Sans Pro"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6684,10 +6763,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F613"/>
+  <dimension ref="A1:F610"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.33203125" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
     <col min="2" max="2" width="82.109375" customWidth="1"/>
     <col min="3" max="3" width="86.6640625" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
@@ -6705,7 +6784,7 @@
       </c>
       <c r="D1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6713,27 +6792,27 @@
         <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
       <c r="C2" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B3" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6744,11 +6823,11 @@
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6756,14 +6835,14 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D5" s="3"/>
       <c r="F5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6778,7 +6857,7 @@
       </c>
       <c r="D6" s="2"/>
       <c r="F6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6786,13 +6865,13 @@
         <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>132</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6800,7 +6879,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
       <c r="C8" t="s">
         <v>133</v>
@@ -6811,7 +6890,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -6822,18 +6901,18 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -6855,10 +6934,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6866,10 +6945,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6888,10 +6967,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C16" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -6932,10 +7011,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -6946,7 +7025,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -6965,10 +7044,10 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C23" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -6987,7 +7066,7 @@
         <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>1543</v>
+        <v>1535</v>
       </c>
       <c r="C25" t="s">
         <v>135</v>
@@ -7017,7 +7096,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B28" t="s">
         <v>53</v>
@@ -7045,7 +7124,7 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -7056,7 +7135,7 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7086,7 +7165,7 @@
         <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C34" t="s">
         <v>136</v>
@@ -7097,7 +7176,7 @@
         <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="C35" t="s">
         <v>65</v>
@@ -7105,10 +7184,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B36" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -7119,10 +7198,10 @@
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
       <c r="C37" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -7152,7 +7231,7 @@
         <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
@@ -7160,32 +7239,32 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B41" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C41" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B42" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B43" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -7193,13 +7272,13 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -7215,90 +7294,90 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B46" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C46" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B48" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C48" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C50" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C51" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B52" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C52" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C53" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -7325,57 +7404,57 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C56" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B57" t="s">
+        <v>245</v>
+      </c>
+      <c r="C57" t="s">
         <v>246</v>
-      </c>
-      <c r="B57" t="s">
-        <v>248</v>
-      </c>
-      <c r="C57" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B58" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C58" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B59" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C59" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="6" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7383,54 +7462,54 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="C61" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B62" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
       <c r="C62" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B63" t="s">
-        <v>1544</v>
+        <v>1536</v>
       </c>
       <c r="C63" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -7449,10 +7528,10 @@
         <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C67" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -7496,7 +7575,7 @@
         <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7512,21 +7591,21 @@
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B74" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7534,10 +7613,10 @@
     </row>
     <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7545,32 +7624,32 @@
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B76" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C76" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B77" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
       <c r="C77" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B78" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7578,120 +7657,120 @@
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C79" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C80" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B81" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C81" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B83" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C83" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B85" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C85" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B86" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C86" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B87" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C87" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B88" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C88" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B89" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7699,54 +7778,54 @@
     </row>
     <row r="90" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B90" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C90" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B91" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C91" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B92" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C92" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B93" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C93" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B94" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -7754,10 +7833,10 @@
     </row>
     <row r="95" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B95" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -7765,142 +7844,142 @@
     </row>
     <row r="96" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>307</v>
+        <v>1591</v>
       </c>
       <c r="B96" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C96" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B97" t="s">
         <v>310</v>
       </c>
       <c r="C97" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B98" t="s">
         <v>313</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>314</v>
-      </c>
-      <c r="C98" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B99" t="s">
-        <v>317</v>
+        <v>540</v>
       </c>
       <c r="C99" t="s">
-        <v>318</v>
+        <v>541</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B100" t="s">
         <v>319</v>
       </c>
-      <c r="B100" t="s">
-        <v>544</v>
-      </c>
       <c r="C100" t="s">
-        <v>545</v>
+        <v>317</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B101" t="s">
         <v>323</v>
       </c>
       <c r="C101" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B102" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C102" t="s">
-        <v>328</v>
+        <v>542</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B103" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C103" t="s">
-        <v>546</v>
+        <v>326</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B104" t="s">
+        <v>328</v>
+      </c>
+      <c r="C104" t="s">
         <v>329</v>
-      </c>
-      <c r="B104" t="s">
-        <v>330</v>
-      </c>
-      <c r="C104" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B105" t="s">
         <v>331</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>332</v>
-      </c>
-      <c r="C105" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B106" t="s">
-        <v>335</v>
+        <v>333</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="C106" t="s">
-        <v>336</v>
+        <v>544</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C107" t="s">
-        <v>548</v>
+        <v>334</v>
+      </c>
+      <c r="B107" t="s">
+        <v>545</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B108" t="s">
-        <v>549</v>
+        <v>336</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -7908,57 +7987,57 @@
     </row>
     <row r="109" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B109" t="s">
+        <v>338</v>
+      </c>
+      <c r="C109" t="s">
         <v>339</v>
-      </c>
-      <c r="B109" t="s">
-        <v>340</v>
-      </c>
-      <c r="C109">
-        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s">
         <v>342</v>
       </c>
       <c r="C110" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B111" t="s">
         <v>344</v>
       </c>
-      <c r="B111" t="s">
-        <v>346</v>
-      </c>
       <c r="C111" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B112" t="s">
+        <v>345</v>
+      </c>
+      <c r="C112" t="s">
         <v>347</v>
-      </c>
-      <c r="B112" t="s">
-        <v>348</v>
-      </c>
-      <c r="C112" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s">
         <v>349</v>
       </c>
       <c r="C113" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7966,304 +8045,304 @@
         <v>352</v>
       </c>
       <c r="B114" t="s">
-        <v>353</v>
+        <v>1525</v>
       </c>
       <c r="C114" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B115" t="s">
-        <v>1533</v>
+        <v>355</v>
       </c>
       <c r="C115" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B116" t="s">
-        <v>359</v>
-      </c>
-      <c r="C116" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B117" t="s">
         <v>360</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B118" t="s">
+        <v>362</v>
+      </c>
+      <c r="C118" t="s">
         <v>363</v>
-      </c>
-      <c r="B118" t="s">
-        <v>364</v>
-      </c>
-      <c r="C118" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B119" t="s">
-        <v>366</v>
+        <v>546</v>
       </c>
       <c r="C119" t="s">
-        <v>367</v>
+        <v>546</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B120" t="s">
-        <v>550</v>
+        <v>368</v>
       </c>
       <c r="C120" t="s">
-        <v>550</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B121" t="s">
-        <v>372</v>
+        <v>547</v>
       </c>
       <c r="C121" t="s">
-        <v>371</v>
+        <v>547</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B122" t="s">
         <v>373</v>
       </c>
-      <c r="B122" t="s">
-        <v>551</v>
-      </c>
       <c r="C122" t="s">
-        <v>551</v>
+        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B123" t="s">
         <v>376</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>377</v>
-      </c>
-      <c r="C123" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B124" t="s">
         <v>380</v>
       </c>
       <c r="C124" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B125" t="s">
         <v>382</v>
       </c>
-      <c r="B125" t="s">
-        <v>384</v>
-      </c>
       <c r="C125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>385</v>
+        <v>431</v>
       </c>
       <c r="B126" t="s">
-        <v>386</v>
+        <v>432</v>
       </c>
       <c r="C126" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>435</v>
+        <v>383</v>
       </c>
       <c r="B127" t="s">
-        <v>436</v>
+        <v>384</v>
       </c>
       <c r="C127" t="s">
-        <v>437</v>
+        <v>384</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B128" t="s">
+        <v>386</v>
+      </c>
+      <c r="C128" t="s">
         <v>387</v>
-      </c>
-      <c r="B128" t="s">
-        <v>388</v>
-      </c>
-      <c r="C128" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B129" t="s">
         <v>389</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>390</v>
-      </c>
-      <c r="C129" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B130" t="s">
         <v>392</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>393</v>
-      </c>
-      <c r="C130" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B131" t="s">
         <v>395</v>
       </c>
-      <c r="B131" t="s">
-        <v>396</v>
-      </c>
-      <c r="C131" t="s">
-        <v>397</v>
+      <c r="C131">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B132" t="s">
+        <v>397</v>
+      </c>
+      <c r="C132" t="s">
         <v>398</v>
-      </c>
-      <c r="B132" t="s">
-        <v>399</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B133" t="s">
         <v>400</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>401</v>
-      </c>
-      <c r="C133" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B134" t="s">
-        <v>404</v>
+        <v>548</v>
       </c>
       <c r="C134" t="s">
-        <v>405</v>
+        <v>548</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B135" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C135" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B136" t="s">
-        <v>553</v>
+        <v>405</v>
       </c>
       <c r="C136" t="s">
-        <v>553</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>408</v>
+        <v>448</v>
       </c>
       <c r="B137" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="C137" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B138" t="s">
         <v>452</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>453</v>
-      </c>
-      <c r="C138" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>455</v>
+        <v>407</v>
       </c>
       <c r="B139" t="s">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="C139" t="s">
-        <v>457</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>411</v>
+        <v>454</v>
       </c>
       <c r="B140" t="s">
-        <v>412</v>
+        <v>550</v>
       </c>
       <c r="C140" t="s">
-        <v>413</v>
+        <v>455</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B141" t="s">
         <v>458</v>
-      </c>
-      <c r="B141" t="s">
-        <v>554</v>
       </c>
       <c r="C141" t="s">
         <v>459</v>
@@ -8271,142 +8350,142 @@
     </row>
     <row r="142" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B142" t="s">
         <v>461</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>462</v>
-      </c>
-      <c r="C142" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B143" t="s">
         <v>465</v>
       </c>
       <c r="C143" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B144" t="s">
+        <v>468</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>467</v>
-      </c>
-      <c r="B144" t="s">
-        <v>469</v>
-      </c>
-      <c r="C144" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B145" t="s">
         <v>470</v>
       </c>
-      <c r="B145" t="s">
-        <v>472</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>471</v>
+      <c r="C145">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B146" t="s">
-        <v>474</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
+        <v>1560</v>
+      </c>
+      <c r="C146" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B147" t="s">
+        <v>474</v>
+      </c>
+      <c r="C147" t="s">
         <v>475</v>
-      </c>
-      <c r="B147" t="s">
-        <v>1568</v>
-      </c>
-      <c r="C147" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B148" t="s">
         <v>477</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>478</v>
-      </c>
-      <c r="C148" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B149" t="s">
-        <v>481</v>
-      </c>
-      <c r="C149" t="s">
-        <v>482</v>
+        <v>551</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B150" t="s">
-        <v>555</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
+        <v>481</v>
+      </c>
+      <c r="C150" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B151" t="s">
         <v>484</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>485</v>
-      </c>
-      <c r="C151" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B152" t="s">
-        <v>488</v>
-      </c>
-      <c r="C152" t="s">
-        <v>489</v>
+        <v>552</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B153" t="s">
-        <v>556</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
+        <v>489</v>
+      </c>
+      <c r="C153" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B154" t="s">
         <v>491</v>
-      </c>
-      <c r="B154" t="s">
-        <v>493</v>
       </c>
       <c r="C154" t="s">
         <v>492</v>
@@ -8414,65 +8493,65 @@
     </row>
     <row r="155" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B155" t="s">
         <v>494</v>
       </c>
-      <c r="B155" t="s">
-        <v>495</v>
-      </c>
-      <c r="C155" t="s">
-        <v>496</v>
+      <c r="C155">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B156" t="s">
+        <v>496</v>
+      </c>
+      <c r="C156" t="s">
         <v>497</v>
-      </c>
-      <c r="B156" t="s">
-        <v>498</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B157" t="s">
         <v>499</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>500</v>
-      </c>
-      <c r="C157" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B158" t="s">
         <v>503</v>
       </c>
       <c r="C158" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B159" t="s">
-        <v>507</v>
-      </c>
-      <c r="C159" t="s">
-        <v>506</v>
+        <v>553</v>
+      </c>
+      <c r="C159" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B160" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C160" s="7">
         <v>0</v>
@@ -8480,109 +8559,109 @@
     </row>
     <row r="161" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B161" t="s">
-        <v>558</v>
-      </c>
-      <c r="C161" s="7">
-        <v>0</v>
+        <v>555</v>
+      </c>
+      <c r="C161" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B162" t="s">
-        <v>559</v>
-      </c>
-      <c r="C162" t="s">
-        <v>511</v>
+        <v>509</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B163" t="s">
+        <v>511</v>
+      </c>
+      <c r="C163" t="s">
         <v>512</v>
-      </c>
-      <c r="B163" t="s">
-        <v>513</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B164" t="s">
         <v>515</v>
       </c>
       <c r="C164" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B165" t="s">
         <v>517</v>
-      </c>
-      <c r="B165" t="s">
-        <v>519</v>
       </c>
       <c r="C165" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
+      <c r="A166" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="B166" t="s">
         <v>520</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>521</v>
-      </c>
-      <c r="C166" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B167" t="s">
         <v>524</v>
       </c>
       <c r="C167" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B168" t="s">
+        <v>527</v>
+      </c>
+      <c r="C168" t="s">
         <v>526</v>
-      </c>
-      <c r="B168" t="s">
-        <v>528</v>
-      </c>
-      <c r="C168" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="B169" t="s">
         <v>529</v>
       </c>
-      <c r="B169" t="s">
-        <v>531</v>
-      </c>
-      <c r="C169" t="s">
-        <v>530</v>
+      <c r="C169">
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B170" t="s">
-        <v>533</v>
+        <v>556</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -8590,54 +8669,54 @@
     </row>
     <row r="171" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>534</v>
+        <v>557</v>
       </c>
       <c r="B171" t="s">
-        <v>560</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
+        <v>558</v>
+      </c>
+      <c r="C171" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="B172" t="s">
         <v>561</v>
       </c>
-      <c r="B172" t="s">
-        <v>562</v>
-      </c>
-      <c r="C172" t="s">
-        <v>563</v>
+      <c r="C172">
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="B173" t="s">
         <v>564</v>
       </c>
-      <c r="B173" t="s">
-        <v>565</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
+      <c r="C173" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="B174" t="s">
+        <v>567</v>
+      </c>
+      <c r="C174" t="s">
         <v>566</v>
-      </c>
-      <c r="B174" t="s">
-        <v>568</v>
-      </c>
-      <c r="C174" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="B175" t="s">
         <v>569</v>
-      </c>
-      <c r="B175" t="s">
-        <v>571</v>
       </c>
       <c r="C175" t="s">
         <v>570</v>
@@ -8645,21 +8724,21 @@
     </row>
     <row r="176" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B176" t="s">
         <v>572</v>
       </c>
-      <c r="B176" t="s">
-        <v>573</v>
-      </c>
-      <c r="C176" t="s">
-        <v>574</v>
+      <c r="C176">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B177" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -8667,10 +8746,10 @@
     </row>
     <row r="178" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B178" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -8678,10 +8757,10 @@
     </row>
     <row r="179" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B179" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -8689,57 +8768,58 @@
     </row>
     <row r="180" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="B180" t="s">
+        <v>580</v>
+      </c>
+      <c r="C180" t="s">
         <v>581</v>
-      </c>
-      <c r="B180" t="s">
-        <v>582</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="B181" t="s">
         <v>583</v>
       </c>
-      <c r="B181" t="s">
-        <v>584</v>
-      </c>
-      <c r="C181" t="s">
-        <v>585</v>
+      <c r="C181">
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="B182" t="s">
+        <v>585</v>
+      </c>
+      <c r="C182" t="s">
         <v>586</v>
-      </c>
-      <c r="B182" t="s">
-        <v>587</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B183" t="s">
-        <v>589</v>
-      </c>
-      <c r="C183" t="s">
-        <v>590</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183" s="1"/>
     </row>
     <row r="184" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>591</v>
       </c>
       <c r="B184" t="s">
-        <v>598</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
+        <v>593</v>
+      </c>
+      <c r="C184" t="s">
+        <v>592</v>
       </c>
       <c r="D184" s="1"/>
     </row>
@@ -8748,139 +8828,139 @@
         <v>595</v>
       </c>
       <c r="B185" t="s">
+        <v>596</v>
+      </c>
+      <c r="C185" t="s">
         <v>597</v>
-      </c>
-      <c r="C185" t="s">
-        <v>596</v>
       </c>
       <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="B186" t="s">
+        <v>598</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C186" t="s">
         <v>600</v>
-      </c>
-      <c r="C186" t="s">
-        <v>601</v>
       </c>
       <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="B187" t="s">
         <v>602</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>605</v>
-      </c>
       <c r="C187" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B188" t="s">
+        <v>605</v>
+      </c>
+      <c r="C188" t="s">
         <v>606</v>
-      </c>
-      <c r="C188" t="s">
-        <v>607</v>
       </c>
       <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="B189" t="s">
         <v>608</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>609</v>
-      </c>
-      <c r="C189" t="s">
-        <v>610</v>
       </c>
       <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="B190" t="s">
         <v>611</v>
       </c>
-      <c r="B190" t="s">
-        <v>612</v>
-      </c>
-      <c r="C190" t="s">
-        <v>613</v>
+      <c r="C190">
+        <v>0</v>
       </c>
       <c r="D190" s="1"/>
     </row>
     <row r="191" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="B191" t="s">
+        <v>613</v>
+      </c>
+      <c r="C191" t="s">
         <v>614</v>
-      </c>
-      <c r="B191" t="s">
-        <v>615</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
       </c>
       <c r="D191" s="1"/>
     </row>
     <row r="192" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="B192" t="s">
         <v>616</v>
       </c>
-      <c r="B192" t="s">
-        <v>617</v>
-      </c>
-      <c r="C192" t="s">
-        <v>618</v>
+      <c r="C192">
+        <v>0</v>
       </c>
       <c r="D192" s="1"/>
     </row>
     <row r="193" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B193" t="s">
+        <v>618</v>
+      </c>
+      <c r="C193" t="s">
         <v>619</v>
-      </c>
-      <c r="B193" t="s">
-        <v>620</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
       </c>
       <c r="D193" s="1"/>
     </row>
     <row r="194" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="B194" t="s">
         <v>621</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>622</v>
-      </c>
-      <c r="C194" t="s">
-        <v>623</v>
       </c>
       <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="B195" t="s">
         <v>624</v>
       </c>
-      <c r="B195" t="s">
-        <v>625</v>
-      </c>
-      <c r="C195" t="s">
-        <v>626</v>
+      <c r="C195">
+        <v>0</v>
       </c>
       <c r="D195" s="1"/>
     </row>
     <row r="196" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B196" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -8889,10 +8969,10 @@
     </row>
     <row r="197" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B197" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8901,34 +8981,34 @@
     </row>
     <row r="198" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="B198" t="s">
+        <v>633</v>
+      </c>
+      <c r="C198" t="s">
         <v>634</v>
-      </c>
-      <c r="B198" t="s">
-        <v>635</v>
-      </c>
-      <c r="C198">
-        <v>0</v>
       </c>
       <c r="D198" s="1"/>
     </row>
     <row r="199" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B199" t="s">
         <v>636</v>
       </c>
-      <c r="B199" t="s">
-        <v>637</v>
-      </c>
-      <c r="C199" t="s">
-        <v>638</v>
+      <c r="C199">
+        <v>0</v>
       </c>
       <c r="D199" s="1"/>
     </row>
     <row r="200" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B200" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -8937,46 +9017,46 @@
     </row>
     <row r="201" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B201" t="s">
         <v>641</v>
       </c>
-      <c r="B201" t="s">
-        <v>642</v>
-      </c>
-      <c r="C201">
-        <v>0</v>
+      <c r="C201" t="s">
+        <v>640</v>
       </c>
       <c r="D201" s="1"/>
     </row>
     <row r="202" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B202" t="s">
+        <v>644</v>
+      </c>
+      <c r="C202" t="s">
         <v>643</v>
-      </c>
-      <c r="B202" t="s">
-        <v>645</v>
-      </c>
-      <c r="C202" t="s">
-        <v>644</v>
       </c>
       <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B203" t="s">
         <v>646</v>
       </c>
-      <c r="B203" t="s">
-        <v>648</v>
-      </c>
-      <c r="C203" t="s">
-        <v>647</v>
+      <c r="C203">
+        <v>0</v>
       </c>
       <c r="D203" s="1"/>
     </row>
     <row r="204" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B204" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -8985,10 +9065,10 @@
     </row>
     <row r="205" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B205" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -8997,10 +9077,10 @@
     </row>
     <row r="206" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B206" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -9009,10 +9089,10 @@
     </row>
     <row r="207" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B207" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -9021,22 +9101,22 @@
     </row>
     <row r="208" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B208" t="s">
         <v>657</v>
       </c>
-      <c r="B208" t="s">
-        <v>658</v>
-      </c>
-      <c r="C208">
-        <v>0</v>
+      <c r="C208" t="s">
+        <v>656</v>
       </c>
       <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="B209" t="s">
         <v>659</v>
-      </c>
-      <c r="B209" t="s">
-        <v>661</v>
       </c>
       <c r="C209" t="s">
         <v>660</v>
@@ -9045,58 +9125,58 @@
     </row>
     <row r="210" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B210" t="s">
         <v>662</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>663</v>
-      </c>
-      <c r="C210" t="s">
-        <v>664</v>
       </c>
       <c r="D210" s="1"/>
     </row>
     <row r="211" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B211" t="s">
         <v>666</v>
       </c>
       <c r="C211" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D211" s="1"/>
     </row>
     <row r="212" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="B212" t="s">
         <v>668</v>
       </c>
-      <c r="B212" t="s">
-        <v>670</v>
-      </c>
-      <c r="C212" t="s">
-        <v>669</v>
+      <c r="C212">
+        <v>0</v>
       </c>
       <c r="D212" s="1"/>
     </row>
     <row r="213" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B213" t="s">
         <v>671</v>
       </c>
-      <c r="B213" t="s">
-        <v>672</v>
-      </c>
-      <c r="C213">
-        <v>0</v>
+      <c r="C213" t="s">
+        <v>670</v>
       </c>
       <c r="D213" s="1"/>
     </row>
     <row r="214" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B214" t="s">
         <v>673</v>
-      </c>
-      <c r="B214" t="s">
-        <v>675</v>
       </c>
       <c r="C214" t="s">
         <v>674</v>
@@ -9105,46 +9185,46 @@
     </row>
     <row r="215" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="B215" t="s">
         <v>676</v>
       </c>
-      <c r="B215" t="s">
-        <v>677</v>
-      </c>
-      <c r="C215" t="s">
-        <v>678</v>
+      <c r="C215">
+        <v>0</v>
       </c>
       <c r="D215" s="1"/>
     </row>
     <row r="216" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B216" t="s">
         <v>679</v>
       </c>
-      <c r="B216" t="s">
-        <v>680</v>
-      </c>
-      <c r="C216">
-        <v>0</v>
+      <c r="C216" t="s">
+        <v>678</v>
       </c>
       <c r="D216" s="1"/>
     </row>
     <row r="217" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B217" t="s">
+        <v>682</v>
+      </c>
+      <c r="C217" t="s">
         <v>681</v>
-      </c>
-      <c r="B217" t="s">
-        <v>683</v>
-      </c>
-      <c r="C217" t="s">
-        <v>682</v>
       </c>
       <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B218" t="s">
         <v>684</v>
-      </c>
-      <c r="B218" t="s">
-        <v>686</v>
       </c>
       <c r="C218" t="s">
         <v>685</v>
@@ -9153,202 +9233,202 @@
     </row>
     <row r="219" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="B219" t="s">
         <v>687</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>688</v>
-      </c>
-      <c r="C219" t="s">
-        <v>689</v>
       </c>
       <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="B220" t="s">
         <v>690</v>
       </c>
-      <c r="B220" t="s">
-        <v>691</v>
-      </c>
-      <c r="C220" t="s">
-        <v>692</v>
+      <c r="C220">
+        <v>0</v>
       </c>
       <c r="D220" s="1"/>
     </row>
     <row r="221" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B221" t="s">
+        <v>692</v>
+      </c>
+      <c r="C221" t="s">
         <v>693</v>
-      </c>
-      <c r="B221" t="s">
-        <v>694</v>
-      </c>
-      <c r="C221">
-        <v>0</v>
       </c>
       <c r="D221" s="1"/>
     </row>
     <row r="222" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="B222" t="s">
         <v>695</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>696</v>
-      </c>
-      <c r="C222" t="s">
-        <v>697</v>
       </c>
       <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B223" t="s">
         <v>699</v>
       </c>
       <c r="C223" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D223" s="1"/>
     </row>
     <row r="224" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="B224" t="s">
+        <v>702</v>
+      </c>
+      <c r="C224" t="s">
         <v>701</v>
-      </c>
-      <c r="B224" t="s">
-        <v>703</v>
-      </c>
-      <c r="C224" t="s">
-        <v>702</v>
       </c>
       <c r="D224" s="1"/>
     </row>
     <row r="225" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="B225" t="s">
         <v>704</v>
       </c>
-      <c r="B225" t="s">
-        <v>706</v>
-      </c>
-      <c r="C225" t="s">
-        <v>705</v>
+      <c r="C225">
+        <v>0</v>
       </c>
       <c r="D225" s="1"/>
     </row>
     <row r="226" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B226" t="s">
-        <v>708</v>
-      </c>
-      <c r="C226">
-        <v>0</v>
+        <v>1529</v>
+      </c>
+      <c r="C226" t="s">
+        <v>1530</v>
       </c>
       <c r="D226" s="1"/>
     </row>
     <row r="227" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B227" t="s">
-        <v>1537</v>
+        <v>707</v>
       </c>
       <c r="C227" t="s">
-        <v>1538</v>
+        <v>708</v>
       </c>
       <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="B228" t="s">
         <v>710</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
         <v>711</v>
-      </c>
-      <c r="C228" t="s">
-        <v>712</v>
       </c>
       <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="B229" t="s">
         <v>713</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>714</v>
-      </c>
-      <c r="C229" t="s">
-        <v>715</v>
       </c>
       <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="B230" t="s">
         <v>716</v>
       </c>
-      <c r="B230" t="s">
-        <v>717</v>
-      </c>
-      <c r="C230" t="s">
-        <v>718</v>
+      <c r="C230">
+        <v>0</v>
       </c>
       <c r="D230" s="1"/>
     </row>
     <row r="231" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B231" t="s">
         <v>719</v>
       </c>
-      <c r="B231" t="s">
-        <v>720</v>
-      </c>
-      <c r="C231">
-        <v>0</v>
+      <c r="C231" t="s">
+        <v>718</v>
       </c>
       <c r="D231" s="1"/>
     </row>
     <row r="232" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B232" t="s">
-        <v>723</v>
-      </c>
-      <c r="C232" t="s">
-        <v>722</v>
+        <v>1564</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
       </c>
       <c r="D232" s="1"/>
     </row>
     <row r="233" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B233" t="s">
-        <v>1572</v>
-      </c>
-      <c r="C233">
-        <v>0</v>
+        <v>722</v>
+      </c>
+      <c r="C233" t="s">
+        <v>723</v>
       </c>
       <c r="D233" s="1"/>
     </row>
     <row r="234" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B234" t="s">
         <v>726</v>
       </c>
       <c r="C234" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D234" s="1"/>
     </row>
     <row r="235" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="B235" t="s">
         <v>728</v>
-      </c>
-      <c r="B235" t="s">
-        <v>730</v>
       </c>
       <c r="C235" t="s">
         <v>729</v>
@@ -9357,22 +9437,22 @@
     </row>
     <row r="236" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="B236" t="s">
         <v>731</v>
       </c>
-      <c r="B236" t="s">
-        <v>732</v>
-      </c>
-      <c r="C236" t="s">
-        <v>733</v>
+      <c r="C236">
+        <v>0</v>
       </c>
       <c r="D236" s="1"/>
     </row>
     <row r="237" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B237" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9381,10 +9461,10 @@
     </row>
     <row r="238" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B238" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9393,46 +9473,46 @@
     </row>
     <row r="239" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B239" t="s">
+        <v>737</v>
+      </c>
+      <c r="C239" t="s">
         <v>738</v>
-      </c>
-      <c r="B239" t="s">
-        <v>739</v>
-      </c>
-      <c r="C239">
-        <v>0</v>
       </c>
       <c r="D239" s="1"/>
     </row>
     <row r="240" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="B240" t="s">
         <v>740</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" t="s">
         <v>741</v>
-      </c>
-      <c r="C240" t="s">
-        <v>742</v>
       </c>
       <c r="D240" s="1"/>
     </row>
     <row r="241" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="B241" t="s">
         <v>743</v>
       </c>
-      <c r="B241" t="s">
-        <v>744</v>
-      </c>
-      <c r="C241" t="s">
-        <v>745</v>
+      <c r="C241">
+        <v>0</v>
       </c>
       <c r="D241" s="1"/>
     </row>
     <row r="242" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B242" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -9441,10 +9521,10 @@
     </row>
     <row r="243" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B243" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -9453,10 +9533,10 @@
     </row>
     <row r="244" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B244" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -9465,10 +9545,10 @@
     </row>
     <row r="245" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B245" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -9477,10 +9557,10 @@
     </row>
     <row r="246" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B246" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9489,58 +9569,58 @@
     </row>
     <row r="247" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="B247" t="s">
+        <v>755</v>
+      </c>
+      <c r="C247" t="s">
         <v>756</v>
-      </c>
-      <c r="B247" t="s">
-        <v>757</v>
-      </c>
-      <c r="C247">
-        <v>0</v>
       </c>
       <c r="D247" s="1"/>
     </row>
     <row r="248" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="B248" t="s">
         <v>758</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" t="s">
         <v>759</v>
-      </c>
-      <c r="C248" t="s">
-        <v>760</v>
       </c>
       <c r="D248" s="1"/>
     </row>
     <row r="249" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
+        <v>760</v>
+      </c>
+      <c r="B249" t="s">
         <v>761</v>
       </c>
-      <c r="B249" t="s">
-        <v>762</v>
-      </c>
-      <c r="C249" t="s">
-        <v>763</v>
+      <c r="C249">
+        <v>0</v>
       </c>
       <c r="D249" s="1"/>
     </row>
     <row r="250" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B250" t="s">
         <v>764</v>
       </c>
-      <c r="B250" t="s">
-        <v>765</v>
-      </c>
-      <c r="C250">
-        <v>0</v>
+      <c r="C250" t="s">
+        <v>763</v>
       </c>
       <c r="D250" s="1"/>
     </row>
     <row r="251" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="B251" t="s">
         <v>766</v>
-      </c>
-      <c r="B251" t="s">
-        <v>768</v>
       </c>
       <c r="C251" t="s">
         <v>767</v>
@@ -9549,61 +9629,61 @@
     </row>
     <row r="252" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
+        <v>768</v>
+      </c>
+      <c r="B252" t="s">
         <v>769</v>
       </c>
-      <c r="B252" t="s">
-        <v>770</v>
-      </c>
-      <c r="C252" t="s">
-        <v>771</v>
+      <c r="C252">
+        <v>0</v>
       </c>
       <c r="D252" s="1"/>
     </row>
     <row r="253" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B253" t="s">
-        <v>773</v>
-      </c>
-      <c r="C253">
-        <v>0</v>
+        <v>771</v>
+      </c>
+      <c r="C253" t="s">
+        <v>377</v>
       </c>
       <c r="D253" s="1"/>
     </row>
     <row r="254" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B254" t="s">
-        <v>775</v>
-      </c>
-      <c r="C254" t="s">
-        <v>381</v>
+        <v>773</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
       </c>
       <c r="D254" s="1"/>
     </row>
     <row r="255" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="8" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B255" t="s">
+        <v>775</v>
+      </c>
+      <c r="C255" t="s">
         <v>777</v>
-      </c>
-      <c r="C255">
-        <v>0</v>
       </c>
       <c r="D255" s="1"/>
     </row>
     <row r="256" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
+        <v>776</v>
+      </c>
+      <c r="B256" t="s">
         <v>778</v>
       </c>
-      <c r="B256" t="s">
+      <c r="C256" t="s">
         <v>779</v>
-      </c>
-      <c r="C256" t="s">
-        <v>781</v>
       </c>
       <c r="D256" s="1"/>
     </row>
@@ -9612,19 +9692,19 @@
         <v>780</v>
       </c>
       <c r="B257" t="s">
-        <v>782</v>
-      </c>
-      <c r="C257" t="s">
-        <v>783</v>
+        <v>781</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
       </c>
       <c r="D257" s="1"/>
     </row>
     <row r="258" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B258" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -9633,58 +9713,58 @@
     </row>
     <row r="259" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="B259" t="s">
+        <v>785</v>
+      </c>
+      <c r="C259" t="s">
         <v>786</v>
-      </c>
-      <c r="B259" t="s">
-        <v>787</v>
-      </c>
-      <c r="C259">
-        <v>0</v>
       </c>
       <c r="D259" s="1"/>
     </row>
     <row r="260" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="B260" t="s">
         <v>788</v>
       </c>
-      <c r="B260" t="s">
-        <v>789</v>
-      </c>
-      <c r="C260" t="s">
-        <v>790</v>
+      <c r="C260">
+        <v>0</v>
       </c>
       <c r="D260" s="1"/>
     </row>
     <row r="261" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="B261" t="s">
+        <v>790</v>
+      </c>
+      <c r="C261" t="s">
         <v>791</v>
-      </c>
-      <c r="B261" t="s">
-        <v>792</v>
-      </c>
-      <c r="C261">
-        <v>0</v>
       </c>
       <c r="D261" s="1"/>
     </row>
     <row r="262" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B262" t="s">
         <v>793</v>
       </c>
-      <c r="B262" t="s">
-        <v>794</v>
-      </c>
-      <c r="C262" t="s">
-        <v>795</v>
+      <c r="C262">
+        <v>0</v>
       </c>
       <c r="D262" s="1"/>
     </row>
     <row r="263" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
-        <v>796</v>
-      </c>
-      <c r="B263" t="s">
-        <v>797</v>
+        <v>794</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>866</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -9693,10 +9773,10 @@
     </row>
     <row r="264" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
-        <v>798</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>872</v>
+        <v>795</v>
+      </c>
+      <c r="B264" t="s">
+        <v>796</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -9705,10 +9785,10 @@
     </row>
     <row r="265" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="8" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B265" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -9717,178 +9797,178 @@
     </row>
     <row r="266" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B266" t="s">
-        <v>802</v>
-      </c>
-      <c r="C266">
-        <v>0</v>
+        <v>524</v>
+      </c>
+      <c r="C266" t="s">
+        <v>523</v>
       </c>
       <c r="D266" s="1"/>
     </row>
     <row r="267" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="8" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B267" t="s">
-        <v>528</v>
+        <v>801</v>
       </c>
       <c r="C267" t="s">
-        <v>527</v>
+        <v>802</v>
       </c>
       <c r="D267" s="1"/>
     </row>
     <row r="268" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="B268" t="s">
         <v>804</v>
       </c>
-      <c r="B268" t="s">
-        <v>805</v>
-      </c>
-      <c r="C268" t="s">
-        <v>806</v>
+      <c r="C268">
+        <v>0</v>
       </c>
       <c r="D268" s="1"/>
     </row>
     <row r="269" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="B269" t="s">
+        <v>806</v>
+      </c>
+      <c r="C269" t="s">
         <v>807</v>
-      </c>
-      <c r="B269" t="s">
-        <v>808</v>
-      </c>
-      <c r="C269">
-        <v>0</v>
       </c>
       <c r="D269" s="1"/>
     </row>
     <row r="270" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="B270" t="s">
         <v>809</v>
       </c>
-      <c r="B270" t="s">
-        <v>810</v>
-      </c>
-      <c r="C270" t="s">
-        <v>811</v>
+      <c r="C270">
+        <v>0</v>
       </c>
       <c r="D270" s="1"/>
     </row>
     <row r="271" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="B271" t="s">
+        <v>811</v>
+      </c>
+      <c r="C271" t="s">
         <v>812</v>
-      </c>
-      <c r="B271" t="s">
-        <v>813</v>
-      </c>
-      <c r="C271">
-        <v>0</v>
       </c>
       <c r="D271" s="1"/>
     </row>
     <row r="272" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="B272" t="s">
-        <v>815</v>
-      </c>
-      <c r="C272" t="s">
-        <v>816</v>
+        <v>813</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
       </c>
       <c r="D272" s="1"/>
     </row>
     <row r="273" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B273" t="s">
-        <v>818</v>
-      </c>
-      <c r="C273">
-        <v>0</v>
+        <v>816</v>
+      </c>
+      <c r="C273" t="s">
+        <v>815</v>
       </c>
       <c r="D273" s="1"/>
     </row>
     <row r="274" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B274" t="s">
+        <v>818</v>
+      </c>
+      <c r="C274" t="s">
         <v>819</v>
-      </c>
-      <c r="B274" t="s">
-        <v>821</v>
-      </c>
-      <c r="C274" t="s">
-        <v>820</v>
       </c>
       <c r="D274" s="1"/>
     </row>
     <row r="275" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B275" t="s">
         <v>822</v>
       </c>
-      <c r="B275" t="s">
-        <v>823</v>
-      </c>
       <c r="C275" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D275" s="1"/>
     </row>
     <row r="276" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B276" t="s">
         <v>825</v>
       </c>
-      <c r="B276" t="s">
-        <v>827</v>
-      </c>
       <c r="C276" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D276" s="1"/>
     </row>
     <row r="277" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="B277" t="s">
+        <v>827</v>
+      </c>
+      <c r="C277" t="s">
         <v>828</v>
-      </c>
-      <c r="B277" t="s">
-        <v>830</v>
-      </c>
-      <c r="C277" t="s">
-        <v>829</v>
       </c>
       <c r="D277" s="1"/>
     </row>
     <row r="278" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B278" t="s">
+        <v>830</v>
+      </c>
+      <c r="C278" t="s">
         <v>831</v>
-      </c>
-      <c r="B278" t="s">
-        <v>832</v>
-      </c>
-      <c r="C278" t="s">
-        <v>833</v>
       </c>
       <c r="D278" s="1"/>
     </row>
     <row r="279" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B279" t="s">
-        <v>835</v>
-      </c>
-      <c r="C279" t="s">
-        <v>836</v>
+        <v>833</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
       </c>
       <c r="D279" s="1"/>
     </row>
     <row r="280" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B280" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -9897,34 +9977,34 @@
     </row>
     <row r="281" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B281" t="s">
-        <v>840</v>
-      </c>
-      <c r="C281">
-        <v>0</v>
+        <v>838</v>
+      </c>
+      <c r="C281" t="s">
+        <v>837</v>
       </c>
       <c r="D281" s="1"/>
     </row>
     <row r="282" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B282" t="s">
-        <v>843</v>
-      </c>
-      <c r="C282" t="s">
-        <v>842</v>
+        <v>840</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
       </c>
       <c r="D282" s="1"/>
     </row>
     <row r="283" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="8" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B283" t="s">
-        <v>845</v>
+        <v>731</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -9933,46 +10013,46 @@
     </row>
     <row r="284" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B284" t="s">
-        <v>735</v>
-      </c>
-      <c r="C284">
-        <v>0</v>
+        <v>843</v>
+      </c>
+      <c r="C284" t="s">
+        <v>844</v>
       </c>
       <c r="D284" s="1"/>
     </row>
     <row r="285" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B285" t="s">
+        <v>846</v>
+      </c>
+      <c r="C285" t="s">
         <v>847</v>
-      </c>
-      <c r="B285" t="s">
-        <v>848</v>
-      </c>
-      <c r="C285" t="s">
-        <v>849</v>
       </c>
       <c r="D285" s="1"/>
     </row>
     <row r="286" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B286" t="s">
-        <v>851</v>
-      </c>
-      <c r="C286" t="s">
-        <v>852</v>
+        <v>849</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
       </c>
       <c r="D286" s="1"/>
     </row>
     <row r="287" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B287" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -9981,214 +10061,214 @@
     </row>
     <row r="288" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="B288" t="s">
-        <v>856</v>
-      </c>
-      <c r="C288">
-        <v>0</v>
+        <v>852</v>
+      </c>
+      <c r="B288" s="9" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C288" s="9" t="s">
+        <v>1590</v>
       </c>
       <c r="D288" s="1"/>
     </row>
     <row r="289" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="8" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B289" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C289" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D289" s="1"/>
     </row>
     <row r="290" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="B290" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="C290" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D290" s="1"/>
     </row>
     <row r="291" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B291" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C291" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D291" s="1"/>
     </row>
     <row r="292" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="B292" t="s">
-        <v>867</v>
-      </c>
-      <c r="C292" t="s">
-        <v>868</v>
+        <v>864</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
       </c>
       <c r="D292" s="1"/>
     </row>
     <row r="293" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="8" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B293" t="s">
-        <v>870</v>
-      </c>
-      <c r="C293">
-        <v>0</v>
+        <v>867</v>
+      </c>
+      <c r="C293" t="s">
+        <v>868</v>
       </c>
       <c r="D293" s="1"/>
     </row>
     <row r="294" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B294" t="s">
+        <v>870</v>
+      </c>
+      <c r="C294" t="s">
         <v>871</v>
-      </c>
-      <c r="B294" t="s">
-        <v>873</v>
-      </c>
-      <c r="C294" t="s">
-        <v>874</v>
       </c>
       <c r="D294" s="1"/>
     </row>
     <row r="295" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="8" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="B295" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C295" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D295" s="1"/>
     </row>
     <row r="296" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="B296" t="s">
-        <v>879</v>
+        <v>875</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D296" s="1"/>
     </row>
     <row r="297" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="8" t="s">
-        <v>881</v>
-      </c>
-      <c r="B297">
-        <v>0</v>
+        <v>877</v>
+      </c>
+      <c r="B297" t="s">
+        <v>879</v>
       </c>
       <c r="C297" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="D297" s="1"/>
     </row>
     <row r="298" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B298" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C298" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D298" s="1"/>
     </row>
     <row r="299" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B299" t="s">
-        <v>887</v>
-      </c>
-      <c r="C299" t="s">
-        <v>888</v>
+        <v>884</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
       </c>
       <c r="D299" s="1"/>
     </row>
     <row r="300" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B300" t="s">
-        <v>890</v>
-      </c>
-      <c r="C300">
-        <v>0</v>
+        <v>886</v>
+      </c>
+      <c r="C300" t="s">
+        <v>887</v>
       </c>
       <c r="D300" s="1"/>
     </row>
     <row r="301" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="8" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B301" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C301" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D301" s="1"/>
     </row>
     <row r="302" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B302" t="s">
-        <v>895</v>
-      </c>
-      <c r="C302" t="s">
-        <v>896</v>
+        <v>892</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
       </c>
       <c r="D302" s="1"/>
     </row>
     <row r="303" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="8" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B303" t="s">
-        <v>898</v>
-      </c>
-      <c r="C303">
-        <v>0</v>
+        <v>895</v>
+      </c>
+      <c r="C303" t="s">
+        <v>894</v>
       </c>
       <c r="D303" s="1"/>
     </row>
     <row r="304" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="B304" t="s">
-        <v>901</v>
-      </c>
-      <c r="C304" t="s">
-        <v>900</v>
+        <v>897</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
       </c>
       <c r="D304" s="1"/>
     </row>
     <row r="305" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B305" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -10197,34 +10277,34 @@
     </row>
     <row r="306" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B306" t="s">
-        <v>905</v>
-      </c>
-      <c r="C306">
-        <v>0</v>
+        <v>903</v>
+      </c>
+      <c r="C306" t="s">
+        <v>901</v>
       </c>
       <c r="D306" s="1"/>
     </row>
     <row r="307" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="8" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B307" t="s">
-        <v>909</v>
-      </c>
-      <c r="C307" t="s">
-        <v>907</v>
+        <v>904</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
       </c>
       <c r="D307" s="1"/>
     </row>
     <row r="308" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="8" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B308" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -10233,10 +10313,10 @@
     </row>
     <row r="309" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="8" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B309" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -10245,10 +10325,10 @@
     </row>
     <row r="310" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B310" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -10257,10 +10337,10 @@
     </row>
     <row r="311" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="8" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B311" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -10269,10 +10349,10 @@
     </row>
     <row r="312" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="8" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B312" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -10281,10 +10361,10 @@
     </row>
     <row r="313" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="8" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B313" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -10293,10 +10373,10 @@
     </row>
     <row r="314" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B314" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -10305,10 +10385,10 @@
     </row>
     <row r="315" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B315" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -10317,10 +10397,10 @@
     </row>
     <row r="316" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B316" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -10329,10 +10409,10 @@
     </row>
     <row r="317" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="8" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B317" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -10341,10 +10421,10 @@
     </row>
     <row r="318" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B318" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -10353,10 +10433,10 @@
     </row>
     <row r="319" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="8" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B319" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -10365,10 +10445,10 @@
     </row>
     <row r="320" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="8" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B320" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -10377,10 +10457,10 @@
     </row>
     <row r="321" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="8" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B321" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -10389,10 +10469,10 @@
     </row>
     <row r="322" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B322" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -10401,10 +10481,10 @@
     </row>
     <row r="323" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B323" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -10413,10 +10493,10 @@
     </row>
     <row r="324" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B324" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -10425,10 +10505,10 @@
     </row>
     <row r="325" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B325" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -10437,10 +10517,10 @@
     </row>
     <row r="326" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B326" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -10449,10 +10529,10 @@
     </row>
     <row r="327" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="8" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B327" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -10461,154 +10541,154 @@
     </row>
     <row r="328" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="8" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B328" t="s">
-        <v>950</v>
-      </c>
-      <c r="C328">
-        <v>0</v>
+        <v>947</v>
+      </c>
+      <c r="C328" t="s">
+        <v>946</v>
       </c>
       <c r="D328" s="1"/>
     </row>
     <row r="329" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="8" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B329" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C329" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D329" s="1"/>
     </row>
     <row r="330" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="8" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B330" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C330" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D330" s="1"/>
     </row>
     <row r="331" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="8" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B331" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C331" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="D331" s="1"/>
     </row>
     <row r="332" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B332" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C332" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="D332" s="1"/>
     </row>
     <row r="333" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="8" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B333" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="C333" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="D333" s="1"/>
     </row>
     <row r="334" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="8" t="s">
-        <v>966</v>
-      </c>
-      <c r="B334" t="s">
-        <v>968</v>
+        <v>963</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D334" s="1"/>
     </row>
     <row r="335" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="8" t="s">
-        <v>969</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
+        <v>965</v>
+      </c>
+      <c r="B335" t="s">
+        <v>967</v>
       </c>
       <c r="C335" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="D335" s="1"/>
     </row>
     <row r="336" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="8" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B336" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C336" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="D336" s="1"/>
     </row>
     <row r="337" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="8" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B337" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C337" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="D337" s="1"/>
     </row>
     <row r="338" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="8" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B338" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="C338" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="D338" s="1"/>
     </row>
     <row r="339" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="8" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B339" t="s">
-        <v>982</v>
-      </c>
-      <c r="C339" t="s">
-        <v>981</v>
+        <v>978</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
       </c>
       <c r="D339" s="1"/>
     </row>
     <row r="340" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="8" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B340" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -10617,142 +10697,142 @@
     </row>
     <row r="341" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="8" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B341" t="s">
-        <v>986</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
+        <v>982</v>
+      </c>
+      <c r="C341" t="s">
+        <v>983</v>
       </c>
       <c r="D341" s="1"/>
     </row>
     <row r="342" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="8" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B342" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C342" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D342" s="1"/>
     </row>
     <row r="343" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="8" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B343" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C343" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D343" s="1"/>
     </row>
     <row r="344" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="8" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B344" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C344" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="D344" s="1"/>
     </row>
     <row r="345" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="8" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B345" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C345" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D345" s="1"/>
     </row>
     <row r="346" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="8" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B346" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C346" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="D346" s="1"/>
     </row>
     <row r="347" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="8" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B347" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="C347" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="D347" s="1"/>
     </row>
     <row r="348" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="8" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B348" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C348" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="D348" s="1"/>
     </row>
     <row r="349" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="8" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B349" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C349" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="D349" s="1"/>
     </row>
     <row r="350" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="8" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="B350" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C350" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="D350" s="1"/>
     </row>
     <row r="351" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="8" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="B351" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1015</v>
+        <v>1012</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
       </c>
       <c r="D351" s="1"/>
     </row>
     <row r="352" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="8" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="B352" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -10761,10 +10841,10 @@
     </row>
     <row r="353" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="8" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B353" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -10773,10 +10853,10 @@
     </row>
     <row r="354" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="8" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B354" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -10785,34 +10865,34 @@
     </row>
     <row r="355" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="8" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B355" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
+        <v>1021</v>
+      </c>
+      <c r="C355" t="s">
+        <v>1022</v>
       </c>
       <c r="D355" s="1"/>
     </row>
     <row r="356" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="8" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B356" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C356" t="s">
-        <v>1028</v>
+        <v>1024</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
       </c>
       <c r="D356" s="1"/>
     </row>
     <row r="357" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="8" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B357" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -10821,10 +10901,10 @@
     </row>
     <row r="358" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="8" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B358" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -10833,46 +10913,46 @@
     </row>
     <row r="359" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="8" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B359" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
+        <v>1031</v>
+      </c>
+      <c r="C359" t="s">
+        <v>1030</v>
       </c>
       <c r="D359" s="1"/>
     </row>
     <row r="360" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="8" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B360" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C360" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="D360" s="1"/>
     </row>
     <row r="361" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B361" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C361" t="s">
-        <v>1039</v>
+        <v>1035</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
       </c>
       <c r="D361" s="1"/>
     </row>
     <row r="362" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="8" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B362">
-        <v>0</v>
+        <v>1036</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1037</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -10881,178 +10961,178 @@
     </row>
     <row r="363" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="8" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B363" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
+        <v>1039</v>
+      </c>
+      <c r="C363" t="s">
+        <v>1040</v>
       </c>
       <c r="D363" s="1"/>
     </row>
     <row r="364" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="8" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="B364" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C364" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="D364" s="1"/>
     </row>
     <row r="365" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="8" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B365" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C365" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="D365" s="1"/>
     </row>
     <row r="366" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="8" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B366" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C366" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D366" s="1"/>
     </row>
     <row r="367" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="8" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B367" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C367" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="D367" s="1"/>
     </row>
     <row r="368" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="B368" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C368" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="D368" s="1"/>
     </row>
     <row r="369" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="8" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B369" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C369" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="D369" s="1"/>
     </row>
     <row r="370" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B370" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C370" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D370" s="1"/>
     </row>
     <row r="371" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="8" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B371" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C371" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="D371" s="1"/>
     </row>
     <row r="372" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="8" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B372" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C372" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="D372" s="1"/>
     </row>
     <row r="373" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="8" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B373" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C373" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D373" s="1"/>
     </row>
     <row r="374" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="8" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B374" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C374" t="s">
-        <v>1076</v>
+        <v>1072</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
       </c>
       <c r="D374" s="1"/>
     </row>
     <row r="375" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="8" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B375" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
+        <v>1074</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1075</v>
       </c>
       <c r="D375" s="1"/>
     </row>
     <row r="376" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="8" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B376" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C376" t="s">
-        <v>1081</v>
+        <v>1077</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
       </c>
       <c r="D376" s="1"/>
     </row>
     <row r="377" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="8" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B377" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -11061,250 +11141,250 @@
     </row>
     <row r="378" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="8" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="B378" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
+        <v>1081</v>
+      </c>
+      <c r="C378" t="s">
+        <v>1082</v>
       </c>
       <c r="D378" s="1"/>
     </row>
     <row r="379" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="8" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="B379" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1088</v>
+        <v>1084</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
       </c>
       <c r="D379" s="1"/>
     </row>
     <row r="380" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="8" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B380" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
+        <v>1085</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380" t="s">
+        <v>1086</v>
       </c>
       <c r="D380" s="1"/>
     </row>
     <row r="381" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="8" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1092</v>
+        <v>1087</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
       </c>
       <c r="D381" s="1"/>
     </row>
     <row r="382" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="8" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="B382" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
+        <v>1091</v>
+      </c>
+      <c r="C382" t="s">
+        <v>1092</v>
       </c>
       <c r="D382" s="1"/>
     </row>
     <row r="383" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="8" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B383" t="s">
-        <v>1097</v>
+        <v>1090</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
       </c>
       <c r="C383" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="D383" s="1"/>
     </row>
     <row r="384" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="8" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B384">
         <v>0</v>
       </c>
       <c r="C384" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="D384" s="1"/>
     </row>
     <row r="385" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="8" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="B385">
         <v>0</v>
       </c>
-      <c r="C385" t="s">
-        <v>1101</v>
+      <c r="C385">
+        <v>0</v>
       </c>
       <c r="D385" s="1"/>
     </row>
     <row r="386" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="8" t="s">
-        <v>1102</v>
-      </c>
-      <c r="B386">
-        <v>0</v>
-      </c>
-      <c r="C386">
-        <v>0</v>
+        <v>1097</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C386" t="s">
+        <v>1099</v>
       </c>
       <c r="D386" s="1"/>
     </row>
     <row r="387" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="8" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="B387" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C387" t="s">
-        <v>1105</v>
+        <v>1101</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
       </c>
       <c r="D387" s="1"/>
     </row>
     <row r="388" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="8" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B388" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C388">
-        <v>0</v>
+        <v>1102</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388" t="s">
+        <v>1103</v>
       </c>
       <c r="D388" s="1"/>
     </row>
     <row r="389" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="8" t="s">
-        <v>1108</v>
-      </c>
-      <c r="B389">
-        <v>0</v>
+        <v>1104</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1105</v>
       </c>
       <c r="C389" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="D389" s="1"/>
     </row>
     <row r="390" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="8" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B390" t="s">
-        <v>1111</v>
+        <v>1107</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
       </c>
       <c r="C390" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="D390" s="1"/>
     </row>
     <row r="391" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="8" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B391">
-        <v>0</v>
+        <v>1109</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1110</v>
       </c>
       <c r="C391" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D391" s="1"/>
     </row>
     <row r="392" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="8" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B392" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C392" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="D392" s="1"/>
     </row>
     <row r="393" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="8" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B393" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C393" t="s">
-        <v>1120</v>
+        <v>1116</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
       </c>
       <c r="D393" s="1"/>
     </row>
     <row r="394" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="8" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="B394" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C394">
-        <v>0</v>
+        <v>1118</v>
+      </c>
+      <c r="C394" t="s">
+        <v>1119</v>
       </c>
       <c r="D394" s="1"/>
     </row>
     <row r="395" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="8" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="B395" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C395" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D395" s="1"/>
     </row>
     <row r="396" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="8" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B396" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C396" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D396" s="1"/>
     </row>
     <row r="397" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="8" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="B397" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C397" t="s">
-        <v>1130</v>
+        <v>1127</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
       </c>
       <c r="D397" s="1"/>
     </row>
     <row r="398" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="8" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="B398" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -11313,238 +11393,238 @@
     </row>
     <row r="399" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="8" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B399" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C399">
-        <v>0</v>
+        <v>1132</v>
+      </c>
+      <c r="C399" t="s">
+        <v>1131</v>
       </c>
       <c r="D399" s="1"/>
     </row>
     <row r="400" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="8" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="B400" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="C400" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="D400" s="1"/>
     </row>
     <row r="401" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="8" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B401" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C401" t="s">
-        <v>1141</v>
+        <v>1137</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
       </c>
       <c r="D401" s="1"/>
     </row>
     <row r="402" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="8" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="B402" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C402">
-        <v>0</v>
+        <v>1139</v>
+      </c>
+      <c r="C402" t="s">
+        <v>1140</v>
       </c>
       <c r="D402" s="1"/>
     </row>
     <row r="403" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="8" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="B403" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="C403" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D403" s="1"/>
     </row>
     <row r="404" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="8" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B404" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C404" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="D404" s="1"/>
     </row>
     <row r="405" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="8" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B405" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C405" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="D405" s="1"/>
     </row>
     <row r="406" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="8" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B406" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C406" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="D406" s="1"/>
     </row>
     <row r="407" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="8" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B407" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="C407" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="D407" s="1"/>
     </row>
     <row r="408" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="8" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B408" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C408" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="D408" s="1"/>
     </row>
     <row r="409" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="8" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B409" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="C409" t="s">
-        <v>1164</v>
+        <v>377</v>
       </c>
       <c r="D409" s="1"/>
     </row>
     <row r="410" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="8" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="B410" t="s">
-        <v>1166</v>
+        <v>1533</v>
       </c>
       <c r="C410" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D410" s="1"/>
     </row>
     <row r="411" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="8" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="B411" t="s">
-        <v>1541</v>
+        <v>1164</v>
       </c>
       <c r="C411" t="s">
-        <v>381</v>
+        <v>1163</v>
       </c>
       <c r="D411" s="1"/>
     </row>
     <row r="412" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="8" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="B412" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C412" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="D412" s="1"/>
     </row>
     <row r="413" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="8" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="B413" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="C413" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="D413" s="1"/>
     </row>
     <row r="414" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="8" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B414" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="C414" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="D414" s="1"/>
     </row>
     <row r="415" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="8" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B415" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C415" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="D415" s="1"/>
     </row>
     <row r="416" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="8" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="B416" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="C416" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D416" s="1"/>
     </row>
     <row r="417" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="8" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="B417" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C417" t="s">
-        <v>1185</v>
+        <v>1181</v>
+      </c>
+      <c r="C417">
+        <v>0</v>
       </c>
       <c r="D417" s="1"/>
     </row>
     <row r="418" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="8" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="B418" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -11553,10 +11633,10 @@
     </row>
     <row r="419" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="8" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="B419" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -11565,94 +11645,94 @@
     </row>
     <row r="420" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="8" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="B420" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C420">
-        <v>0</v>
+        <v>1110</v>
+      </c>
+      <c r="C420" t="s">
+        <v>1187</v>
       </c>
       <c r="D420" s="1"/>
     </row>
     <row r="421" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="8" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="B421" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="C421" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D421" s="1"/>
     </row>
     <row r="422" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="8" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B422" t="s">
-        <v>1116</v>
+        <v>1191</v>
       </c>
       <c r="C422" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D422" s="1"/>
     </row>
     <row r="423" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="8" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="B423" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C423" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D423" s="1"/>
     </row>
     <row r="424" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="8" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="B424" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="C424" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D424" s="1"/>
     </row>
     <row r="425" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="8" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="B425" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="C425" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="D425" s="1"/>
     </row>
     <row r="426" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="8" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B426" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C426" t="s">
-        <v>1207</v>
+        <v>1203</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
       </c>
       <c r="D426" s="1"/>
     </row>
     <row r="427" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="8" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="B427" t="s">
-        <v>1209</v>
+        <v>1116</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -11661,94 +11741,94 @@
     </row>
     <row r="428" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="8" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B428" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C428">
-        <v>0</v>
+        <v>1205</v>
+      </c>
+      <c r="B428" s="9" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C428" s="9" t="s">
+        <v>1585</v>
       </c>
       <c r="D428" s="1"/>
     </row>
     <row r="429" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="8" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="B429" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="C429" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="D429" s="1"/>
     </row>
     <row r="430" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="8" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="B430" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="C430" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="D430" s="1"/>
     </row>
     <row r="431" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="8" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="B431" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="C431" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="D431" s="1"/>
     </row>
     <row r="432" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="8" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B432" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="C432" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="D432" s="1"/>
     </row>
     <row r="433" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="B433" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="C433" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="D433" s="1"/>
     </row>
     <row r="434" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="B434" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C434" t="s">
-        <v>1228</v>
+        <v>1222</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
       </c>
       <c r="D434" s="1"/>
     </row>
     <row r="435" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="8" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B435" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -11757,10 +11837,10 @@
     </row>
     <row r="436" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="8" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="B436" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -11769,142 +11849,142 @@
     </row>
     <row r="437" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="8" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="B437" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C437">
-        <v>0</v>
+        <v>1228</v>
+      </c>
+      <c r="C437" t="s">
+        <v>1229</v>
       </c>
       <c r="D437" s="1"/>
     </row>
     <row r="438" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="8" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="B438" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C438" t="s">
-        <v>1237</v>
+        <v>1231</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
       </c>
       <c r="D438" s="1"/>
     </row>
     <row r="439" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="8" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="B439" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C439">
-        <v>0</v>
+        <v>1233</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>1234</v>
       </c>
       <c r="D439" s="1"/>
     </row>
     <row r="440" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="8" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="B440" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>1242</v>
+        <v>1236</v>
+      </c>
+      <c r="C440" t="s">
+        <v>1237</v>
       </c>
       <c r="D440" s="1"/>
     </row>
     <row r="441" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="8" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="B441" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C441" t="s">
-        <v>1245</v>
+        <v>1239</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
       </c>
       <c r="D441" s="1"/>
     </row>
     <row r="442" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="8" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="B442" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C442">
-        <v>0</v>
+        <v>1241</v>
+      </c>
+      <c r="C442" t="s">
+        <v>1242</v>
       </c>
       <c r="D442" s="1"/>
     </row>
     <row r="443" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="8" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B443" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="C443" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="D443" s="1"/>
     </row>
     <row r="444" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="B444" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="C444" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="D444" s="1"/>
     </row>
     <row r="445" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="8" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="B445" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="C445" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="D445" s="1"/>
     </row>
     <row r="446" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="8" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="B446" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C446" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
       <c r="D446" s="1"/>
     </row>
     <row r="447" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="8" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="B447" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C447" t="s">
-        <v>1261</v>
+        <v>1256</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
       </c>
       <c r="D447" s="1"/>
     </row>
     <row r="448" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="8" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B448" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -11913,10 +11993,10 @@
     </row>
     <row r="449" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="8" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
       <c r="B449" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -11925,322 +12005,322 @@
     </row>
     <row r="450" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="8" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="B450" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C450">
-        <v>0</v>
+        <v>1526</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1262</v>
       </c>
       <c r="D450" s="1"/>
     </row>
     <row r="451" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="8" t="s">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="B451" t="s">
-        <v>1534</v>
+        <v>1265</v>
       </c>
       <c r="C451" t="s">
-        <v>1270</v>
+        <v>1264</v>
       </c>
       <c r="D451" s="1"/>
     </row>
     <row r="452" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="8" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="B452" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="C452" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D452" s="1"/>
     </row>
     <row r="453" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="8" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="B453" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="C453" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="D453" s="1"/>
     </row>
     <row r="454" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="8" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="B454" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="C454" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="D454" s="1"/>
     </row>
     <row r="455" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="8" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="B455" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="C455" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D455" s="1"/>
     </row>
     <row r="456" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="8" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="B456" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="C456" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="D456" s="1"/>
     </row>
     <row r="457" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="8" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="B457" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="C457" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="D457" s="1"/>
     </row>
     <row r="458" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="8" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="B458" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="C458" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="D458" s="1"/>
     </row>
     <row r="459" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="8" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="B459" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="C459" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="D459" s="1"/>
     </row>
     <row r="460" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="8" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="B460" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="C460" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="D460" s="1"/>
     </row>
     <row r="461" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="8" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="B461" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C461" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
       <c r="D461" s="1"/>
     </row>
     <row r="462" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="8" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="B462" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="C462" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="D462" s="1"/>
     </row>
     <row r="463" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="8" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="B463" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C463" t="s">
-        <v>1306</v>
+        <v>1300</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
       </c>
       <c r="D463" s="1"/>
     </row>
     <row r="464" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="8" t="s">
-        <v>1307</v>
+        <v>1301</v>
       </c>
       <c r="B464" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C464">
-        <v>0</v>
+        <v>1302</v>
+      </c>
+      <c r="C464" t="s">
+        <v>377</v>
       </c>
       <c r="D464" s="1"/>
     </row>
     <row r="465" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="8" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="B465" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C465" t="s">
-        <v>381</v>
+        <v>1304</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
       </c>
       <c r="D465" s="1"/>
     </row>
     <row r="466" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="8" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
       <c r="B466" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C466">
-        <v>0</v>
+        <v>1306</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1307</v>
       </c>
       <c r="D466" s="1"/>
     </row>
     <row r="467" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="8" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="B467" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="C467" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="D467" s="1"/>
     </row>
     <row r="468" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="8" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="B468" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="C468" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="D468" s="1"/>
     </row>
     <row r="469" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="8" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="B469" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="C469" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="D469" s="1"/>
     </row>
     <row r="470" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="8" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="B470" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="C470" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="D470" s="1"/>
     </row>
     <row r="471" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="8" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="B471" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="C471" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="D471" s="1"/>
     </row>
     <row r="472" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="8" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="B472" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="C472" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="D472" s="1"/>
     </row>
     <row r="473" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="8" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="B473" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="C473" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="D473" s="1"/>
     </row>
     <row r="474" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="8" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="B474" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="C474" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="D474" s="1"/>
     </row>
     <row r="475" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="8" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="B475" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C475" t="s">
-        <v>1339</v>
+        <v>1332</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
       </c>
       <c r="D475" s="1"/>
     </row>
     <row r="476" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="8" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="B476" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="C476">
         <v>0</v>
@@ -12249,274 +12329,274 @@
     </row>
     <row r="477" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="8" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="B477" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C477">
-        <v>0</v>
+        <v>1337</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1338</v>
       </c>
       <c r="D477" s="1"/>
     </row>
     <row r="478" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="8" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="B478" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C478" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="D478" s="1"/>
     </row>
     <row r="479" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="8" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="B479" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C479" t="s">
-        <v>1348</v>
+        <v>1343</v>
+      </c>
+      <c r="C479" s="7">
+        <v>0</v>
       </c>
       <c r="D479" s="1"/>
     </row>
     <row r="480" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="8" t="s">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="B480" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C480" s="7">
-        <v>0</v>
+        <v>1346</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1345</v>
       </c>
       <c r="D480" s="1"/>
     </row>
     <row r="481" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="8" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="B481" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="C481" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="D481" s="1"/>
     </row>
     <row r="482" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="8" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="B482" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="C482" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="D482" s="1"/>
     </row>
     <row r="483" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="8" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="B483" t="s">
-        <v>1359</v>
+        <v>1528</v>
       </c>
       <c r="C483" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="D483" s="1"/>
     </row>
     <row r="484" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="8" t="s">
-        <v>1361</v>
+        <v>1355</v>
       </c>
       <c r="B484" t="s">
-        <v>1536</v>
+        <v>1356</v>
       </c>
       <c r="C484" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="D484" s="1"/>
     </row>
     <row r="485" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="8" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="B485" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="C485" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="D485" s="1"/>
     </row>
     <row r="486" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="8" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="B486" t="s">
-        <v>1367</v>
+        <v>679</v>
       </c>
       <c r="C486" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="D486" s="1"/>
     </row>
     <row r="487" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="8" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="B487" t="s">
-        <v>683</v>
+        <v>1364</v>
       </c>
       <c r="C487" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="D487" s="1"/>
     </row>
     <row r="488" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="8" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="B488" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="C488" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="D488" s="1"/>
     </row>
     <row r="489" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="8" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="B489" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="C489" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="D489" s="1"/>
     </row>
     <row r="490" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="8" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="B490" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="C490" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="D490" s="1"/>
     </row>
     <row r="491" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="8" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="B491" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C491" t="s">
-        <v>1382</v>
+        <v>1376</v>
+      </c>
+      <c r="C491">
+        <v>0</v>
       </c>
       <c r="D491" s="1"/>
     </row>
     <row r="492" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="8" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="B492" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C492">
-        <v>0</v>
+        <v>1378</v>
+      </c>
+      <c r="C492" t="s">
+        <v>1379</v>
       </c>
       <c r="D492" s="1"/>
     </row>
     <row r="493" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="8" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="B493" t="s">
-        <v>1386</v>
-      </c>
-      <c r="C493" t="s">
-        <v>1387</v>
+        <v>1381</v>
+      </c>
+      <c r="C493">
+        <v>0</v>
       </c>
       <c r="D493" s="1"/>
     </row>
     <row r="494" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="8" t="s">
-        <v>1388</v>
+        <v>1382</v>
       </c>
       <c r="B494" t="s">
-        <v>1389</v>
-      </c>
-      <c r="C494">
-        <v>0</v>
+        <v>1383</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1384</v>
       </c>
       <c r="D494" s="1"/>
     </row>
     <row r="495" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="8" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="B495" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="C495" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="D495" s="1"/>
     </row>
     <row r="496" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="8" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1394</v>
+        <v>1388</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
       </c>
       <c r="C496" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="D496" s="1"/>
     </row>
     <row r="497" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="8" t="s">
-        <v>1396</v>
-      </c>
-      <c r="B497">
-        <v>0</v>
+        <v>1390</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1391</v>
       </c>
       <c r="C497" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="D497" s="1"/>
     </row>
     <row r="498" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="8" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="B498" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C498" t="s">
-        <v>1400</v>
+        <v>1394</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
       </c>
       <c r="D498" s="1"/>
     </row>
     <row r="499" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="8" t="s">
-        <v>1401</v>
+        <v>1395</v>
       </c>
       <c r="B499" t="s">
-        <v>1402</v>
+        <v>1396</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -12525,46 +12605,46 @@
     </row>
     <row r="500" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="8" t="s">
-        <v>1403</v>
+        <v>1397</v>
       </c>
       <c r="B500" t="s">
-        <v>1404</v>
-      </c>
-      <c r="C500">
-        <v>0</v>
+        <v>1399</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1398</v>
       </c>
       <c r="D500" s="1"/>
     </row>
     <row r="501" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="8" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="B501" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="C501" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="D501" s="1"/>
     </row>
     <row r="502" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="8" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="B502" t="s">
-        <v>1410</v>
-      </c>
-      <c r="C502" t="s">
-        <v>1409</v>
+        <v>1404</v>
+      </c>
+      <c r="C502">
+        <v>0</v>
       </c>
       <c r="D502" s="1"/>
     </row>
     <row r="503" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="8" t="s">
-        <v>1411</v>
+        <v>1405</v>
       </c>
       <c r="B503" t="s">
-        <v>1412</v>
+        <v>1406</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -12573,10 +12653,10 @@
     </row>
     <row r="504" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="8" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="B504" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -12585,238 +12665,238 @@
     </row>
     <row r="505" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="8" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
       <c r="B505" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C505">
-        <v>0</v>
+        <v>1410</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1411</v>
       </c>
       <c r="D505" s="1"/>
     </row>
     <row r="506" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="8" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B506" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1419</v>
+        <v>1413</v>
+      </c>
+      <c r="C506">
+        <v>0</v>
       </c>
       <c r="D506" s="1"/>
     </row>
     <row r="507" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="8" t="s">
-        <v>1420</v>
+        <v>1414</v>
       </c>
       <c r="B507" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C507">
-        <v>0</v>
+        <v>1415</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1416</v>
       </c>
       <c r="D507" s="1"/>
     </row>
     <row r="508" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="8" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="B508" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="C508" t="s">
-        <v>1424</v>
+        <v>1418</v>
       </c>
       <c r="D508" s="1"/>
     </row>
     <row r="509" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="8" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="B509" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="C509" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="D509" s="1"/>
     </row>
     <row r="510" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="8" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="B510" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="C510" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="D510" s="1"/>
     </row>
     <row r="511" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="8" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="B511" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="C511" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="D511" s="1"/>
     </row>
     <row r="512" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="8" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="B512" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="C512" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="D512" s="1"/>
     </row>
     <row r="513" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="8" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="B513" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="C513" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="D513" s="1"/>
     </row>
     <row r="514" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="8" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="B514" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="C514" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="D514" s="1"/>
     </row>
     <row r="515" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="8" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="B515" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="C515" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="D515" s="1"/>
     </row>
     <row r="516" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="8" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="B516" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="C516" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="D516" s="1"/>
     </row>
     <row r="517" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="8" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B517" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="C517" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="D517" s="1"/>
     </row>
     <row r="518" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="8" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="B518" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="C518" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="D518" s="1"/>
     </row>
     <row r="519" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="8" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="B519" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="C519" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="D519" s="1"/>
     </row>
     <row r="520" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="8" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B520" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="C520" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="D520" s="1"/>
     </row>
     <row r="521" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="8" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
       <c r="B521" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="C521" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="D521" s="1"/>
     </row>
     <row r="522" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="8" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="B522" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="C522" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="D522" s="1"/>
     </row>
     <row r="523" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="8" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="B523" t="s">
-        <v>1468</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1469</v>
+        <v>1463</v>
+      </c>
+      <c r="C523">
+        <v>0</v>
       </c>
       <c r="D523" s="1"/>
     </row>
     <row r="524" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="8" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="B524" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="C524">
         <v>0</v>
@@ -12825,10 +12905,10 @@
     </row>
     <row r="525" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="8" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="B525" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -12837,46 +12917,46 @@
     </row>
     <row r="526" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="8" t="s">
-        <v>1474</v>
-      </c>
-      <c r="B526" t="s">
-        <v>1475</v>
-      </c>
-      <c r="C526">
-        <v>0</v>
+        <v>1468</v>
+      </c>
+      <c r="B526" s="7">
+        <v>0</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1469</v>
       </c>
       <c r="D526" s="1"/>
     </row>
     <row r="527" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="8" t="s">
-        <v>1476</v>
-      </c>
-      <c r="B527" s="7">
-        <v>0</v>
+        <v>1470</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1472</v>
       </c>
       <c r="C527" t="s">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="D527" s="1"/>
     </row>
-    <row r="528" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="8" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="B528" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1479</v>
+        <v>1474</v>
+      </c>
+      <c r="C528">
+        <v>0</v>
       </c>
       <c r="D528" s="1"/>
     </row>
     <row r="529" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="8" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="B529" t="s">
-        <v>1482</v>
+        <v>1475</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -12885,94 +12965,94 @@
     </row>
     <row r="530" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="8" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
       <c r="B530" t="s">
-        <v>1483</v>
-      </c>
-      <c r="C530">
-        <v>0</v>
+        <v>1478</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1479</v>
       </c>
       <c r="D530" s="1"/>
     </row>
     <row r="531" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="8" t="s">
-        <v>1485</v>
-      </c>
-      <c r="B531" t="s">
-        <v>1486</v>
+        <v>1480</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
       </c>
       <c r="C531" t="s">
-        <v>1487</v>
+        <v>1481</v>
       </c>
       <c r="D531" s="1"/>
     </row>
     <row r="532" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="8" t="s">
-        <v>1488</v>
-      </c>
-      <c r="B532">
-        <v>0</v>
+        <v>1482</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1484</v>
       </c>
       <c r="C532" t="s">
-        <v>1489</v>
+        <v>1483</v>
       </c>
       <c r="D532" s="1"/>
     </row>
     <row r="533" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="8" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="B533" t="s">
-        <v>1492</v>
+        <v>1486</v>
       </c>
       <c r="C533" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="D533" s="1"/>
     </row>
     <row r="534" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="8" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="B534" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="C534" t="s">
-        <v>1495</v>
+        <v>1489</v>
       </c>
       <c r="D534" s="1"/>
     </row>
     <row r="535" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="8" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
       <c r="B535" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="C535" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="D535" s="1"/>
     </row>
     <row r="536" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="8" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="B536" t="s">
-        <v>1501</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1500</v>
+        <v>1495</v>
+      </c>
+      <c r="C536">
+        <v>0</v>
       </c>
       <c r="D536" s="1"/>
     </row>
     <row r="537" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="8" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="B537" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -12981,10 +13061,10 @@
     </row>
     <row r="538" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="8" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
       <c r="B538" t="s">
-        <v>1505</v>
+        <v>1110</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -12993,70 +13073,70 @@
     </row>
     <row r="539" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="8" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
       <c r="B539" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C539">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1501</v>
       </c>
       <c r="D539" s="1"/>
     </row>
     <row r="540" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="8" t="s">
-        <v>1507</v>
-      </c>
-      <c r="B540" t="s">
-        <v>1508</v>
+        <v>1502</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
       </c>
       <c r="C540" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
       <c r="D540" s="1"/>
     </row>
     <row r="541" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="8" t="s">
-        <v>1510</v>
-      </c>
-      <c r="B541">
-        <v>0</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1511</v>
+        <v>1504</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C541">
+        <v>0</v>
       </c>
       <c r="D541" s="1"/>
     </row>
     <row r="542" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="8" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="B542" t="s">
-        <v>1513</v>
-      </c>
-      <c r="C542">
-        <v>0</v>
+        <v>1507</v>
+      </c>
+      <c r="C542" t="s">
+        <v>1508</v>
       </c>
       <c r="D542" s="1"/>
     </row>
     <row r="543" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="8" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="B543" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1516</v>
+        <v>1510</v>
+      </c>
+      <c r="C543">
+        <v>0</v>
       </c>
       <c r="D543" s="1"/>
     </row>
     <row r="544" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="8" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
       <c r="B544" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -13065,34 +13145,34 @@
     </row>
     <row r="545" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="8" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
       <c r="B545" t="s">
-        <v>1520</v>
-      </c>
-      <c r="C545">
-        <v>0</v>
+        <v>1514</v>
+      </c>
+      <c r="C545" t="s">
+        <v>1515</v>
       </c>
       <c r="D545" s="1"/>
     </row>
     <row r="546" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="8" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="B546" t="s">
-        <v>1522</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1523</v>
+        <v>1517</v>
+      </c>
+      <c r="C546">
+        <v>0</v>
       </c>
       <c r="D546" s="1"/>
     </row>
     <row r="547" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="8" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="B547" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="C547">
         <v>0</v>
@@ -13101,10 +13181,10 @@
     </row>
     <row r="548" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="8" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="B548" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="C548">
         <v>0</v>
@@ -13113,10 +13193,10 @@
     </row>
     <row r="549" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="8" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="B549" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="C549">
         <v>0</v>
@@ -13125,10 +13205,10 @@
     </row>
     <row r="550" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="8" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B550" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="C550">
         <v>0</v>
@@ -13137,10 +13217,10 @@
     </row>
     <row r="551" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="8" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="B551" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="C551">
         <v>0</v>
@@ -13149,45 +13229,44 @@
     </row>
     <row r="552" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="8" t="s">
-        <v>1551</v>
+        <v>1570</v>
       </c>
       <c r="B552" t="s">
-        <v>1552</v>
+        <v>1571</v>
       </c>
       <c r="C552">
         <v>0</v>
       </c>
       <c r="D552" s="1"/>
     </row>
-    <row r="553" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A553" s="8" t="s">
-        <v>1578</v>
+    <row r="553" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A553" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="B553" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C553">
-        <v>0</v>
-      </c>
-      <c r="D553" s="1"/>
-    </row>
-    <row r="554" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="C553" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B554" t="s">
-        <v>191</v>
-      </c>
-      <c r="C554" t="s">
-        <v>190</v>
+        <v>8</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C554" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B555" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1013</v>
       </c>
       <c r="C555" s="1">
         <v>0</v>
@@ -13195,157 +13274,157 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="B556" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C556" s="1">
-        <v>0</v>
+        <v>274</v>
+      </c>
+      <c r="C556" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>276</v>
+        <v>182</v>
       </c>
       <c r="B557" t="s">
-        <v>277</v>
+        <v>1561</v>
       </c>
       <c r="C557" t="s">
-        <v>278</v>
+        <v>183</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B558" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C558" t="s">
-        <v>186</v>
+        <v>37</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B559" s="1" t="s">
-        <v>36</v>
+        <v>197</v>
+      </c>
+      <c r="B559" t="s">
+        <v>196</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E559" s="1"/>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
-        <v>200</v>
+        <v>1556</v>
       </c>
       <c r="B560" t="s">
-        <v>199</v>
-      </c>
-      <c r="C560" s="1" t="s">
-        <v>43</v>
+        <v>1558</v>
+      </c>
+      <c r="C560" t="s">
+        <v>1557</v>
       </c>
       <c r="E560" s="1"/>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>1564</v>
+        <v>160</v>
       </c>
       <c r="B561" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="C561" t="s">
-        <v>1565</v>
+        <v>181</v>
       </c>
       <c r="E561" s="1"/>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="B562" t="s">
-        <v>1571</v>
+        <v>194</v>
       </c>
       <c r="C562" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E562" s="1"/>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B563" t="s">
-        <v>197</v>
-      </c>
-      <c r="C563" t="s">
-        <v>198</v>
-      </c>
-      <c r="E563" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B564" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C564" s="1" t="s">
-        <v>46</v>
+        <v>213</v>
+      </c>
+      <c r="B564" t="s">
+        <v>212</v>
+      </c>
+      <c r="C564" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>216</v>
+        <v>434</v>
       </c>
       <c r="B565" t="s">
-        <v>215</v>
-      </c>
-      <c r="C565" t="s">
-        <v>214</v>
+        <v>435</v>
+      </c>
+      <c r="C565">
+        <v>0</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A566" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B566" t="s">
-        <v>439</v>
-      </c>
-      <c r="C566">
+      <c r="A566" t="s">
+        <v>76</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C566" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A567" t="s">
-        <v>76</v>
-      </c>
-      <c r="B567" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C567" s="1">
-        <v>0</v>
+      <c r="A567" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B567" t="s">
+        <v>224</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="B568" t="s">
-        <v>227</v>
-      </c>
-      <c r="C568" s="1" t="s">
-        <v>31</v>
+        <v>1531</v>
+      </c>
+      <c r="C568">
+        <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B569" t="s">
-        <v>1539</v>
+        <v>164</v>
       </c>
       <c r="C569">
         <v>0</v>
@@ -13353,219 +13432,220 @@
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B570" t="s">
-        <v>167</v>
-      </c>
-      <c r="C570">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="C570" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B571" t="s">
-        <v>110</v>
-      </c>
-      <c r="C571">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C571" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B572" t="s">
-        <v>115</v>
+        <v>266</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
       </c>
       <c r="C572" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="573" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B573" s="1" t="s">
-        <v>1545</v>
+        <v>445</v>
+      </c>
+      <c r="B573" t="s">
+        <v>446</v>
       </c>
       <c r="C573" t="s">
-        <v>138</v>
+        <v>447</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B574">
-        <v>0</v>
+        <v>1575</v>
+      </c>
+      <c r="B574" t="s">
+        <v>175</v>
       </c>
       <c r="C574" t="s">
-        <v>270</v>
+        <v>145</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
-        <v>449</v>
+        <v>147</v>
       </c>
       <c r="B575" t="s">
-        <v>450</v>
-      </c>
-      <c r="C575" t="s">
-        <v>451</v>
+        <v>1523</v>
+      </c>
+      <c r="C575">
+        <v>0</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B576" t="s">
-        <v>178</v>
-      </c>
-      <c r="C576" t="s">
-        <v>146</v>
+        <v>149</v>
+      </c>
+      <c r="C576">
+        <v>0</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>149</v>
+        <v>1576</v>
       </c>
       <c r="B577" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C577">
-        <v>0</v>
+        <v>151</v>
+      </c>
+      <c r="C577" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B578" t="s">
-        <v>151</v>
-      </c>
-      <c r="C578">
-        <v>0</v>
+        <v>1567</v>
+      </c>
+      <c r="C578" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B579" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C579" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
-        <v>157</v>
+        <v>419</v>
       </c>
       <c r="B580" t="s">
-        <v>1575</v>
+        <v>421</v>
       </c>
       <c r="C580" t="s">
-        <v>633</v>
+        <v>420</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="B581" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="C581" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>423</v>
+        <v>98</v>
       </c>
       <c r="B582" t="s">
-        <v>425</v>
+        <v>1548</v>
       </c>
       <c r="C582" t="s">
-        <v>424</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A583" s="1" t="s">
-        <v>95</v>
+      <c r="A583" t="s">
+        <v>97</v>
       </c>
       <c r="B583" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="C583" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A584" s="1" t="s">
-        <v>98</v>
+      <c r="A584" t="s">
+        <v>99</v>
       </c>
       <c r="B584" t="s">
-        <v>1556</v>
+        <v>103</v>
       </c>
       <c r="C584" t="s">
-        <v>1574</v>
+        <v>141</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A585" t="s">
-        <v>97</v>
+      <c r="A585" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="B585" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="C585" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A586" t="s">
-        <v>99</v>
+      <c r="A586" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="B586" t="s">
-        <v>103</v>
-      </c>
-      <c r="C586" t="s">
-        <v>141</v>
+        <v>118</v>
+      </c>
+      <c r="C586">
+        <v>0</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B587" t="s">
-        <v>108</v>
-      </c>
-      <c r="C587">
-        <v>0</v>
+        <v>1572</v>
+      </c>
+      <c r="C587" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="B588" t="s">
-        <v>112</v>
+        <v>1540</v>
       </c>
       <c r="C588" t="s">
-        <v>113</v>
-      </c>
+        <v>1552</v>
+      </c>
+      <c r="E588" s="1"/>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="B589" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="C589">
         <v>0</v>
@@ -13573,44 +13653,45 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="B590" t="s">
-        <v>1580</v>
-      </c>
-      <c r="C590" t="s">
-        <v>120</v>
+        <v>158</v>
+      </c>
+      <c r="C590">
+        <v>0</v>
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B591" t="s">
         <v>166</v>
       </c>
-      <c r="B591" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1560</v>
-      </c>
-      <c r="E591" s="1"/>
-    </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C591">
+        <v>0</v>
+      </c>
+      <c r="D591" s="1"/>
+    </row>
+    <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="B592" t="s">
-        <v>274</v>
-      </c>
-      <c r="C592" t="s">
-        <v>275</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C592">
+        <v>0</v>
+      </c>
+      <c r="D592" s="1"/>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>143</v>
+        <v>413</v>
       </c>
       <c r="B593" t="s">
-        <v>165</v>
+        <v>414</v>
       </c>
       <c r="C593">
         <v>0</v>
@@ -13618,120 +13699,123 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
-        <v>144</v>
+        <v>588</v>
       </c>
       <c r="B594" t="s">
-        <v>145</v>
-      </c>
-      <c r="C594">
-        <v>0</v>
+        <v>590</v>
+      </c>
+      <c r="C594" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>160</v>
+        <v>627</v>
       </c>
       <c r="B595" t="s">
-        <v>1581</v>
-      </c>
-      <c r="C595" t="s">
-        <v>268</v>
+        <v>628</v>
+      </c>
+      <c r="C595">
+        <v>0</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>172</v>
+        <v>1522</v>
       </c>
       <c r="B596" t="s">
-        <v>173</v>
-      </c>
-      <c r="C596">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A597" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B597" t="s">
-        <v>177</v>
-      </c>
-      <c r="C597">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A598" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B598" t="s">
-        <v>156</v>
-      </c>
-      <c r="C598">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A599" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B599" t="s">
-        <v>161</v>
-      </c>
-      <c r="C599">
-        <v>0</v>
-      </c>
+        <v>1574</v>
+      </c>
+      <c r="C596" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="8" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B597" s="9" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C597" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="D597" s="1"/>
+    </row>
+    <row r="598" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="8" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B598" s="9" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C598" s="9" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D598" s="1"/>
+    </row>
+    <row r="599" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="8" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B599" s="9" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C599" s="9" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D599" s="1"/>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="B600" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="C600">
         <v>0</v>
       </c>
-      <c r="D600" s="1"/>
-    </row>
-    <row r="601" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="B601" t="s">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="C601">
         <v>0</v>
       </c>
-      <c r="D601" s="1"/>
-    </row>
-    <row r="602" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="602" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>1576</v>
+        <v>307</v>
       </c>
       <c r="B602" t="s">
-        <v>1577</v>
-      </c>
-      <c r="D602" s="1"/>
+        <v>306</v>
+      </c>
+      <c r="C602" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B603" t="s">
         <v>271</v>
       </c>
-      <c r="B603" t="s">
+      <c r="C603" t="s">
         <v>272</v>
-      </c>
-      <c r="C603" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
-        <v>417</v>
+        <v>142</v>
       </c>
       <c r="B604" t="s">
-        <v>418</v>
+        <v>162</v>
       </c>
       <c r="C604">
         <v>0</v>
@@ -13739,53 +13823,72 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
-        <v>592</v>
+        <v>143</v>
       </c>
       <c r="B605" t="s">
-        <v>594</v>
-      </c>
-      <c r="C605" t="s">
-        <v>593</v>
+        <v>144</v>
+      </c>
+      <c r="C605">
+        <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>631</v>
+        <v>157</v>
       </c>
       <c r="B606" t="s">
-        <v>632</v>
-      </c>
-      <c r="C606">
-        <v>0</v>
+        <v>1573</v>
+      </c>
+      <c r="C606" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1530</v>
-      </c>
-      <c r="B607" s="9" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C607" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="611" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B611" s="3"/>
-    </row>
-    <row r="612" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B612" s="3"/>
-    </row>
-    <row r="613" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B613" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="B607" t="s">
+        <v>170</v>
+      </c>
+      <c r="C607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A608" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B608" t="s">
+        <v>174</v>
+      </c>
+      <c r="C608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A609" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D609" s="1"/>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A610" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B610" t="s">
+        <v>269</v>
+      </c>
+      <c r="C610" t="s">
+        <v>270</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{5A58CD41-CC61-4D83-8620-3795E86571BA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/前缀.xlsx
+++ b/前缀.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lazy\Desktop\Research-on-the-Identification-Mechanism-of-Altmetrics-Data-for-Sina-Weibo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F998900-D0AD-4E08-A090-F7D503EE24D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C368AF-94B8-4169-BDD2-4D4122095254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -672,10 +672,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>百度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://xueshu.baidu.com/usercenter/paper/show?paperid=</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6371,6 +6367,10 @@
   </si>
   <si>
     <t>HIGHER EDUCATION PRESS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>百度学术</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6464,7 +6464,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6490,9 +6490,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6784,7 +6781,7 @@
       </c>
       <c r="D1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6792,27 +6789,27 @@
         <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="C2" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="C3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6823,11 +6820,11 @@
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6835,14 +6832,14 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" s="3"/>
       <c r="F5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6857,7 +6854,7 @@
       </c>
       <c r="D6" s="2"/>
       <c r="F6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6865,13 +6862,13 @@
         <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>132</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6879,7 +6876,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C8" t="s">
         <v>133</v>
@@ -6890,7 +6887,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -6901,10 +6898,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6934,10 +6931,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" t="s">
         <v>370</v>
-      </c>
-      <c r="C13" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6945,10 +6942,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6967,10 +6964,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
+        <v>415</v>
+      </c>
+      <c r="C16" t="s">
         <v>416</v>
-      </c>
-      <c r="C16" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -7011,10 +7008,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -7025,7 +7022,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -7044,10 +7041,10 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -7066,7 +7063,7 @@
         <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C25" t="s">
         <v>135</v>
@@ -7124,7 +7121,7 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -7135,7 +7132,7 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7165,7 +7162,7 @@
         <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C34" t="s">
         <v>136</v>
@@ -7176,7 +7173,7 @@
         <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="C35" t="s">
         <v>65</v>
@@ -7184,10 +7181,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -7198,10 +7195,10 @@
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C37" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -7231,7 +7228,7 @@
         <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
@@ -7239,32 +7236,32 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B41" t="s">
         <v>436</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>437</v>
-      </c>
-      <c r="C41" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B42" t="s">
         <v>439</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>440</v>
-      </c>
-      <c r="C42" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B43" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -7272,13 +7269,13 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B44" t="s">
         <v>221</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>222</v>
-      </c>
-      <c r="C44" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -7294,90 +7291,90 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" t="s">
         <v>228</v>
-      </c>
-      <c r="B47" t="s">
-        <v>234</v>
-      </c>
-      <c r="C47" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B48" t="s">
+        <v>530</v>
+      </c>
+      <c r="C48" t="s">
         <v>226</v>
-      </c>
-      <c r="B48" t="s">
-        <v>531</v>
-      </c>
-      <c r="C48" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B49" t="s">
         <v>232</v>
       </c>
-      <c r="B49" t="s">
-        <v>233</v>
-      </c>
       <c r="C49" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B50" t="s">
         <v>235</v>
       </c>
-      <c r="B50" t="s">
-        <v>236</v>
-      </c>
       <c r="C50" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B51" t="s">
         <v>237</v>
       </c>
-      <c r="B51" t="s">
-        <v>238</v>
-      </c>
       <c r="C51" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C52" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B53" t="s">
         <v>241</v>
       </c>
-      <c r="B53" t="s">
-        <v>242</v>
-      </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -7404,57 +7401,57 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B57" t="s">
+        <v>244</v>
+      </c>
+      <c r="C57" t="s">
         <v>245</v>
-      </c>
-      <c r="C57" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B58" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" t="s">
         <v>248</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>249</v>
-      </c>
-      <c r="C59" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" t="s">
         <v>177</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>178</v>
-      </c>
-      <c r="C60" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="6" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7462,54 +7459,54 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="C61" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B62" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C62" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C63" t="s">
         <v>190</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1536</v>
-      </c>
-      <c r="C63" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64" t="s">
         <v>202</v>
-      </c>
-      <c r="B64" t="s">
-        <v>204</v>
-      </c>
-      <c r="C64" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B65" t="s">
+        <v>209</v>
+      </c>
+      <c r="C65" t="s">
         <v>208</v>
-      </c>
-      <c r="B65" t="s">
-        <v>210</v>
-      </c>
-      <c r="C65" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -7528,10 +7525,10 @@
         <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C67" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -7575,7 +7572,7 @@
         <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7591,21 +7588,21 @@
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>426</v>
+      </c>
+      <c r="B74" t="s">
         <v>427</v>
-      </c>
-      <c r="B74" t="s">
-        <v>428</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7613,10 +7610,10 @@
     </row>
     <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B75" t="s">
         <v>443</v>
-      </c>
-      <c r="B75" t="s">
-        <v>444</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7624,32 +7621,32 @@
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B76" t="s">
+        <v>536</v>
+      </c>
+      <c r="C76" t="s">
         <v>429</v>
-      </c>
-      <c r="B76" t="s">
-        <v>537</v>
-      </c>
-      <c r="C76" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C77" t="s">
         <v>424</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C77" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B78" t="s">
         <v>422</v>
-      </c>
-      <c r="B78" t="s">
-        <v>423</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7657,120 +7654,120 @@
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B79" t="s">
         <v>251</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>252</v>
-      </c>
-      <c r="C79" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B80" t="s">
         <v>257</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>258</v>
-      </c>
-      <c r="C80" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B81" t="s">
         <v>263</v>
       </c>
-      <c r="B81" t="s">
-        <v>264</v>
-      </c>
       <c r="C81" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82" t="s">
         <v>260</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
-      </c>
-      <c r="C82" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C83" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B84" t="s">
         <v>254</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>255</v>
-      </c>
-      <c r="C84" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B85" t="s">
         <v>276</v>
       </c>
-      <c r="B85" t="s">
-        <v>277</v>
-      </c>
       <c r="C85" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B86" t="s">
         <v>278</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>279</v>
-      </c>
-      <c r="C86" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B87" t="s">
         <v>281</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>282</v>
-      </c>
-      <c r="C87" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B88" t="s">
+        <v>285</v>
+      </c>
+      <c r="C88" t="s">
         <v>284</v>
-      </c>
-      <c r="B88" t="s">
-        <v>286</v>
-      </c>
-      <c r="C88" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B89" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7778,54 +7775,54 @@
     </row>
     <row r="90" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B90" t="s">
         <v>289</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>290</v>
-      </c>
-      <c r="C90" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B91" t="s">
         <v>292</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>293</v>
-      </c>
-      <c r="C91" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B92" t="s">
         <v>295</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>296</v>
-      </c>
-      <c r="C92" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B93" t="s">
         <v>298</v>
       </c>
-      <c r="B93" t="s">
-        <v>299</v>
-      </c>
       <c r="C93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B94" t="s">
         <v>300</v>
-      </c>
-      <c r="B94" t="s">
-        <v>301</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -7833,10 +7830,10 @@
     </row>
     <row r="95" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B95" t="s">
         <v>302</v>
-      </c>
-      <c r="B95" t="s">
-        <v>303</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -7844,131 +7841,131 @@
     </row>
     <row r="96" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B96" t="s">
+        <v>303</v>
+      </c>
+      <c r="C96" t="s">
         <v>304</v>
-      </c>
-      <c r="C96" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B97" t="s">
         <v>309</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>310</v>
-      </c>
-      <c r="C97" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B98" t="s">
         <v>312</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>313</v>
-      </c>
-      <c r="C98" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B99" t="s">
+        <v>539</v>
+      </c>
+      <c r="C99" t="s">
         <v>540</v>
-      </c>
-      <c r="C99" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B100" t="s">
+        <v>318</v>
+      </c>
+      <c r="C100" t="s">
         <v>316</v>
-      </c>
-      <c r="B100" t="s">
-        <v>319</v>
-      </c>
-      <c r="C100" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B101" t="s">
         <v>322</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>323</v>
-      </c>
-      <c r="C101" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B102" t="s">
         <v>320</v>
       </c>
-      <c r="B102" t="s">
-        <v>321</v>
-      </c>
       <c r="C102" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B103" t="s">
         <v>325</v>
       </c>
-      <c r="B103" t="s">
-        <v>326</v>
-      </c>
       <c r="C103" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B104" t="s">
         <v>327</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
         <v>328</v>
-      </c>
-      <c r="C104" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B105" t="s">
         <v>330</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C105" t="s">
         <v>331</v>
-      </c>
-      <c r="C105" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C106" t="s">
         <v>543</v>
-      </c>
-      <c r="C106" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -7976,10 +7973,10 @@
     </row>
     <row r="108" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B108" t="s">
         <v>335</v>
-      </c>
-      <c r="B108" t="s">
-        <v>336</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -7987,252 +7984,252 @@
     </row>
     <row r="109" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B109" t="s">
         <v>337</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>338</v>
-      </c>
-      <c r="C109" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B110" t="s">
+        <v>341</v>
+      </c>
+      <c r="C110" t="s">
         <v>340</v>
-      </c>
-      <c r="B110" t="s">
-        <v>342</v>
-      </c>
-      <c r="C110" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B111" t="s">
         <v>343</v>
       </c>
-      <c r="B111" t="s">
-        <v>344</v>
-      </c>
       <c r="C111" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B112" t="s">
+        <v>344</v>
+      </c>
+      <c r="C112" t="s">
         <v>346</v>
-      </c>
-      <c r="B112" t="s">
-        <v>345</v>
-      </c>
-      <c r="C112" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B113" t="s">
         <v>348</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>349</v>
-      </c>
-      <c r="C113" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B114" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="C114" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B115" t="s">
+        <v>354</v>
+      </c>
+      <c r="C115" t="s">
         <v>353</v>
-      </c>
-      <c r="B115" t="s">
-        <v>355</v>
-      </c>
-      <c r="C115" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B117" t="s">
         <v>359</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>360</v>
-      </c>
-      <c r="C117" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B118" t="s">
+        <v>361</v>
+      </c>
+      <c r="C118" t="s">
         <v>362</v>
-      </c>
-      <c r="C118" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C119" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B120" t="s">
+        <v>367</v>
+      </c>
+      <c r="C120" t="s">
         <v>366</v>
-      </c>
-      <c r="B120" t="s">
-        <v>368</v>
-      </c>
-      <c r="C120" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B122" t="s">
         <v>372</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>373</v>
-      </c>
-      <c r="C122" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B123" t="s">
         <v>375</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>376</v>
-      </c>
-      <c r="C123" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B124" t="s">
+        <v>379</v>
+      </c>
+      <c r="C124" t="s">
         <v>378</v>
-      </c>
-      <c r="B124" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B125" t="s">
         <v>381</v>
       </c>
-      <c r="B125" t="s">
-        <v>382</v>
-      </c>
       <c r="C125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B126" t="s">
         <v>431</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>432</v>
-      </c>
-      <c r="C126" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B127" t="s">
         <v>383</v>
       </c>
-      <c r="B127" t="s">
-        <v>384</v>
-      </c>
       <c r="C127" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B128" t="s">
         <v>385</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>386</v>
-      </c>
-      <c r="C128" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B129" t="s">
         <v>388</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>389</v>
-      </c>
-      <c r="C129" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B130" t="s">
         <v>391</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>392</v>
-      </c>
-      <c r="C130" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B131" t="s">
         <v>394</v>
-      </c>
-      <c r="B131" t="s">
-        <v>395</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -8240,153 +8237,153 @@
     </row>
     <row r="132" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B132" t="s">
         <v>396</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>397</v>
-      </c>
-      <c r="C132" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B133" t="s">
         <v>399</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>400</v>
-      </c>
-      <c r="C133" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B134" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C134" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B135" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C135" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B136" t="s">
         <v>404</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>405</v>
-      </c>
-      <c r="C136" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B137" t="s">
         <v>448</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C137" t="s">
         <v>449</v>
-      </c>
-      <c r="C137" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B138" t="s">
         <v>451</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C138" t="s">
         <v>452</v>
-      </c>
-      <c r="C138" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B139" t="s">
         <v>407</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>408</v>
-      </c>
-      <c r="C139" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B140" t="s">
+        <v>549</v>
+      </c>
+      <c r="C140" t="s">
         <v>454</v>
-      </c>
-      <c r="B140" t="s">
-        <v>550</v>
-      </c>
-      <c r="C140" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B141" t="s">
         <v>457</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>458</v>
-      </c>
-      <c r="C141" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B142" t="s">
         <v>460</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C142" t="s">
         <v>461</v>
-      </c>
-      <c r="C142" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B143" t="s">
+        <v>464</v>
+      </c>
+      <c r="C143" t="s">
         <v>463</v>
-      </c>
-      <c r="B143" t="s">
-        <v>465</v>
-      </c>
-      <c r="C143" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B144" t="s">
+        <v>467</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="B144" t="s">
-        <v>468</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B145" t="s">
         <v>469</v>
-      </c>
-      <c r="B145" t="s">
-        <v>470</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -8394,43 +8391,43 @@
     </row>
     <row r="146" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C146" t="s">
         <v>471</v>
-      </c>
-      <c r="B146" t="s">
-        <v>1560</v>
-      </c>
-      <c r="C146" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B147" t="s">
         <v>473</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" t="s">
         <v>474</v>
-      </c>
-      <c r="C147" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B148" t="s">
         <v>476</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>477</v>
-      </c>
-      <c r="C148" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B149" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -8438,32 +8435,32 @@
     </row>
     <row r="150" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B150" t="s">
         <v>480</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
         <v>481</v>
-      </c>
-      <c r="C150" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B151" t="s">
         <v>483</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>484</v>
-      </c>
-      <c r="C151" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B152" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -8471,32 +8468,32 @@
     </row>
     <row r="153" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B153" t="s">
+        <v>488</v>
+      </c>
+      <c r="C153" t="s">
         <v>487</v>
-      </c>
-      <c r="B153" t="s">
-        <v>489</v>
-      </c>
-      <c r="C153" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B154" t="s">
         <v>490</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" t="s">
         <v>491</v>
-      </c>
-      <c r="C154" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B155" t="s">
         <v>493</v>
-      </c>
-      <c r="B155" t="s">
-        <v>494</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -8504,43 +8501,43 @@
     </row>
     <row r="156" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B156" t="s">
         <v>495</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>496</v>
-      </c>
-      <c r="C156" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B157" t="s">
         <v>498</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" t="s">
         <v>499</v>
-      </c>
-      <c r="C157" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B158" t="s">
+        <v>502</v>
+      </c>
+      <c r="C158" t="s">
         <v>501</v>
-      </c>
-      <c r="B158" t="s">
-        <v>503</v>
-      </c>
-      <c r="C158" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B159" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C159" s="7">
         <v>0</v>
@@ -8548,10 +8545,10 @@
     </row>
     <row r="160" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B160" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C160" s="7">
         <v>0</v>
@@ -8559,21 +8556,21 @@
     </row>
     <row r="161" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B161" t="s">
+        <v>554</v>
+      </c>
+      <c r="C161" t="s">
         <v>506</v>
-      </c>
-      <c r="B161" t="s">
-        <v>555</v>
-      </c>
-      <c r="C161" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B162" t="s">
         <v>508</v>
-      </c>
-      <c r="B162" t="s">
-        <v>509</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -8581,76 +8578,76 @@
     </row>
     <row r="163" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B163" t="s">
         <v>510</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C163" t="s">
         <v>511</v>
-      </c>
-      <c r="C163" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B164" t="s">
+        <v>514</v>
+      </c>
+      <c r="C164" t="s">
         <v>513</v>
-      </c>
-      <c r="B164" t="s">
-        <v>515</v>
-      </c>
-      <c r="C164" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B165" t="s">
         <v>516</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C165" t="s">
         <v>517</v>
-      </c>
-      <c r="C165" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B166" t="s">
         <v>519</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C166" t="s">
         <v>520</v>
-      </c>
-      <c r="C166" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="B167" t="s">
+        <v>523</v>
+      </c>
+      <c r="C167" t="s">
         <v>522</v>
-      </c>
-      <c r="B167" t="s">
-        <v>524</v>
-      </c>
-      <c r="C167" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B168" t="s">
+        <v>526</v>
+      </c>
+      <c r="C168" t="s">
         <v>525</v>
-      </c>
-      <c r="B168" t="s">
-        <v>527</v>
-      </c>
-      <c r="C168" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="B169" t="s">
         <v>528</v>
-      </c>
-      <c r="B169" t="s">
-        <v>529</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -8658,10 +8655,10 @@
     </row>
     <row r="170" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B170" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -8669,21 +8666,21 @@
     </row>
     <row r="171" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="B171" t="s">
         <v>557</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
         <v>558</v>
-      </c>
-      <c r="C171" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B172" t="s">
         <v>560</v>
-      </c>
-      <c r="B172" t="s">
-        <v>561</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -8691,43 +8688,43 @@
     </row>
     <row r="173" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="B173" t="s">
+        <v>563</v>
+      </c>
+      <c r="C173" t="s">
         <v>562</v>
-      </c>
-      <c r="B173" t="s">
-        <v>564</v>
-      </c>
-      <c r="C173" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="B174" t="s">
+        <v>566</v>
+      </c>
+      <c r="C174" t="s">
         <v>565</v>
-      </c>
-      <c r="B174" t="s">
-        <v>567</v>
-      </c>
-      <c r="C174" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="B175" t="s">
         <v>568</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C175" t="s">
         <v>569</v>
-      </c>
-      <c r="C175" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="B176" t="s">
         <v>571</v>
-      </c>
-      <c r="B176" t="s">
-        <v>572</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -8735,10 +8732,10 @@
     </row>
     <row r="177" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="B177" t="s">
         <v>573</v>
-      </c>
-      <c r="B177" t="s">
-        <v>574</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -8746,10 +8743,10 @@
     </row>
     <row r="178" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="B178" t="s">
         <v>575</v>
-      </c>
-      <c r="B178" t="s">
-        <v>576</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -8757,10 +8754,10 @@
     </row>
     <row r="179" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="B179" t="s">
         <v>577</v>
-      </c>
-      <c r="B179" t="s">
-        <v>578</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -8768,21 +8765,21 @@
     </row>
     <row r="180" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="B180" t="s">
         <v>579</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C180" t="s">
         <v>580</v>
-      </c>
-      <c r="C180" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B181" t="s">
         <v>582</v>
-      </c>
-      <c r="B181" t="s">
-        <v>583</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -8790,21 +8787,21 @@
     </row>
     <row r="182" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="B182" t="s">
         <v>584</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>585</v>
-      </c>
-      <c r="C182" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B183" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -8813,82 +8810,82 @@
     </row>
     <row r="184" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="B184" t="s">
+        <v>592</v>
+      </c>
+      <c r="C184" t="s">
         <v>591</v>
-      </c>
-      <c r="B184" t="s">
-        <v>593</v>
-      </c>
-      <c r="C184" t="s">
-        <v>592</v>
       </c>
       <c r="D184" s="1"/>
     </row>
     <row r="185" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="B185" t="s">
         <v>595</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>596</v>
-      </c>
-      <c r="C185" t="s">
-        <v>597</v>
       </c>
       <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C186" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B187" t="s">
+        <v>601</v>
+      </c>
+      <c r="C187" t="s">
         <v>602</v>
-      </c>
-      <c r="C187" t="s">
-        <v>603</v>
       </c>
       <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="B188" t="s">
         <v>604</v>
       </c>
-      <c r="B188" t="s">
+      <c r="C188" t="s">
         <v>605</v>
-      </c>
-      <c r="C188" t="s">
-        <v>606</v>
       </c>
       <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="B189" t="s">
         <v>607</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>608</v>
-      </c>
-      <c r="C189" t="s">
-        <v>609</v>
       </c>
       <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B190" t="s">
         <v>610</v>
-      </c>
-      <c r="B190" t="s">
-        <v>611</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -8897,22 +8894,22 @@
     </row>
     <row r="191" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B191" t="s">
         <v>612</v>
       </c>
-      <c r="B191" t="s">
+      <c r="C191" t="s">
         <v>613</v>
-      </c>
-      <c r="C191" t="s">
-        <v>614</v>
       </c>
       <c r="D191" s="1"/>
     </row>
     <row r="192" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="B192" t="s">
         <v>615</v>
-      </c>
-      <c r="B192" t="s">
-        <v>616</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -8921,34 +8918,34 @@
     </row>
     <row r="193" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B193" t="s">
         <v>617</v>
       </c>
-      <c r="B193" t="s">
+      <c r="C193" t="s">
         <v>618</v>
-      </c>
-      <c r="C193" t="s">
-        <v>619</v>
       </c>
       <c r="D193" s="1"/>
     </row>
     <row r="194" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B194" t="s">
         <v>620</v>
       </c>
-      <c r="B194" t="s">
+      <c r="C194" t="s">
         <v>621</v>
-      </c>
-      <c r="C194" t="s">
-        <v>622</v>
       </c>
       <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B195" t="s">
         <v>623</v>
-      </c>
-      <c r="B195" t="s">
-        <v>624</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -8957,10 +8954,10 @@
     </row>
     <row r="196" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="B196" t="s">
         <v>625</v>
-      </c>
-      <c r="B196" t="s">
-        <v>626</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -8969,10 +8966,10 @@
     </row>
     <row r="197" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B197" t="s">
         <v>630</v>
-      </c>
-      <c r="B197" t="s">
-        <v>631</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8981,22 +8978,22 @@
     </row>
     <row r="198" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B198" t="s">
         <v>632</v>
       </c>
-      <c r="B198" t="s">
+      <c r="C198" t="s">
         <v>633</v>
-      </c>
-      <c r="C198" t="s">
-        <v>634</v>
       </c>
       <c r="D198" s="1"/>
     </row>
     <row r="199" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="B199" t="s">
         <v>635</v>
-      </c>
-      <c r="B199" t="s">
-        <v>636</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -9005,10 +9002,10 @@
     </row>
     <row r="200" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B200" t="s">
         <v>637</v>
-      </c>
-      <c r="B200" t="s">
-        <v>638</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -9017,34 +9014,34 @@
     </row>
     <row r="201" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B201" t="s">
+        <v>640</v>
+      </c>
+      <c r="C201" t="s">
         <v>639</v>
-      </c>
-      <c r="B201" t="s">
-        <v>641</v>
-      </c>
-      <c r="C201" t="s">
-        <v>640</v>
       </c>
       <c r="D201" s="1"/>
     </row>
     <row r="202" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B202" t="s">
+        <v>643</v>
+      </c>
+      <c r="C202" t="s">
         <v>642</v>
-      </c>
-      <c r="B202" t="s">
-        <v>644</v>
-      </c>
-      <c r="C202" t="s">
-        <v>643</v>
       </c>
       <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="B203" t="s">
         <v>645</v>
-      </c>
-      <c r="B203" t="s">
-        <v>646</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -9053,10 +9050,10 @@
     </row>
     <row r="204" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="B204" t="s">
         <v>647</v>
-      </c>
-      <c r="B204" t="s">
-        <v>648</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -9065,10 +9062,10 @@
     </row>
     <row r="205" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="B205" t="s">
         <v>649</v>
-      </c>
-      <c r="B205" t="s">
-        <v>650</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -9077,10 +9074,10 @@
     </row>
     <row r="206" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="B206" t="s">
         <v>651</v>
-      </c>
-      <c r="B206" t="s">
-        <v>652</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -9089,10 +9086,10 @@
     </row>
     <row r="207" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B207" t="s">
         <v>653</v>
-      </c>
-      <c r="B207" t="s">
-        <v>654</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -9101,58 +9098,58 @@
     </row>
     <row r="208" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="B208" t="s">
+        <v>656</v>
+      </c>
+      <c r="C208" t="s">
         <v>655</v>
-      </c>
-      <c r="B208" t="s">
-        <v>657</v>
-      </c>
-      <c r="C208" t="s">
-        <v>656</v>
       </c>
       <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="B209" t="s">
         <v>658</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>659</v>
-      </c>
-      <c r="C209" t="s">
-        <v>660</v>
       </c>
       <c r="D209" s="1"/>
     </row>
     <row r="210" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="B210" t="s">
         <v>661</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>662</v>
-      </c>
-      <c r="C210" t="s">
-        <v>663</v>
       </c>
       <c r="D210" s="1"/>
     </row>
     <row r="211" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="B211" t="s">
+        <v>665</v>
+      </c>
+      <c r="C211" t="s">
         <v>664</v>
-      </c>
-      <c r="B211" t="s">
-        <v>666</v>
-      </c>
-      <c r="C211" t="s">
-        <v>665</v>
       </c>
       <c r="D211" s="1"/>
     </row>
     <row r="212" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="B212" t="s">
         <v>667</v>
-      </c>
-      <c r="B212" t="s">
-        <v>668</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -9161,34 +9158,34 @@
     </row>
     <row r="213" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="B213" t="s">
+        <v>670</v>
+      </c>
+      <c r="C213" t="s">
         <v>669</v>
-      </c>
-      <c r="B213" t="s">
-        <v>671</v>
-      </c>
-      <c r="C213" t="s">
-        <v>670</v>
       </c>
       <c r="D213" s="1"/>
     </row>
     <row r="214" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B214" t="s">
         <v>672</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>673</v>
-      </c>
-      <c r="C214" t="s">
-        <v>674</v>
       </c>
       <c r="D214" s="1"/>
     </row>
     <row r="215" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="B215" t="s">
         <v>675</v>
-      </c>
-      <c r="B215" t="s">
-        <v>676</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -9197,58 +9194,58 @@
     </row>
     <row r="216" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="B216" t="s">
+        <v>678</v>
+      </c>
+      <c r="C216" t="s">
         <v>677</v>
-      </c>
-      <c r="B216" t="s">
-        <v>679</v>
-      </c>
-      <c r="C216" t="s">
-        <v>678</v>
       </c>
       <c r="D216" s="1"/>
     </row>
     <row r="217" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="B217" t="s">
+        <v>681</v>
+      </c>
+      <c r="C217" t="s">
         <v>680</v>
-      </c>
-      <c r="B217" t="s">
-        <v>682</v>
-      </c>
-      <c r="C217" t="s">
-        <v>681</v>
       </c>
       <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="B218" t="s">
         <v>683</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>684</v>
-      </c>
-      <c r="C218" t="s">
-        <v>685</v>
       </c>
       <c r="D218" s="1"/>
     </row>
     <row r="219" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B219" t="s">
         <v>686</v>
       </c>
-      <c r="B219" t="s">
+      <c r="C219" t="s">
         <v>687</v>
-      </c>
-      <c r="C219" t="s">
-        <v>688</v>
       </c>
       <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B220" t="s">
         <v>689</v>
-      </c>
-      <c r="B220" t="s">
-        <v>690</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -9257,58 +9254,58 @@
     </row>
     <row r="221" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B221" t="s">
         <v>691</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>692</v>
-      </c>
-      <c r="C221" t="s">
-        <v>693</v>
       </c>
       <c r="D221" s="1"/>
     </row>
     <row r="222" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B222" t="s">
         <v>694</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>695</v>
-      </c>
-      <c r="C222" t="s">
-        <v>696</v>
       </c>
       <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="B223" t="s">
+        <v>698</v>
+      </c>
+      <c r="C223" t="s">
         <v>697</v>
-      </c>
-      <c r="B223" t="s">
-        <v>699</v>
-      </c>
-      <c r="C223" t="s">
-        <v>698</v>
       </c>
       <c r="D223" s="1"/>
     </row>
     <row r="224" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="B224" t="s">
+        <v>701</v>
+      </c>
+      <c r="C224" t="s">
         <v>700</v>
-      </c>
-      <c r="B224" t="s">
-        <v>702</v>
-      </c>
-      <c r="C224" t="s">
-        <v>701</v>
       </c>
       <c r="D224" s="1"/>
     </row>
     <row r="225" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="B225" t="s">
         <v>703</v>
-      </c>
-      <c r="B225" t="s">
-        <v>704</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -9317,58 +9314,58 @@
     </row>
     <row r="226" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B226" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C226" t="s">
         <v>1529</v>
-      </c>
-      <c r="C226" t="s">
-        <v>1530</v>
       </c>
       <c r="D226" s="1"/>
     </row>
     <row r="227" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="B227" t="s">
         <v>706</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C227" t="s">
         <v>707</v>
-      </c>
-      <c r="C227" t="s">
-        <v>708</v>
       </c>
       <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="B228" t="s">
         <v>709</v>
       </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
         <v>710</v>
-      </c>
-      <c r="C228" t="s">
-        <v>711</v>
       </c>
       <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="B229" t="s">
         <v>712</v>
       </c>
-      <c r="B229" t="s">
+      <c r="C229" t="s">
         <v>713</v>
-      </c>
-      <c r="C229" t="s">
-        <v>714</v>
       </c>
       <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="B230" t="s">
         <v>715</v>
-      </c>
-      <c r="B230" t="s">
-        <v>716</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -9377,22 +9374,22 @@
     </row>
     <row r="231" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="B231" t="s">
+        <v>718</v>
+      </c>
+      <c r="C231" t="s">
         <v>717</v>
-      </c>
-      <c r="B231" t="s">
-        <v>719</v>
-      </c>
-      <c r="C231" t="s">
-        <v>718</v>
       </c>
       <c r="D231" s="1"/>
     </row>
     <row r="232" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B232" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -9401,46 +9398,46 @@
     </row>
     <row r="233" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="B233" t="s">
         <v>721</v>
       </c>
-      <c r="B233" t="s">
+      <c r="C233" t="s">
         <v>722</v>
-      </c>
-      <c r="C233" t="s">
-        <v>723</v>
       </c>
       <c r="D233" s="1"/>
     </row>
     <row r="234" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="B234" t="s">
+        <v>725</v>
+      </c>
+      <c r="C234" t="s">
         <v>724</v>
-      </c>
-      <c r="B234" t="s">
-        <v>726</v>
-      </c>
-      <c r="C234" t="s">
-        <v>725</v>
       </c>
       <c r="D234" s="1"/>
     </row>
     <row r="235" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="B235" t="s">
         <v>727</v>
       </c>
-      <c r="B235" t="s">
+      <c r="C235" t="s">
         <v>728</v>
-      </c>
-      <c r="C235" t="s">
-        <v>729</v>
       </c>
       <c r="D235" s="1"/>
     </row>
     <row r="236" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="B236" t="s">
         <v>730</v>
-      </c>
-      <c r="B236" t="s">
-        <v>731</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -9449,10 +9446,10 @@
     </row>
     <row r="237" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B237" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9461,10 +9458,10 @@
     </row>
     <row r="238" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="B238" t="s">
         <v>734</v>
-      </c>
-      <c r="B238" t="s">
-        <v>735</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9473,34 +9470,34 @@
     </row>
     <row r="239" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B239" t="s">
         <v>736</v>
       </c>
-      <c r="B239" t="s">
+      <c r="C239" t="s">
         <v>737</v>
-      </c>
-      <c r="C239" t="s">
-        <v>738</v>
       </c>
       <c r="D239" s="1"/>
     </row>
     <row r="240" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B240" t="s">
         <v>739</v>
       </c>
-      <c r="B240" t="s">
+      <c r="C240" t="s">
         <v>740</v>
-      </c>
-      <c r="C240" t="s">
-        <v>741</v>
       </c>
       <c r="D240" s="1"/>
     </row>
     <row r="241" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="B241" t="s">
         <v>742</v>
-      </c>
-      <c r="B241" t="s">
-        <v>743</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -9509,10 +9506,10 @@
     </row>
     <row r="242" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="B242" t="s">
         <v>744</v>
-      </c>
-      <c r="B242" t="s">
-        <v>745</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -9521,10 +9518,10 @@
     </row>
     <row r="243" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="B243" t="s">
         <v>746</v>
-      </c>
-      <c r="B243" t="s">
-        <v>747</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -9533,10 +9530,10 @@
     </row>
     <row r="244" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="B244" t="s">
         <v>748</v>
-      </c>
-      <c r="B244" t="s">
-        <v>749</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -9545,10 +9542,10 @@
     </row>
     <row r="245" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="B245" t="s">
         <v>750</v>
-      </c>
-      <c r="B245" t="s">
-        <v>751</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -9557,10 +9554,10 @@
     </row>
     <row r="246" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="B246" t="s">
         <v>752</v>
-      </c>
-      <c r="B246" t="s">
-        <v>753</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9569,34 +9566,34 @@
     </row>
     <row r="247" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="B247" t="s">
         <v>754</v>
       </c>
-      <c r="B247" t="s">
+      <c r="C247" t="s">
         <v>755</v>
-      </c>
-      <c r="C247" t="s">
-        <v>756</v>
       </c>
       <c r="D247" s="1"/>
     </row>
     <row r="248" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="B248" t="s">
         <v>757</v>
       </c>
-      <c r="B248" t="s">
+      <c r="C248" t="s">
         <v>758</v>
-      </c>
-      <c r="C248" t="s">
-        <v>759</v>
       </c>
       <c r="D248" s="1"/>
     </row>
     <row r="249" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="B249" t="s">
         <v>760</v>
-      </c>
-      <c r="B249" t="s">
-        <v>761</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -9605,34 +9602,34 @@
     </row>
     <row r="250" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="B250" t="s">
+        <v>763</v>
+      </c>
+      <c r="C250" t="s">
         <v>762</v>
-      </c>
-      <c r="B250" t="s">
-        <v>764</v>
-      </c>
-      <c r="C250" t="s">
-        <v>763</v>
       </c>
       <c r="D250" s="1"/>
     </row>
     <row r="251" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="B251" t="s">
         <v>765</v>
       </c>
-      <c r="B251" t="s">
+      <c r="C251" t="s">
         <v>766</v>
-      </c>
-      <c r="C251" t="s">
-        <v>767</v>
       </c>
       <c r="D251" s="1"/>
     </row>
     <row r="252" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="B252" t="s">
         <v>768</v>
-      </c>
-      <c r="B252" t="s">
-        <v>769</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -9641,22 +9638,22 @@
     </row>
     <row r="253" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="B253" t="s">
         <v>770</v>
       </c>
-      <c r="B253" t="s">
-        <v>771</v>
-      </c>
       <c r="C253" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D253" s="1"/>
     </row>
     <row r="254" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="B254" t="s">
         <v>772</v>
-      </c>
-      <c r="B254" t="s">
-        <v>773</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -9665,34 +9662,34 @@
     </row>
     <row r="255" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="B255" t="s">
         <v>774</v>
       </c>
-      <c r="B255" t="s">
-        <v>775</v>
-      </c>
       <c r="C255" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D255" s="1"/>
     </row>
     <row r="256" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B256" t="s">
+        <v>777</v>
+      </c>
+      <c r="C256" t="s">
         <v>778</v>
-      </c>
-      <c r="C256" t="s">
-        <v>779</v>
       </c>
       <c r="D256" s="1"/>
     </row>
     <row r="257" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="B257" t="s">
         <v>780</v>
-      </c>
-      <c r="B257" t="s">
-        <v>781</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -9701,10 +9698,10 @@
     </row>
     <row r="258" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="B258" t="s">
         <v>782</v>
-      </c>
-      <c r="B258" t="s">
-        <v>783</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -9713,22 +9710,22 @@
     </row>
     <row r="259" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="B259" t="s">
         <v>784</v>
       </c>
-      <c r="B259" t="s">
+      <c r="C259" t="s">
         <v>785</v>
-      </c>
-      <c r="C259" t="s">
-        <v>786</v>
       </c>
       <c r="D259" s="1"/>
     </row>
     <row r="260" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="B260" t="s">
         <v>787</v>
-      </c>
-      <c r="B260" t="s">
-        <v>788</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -9737,22 +9734,22 @@
     </row>
     <row r="261" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="B261" t="s">
         <v>789</v>
       </c>
-      <c r="B261" t="s">
+      <c r="C261" t="s">
         <v>790</v>
-      </c>
-      <c r="C261" t="s">
-        <v>791</v>
       </c>
       <c r="D261" s="1"/>
     </row>
     <row r="262" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="B262" t="s">
         <v>792</v>
-      </c>
-      <c r="B262" t="s">
-        <v>793</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -9761,10 +9758,10 @@
     </row>
     <row r="263" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -9773,10 +9770,10 @@
     </row>
     <row r="264" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="B264" t="s">
         <v>795</v>
-      </c>
-      <c r="B264" t="s">
-        <v>796</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -9785,10 +9782,10 @@
     </row>
     <row r="265" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="8" t="s">
+        <v>796</v>
+      </c>
+      <c r="B265" t="s">
         <v>797</v>
-      </c>
-      <c r="B265" t="s">
-        <v>798</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -9797,34 +9794,34 @@
     </row>
     <row r="266" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B266" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C266" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D266" s="1"/>
     </row>
     <row r="267" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="8" t="s">
+        <v>799</v>
+      </c>
+      <c r="B267" t="s">
         <v>800</v>
       </c>
-      <c r="B267" t="s">
+      <c r="C267" t="s">
         <v>801</v>
-      </c>
-      <c r="C267" t="s">
-        <v>802</v>
       </c>
       <c r="D267" s="1"/>
     </row>
     <row r="268" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="B268" t="s">
         <v>803</v>
-      </c>
-      <c r="B268" t="s">
-        <v>804</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -9833,22 +9830,22 @@
     </row>
     <row r="269" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="B269" t="s">
         <v>805</v>
       </c>
-      <c r="B269" t="s">
+      <c r="C269" t="s">
         <v>806</v>
-      </c>
-      <c r="C269" t="s">
-        <v>807</v>
       </c>
       <c r="D269" s="1"/>
     </row>
     <row r="270" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="B270" t="s">
         <v>808</v>
-      </c>
-      <c r="B270" t="s">
-        <v>809</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -9857,22 +9854,22 @@
     </row>
     <row r="271" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B271" t="s">
         <v>810</v>
       </c>
-      <c r="B271" t="s">
+      <c r="C271" t="s">
         <v>811</v>
-      </c>
-      <c r="C271" t="s">
-        <v>812</v>
       </c>
       <c r="D271" s="1"/>
     </row>
     <row r="272" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
-        <v>813</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>1578</v>
+        <v>812</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1577</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -9881,82 +9878,82 @@
     </row>
     <row r="273" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="B273" t="s">
+        <v>815</v>
+      </c>
+      <c r="C273" t="s">
         <v>814</v>
-      </c>
-      <c r="B273" t="s">
-        <v>816</v>
-      </c>
-      <c r="C273" t="s">
-        <v>815</v>
       </c>
       <c r="D273" s="1"/>
     </row>
     <row r="274" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="B274" t="s">
         <v>817</v>
       </c>
-      <c r="B274" t="s">
+      <c r="C274" t="s">
         <v>818</v>
-      </c>
-      <c r="C274" t="s">
-        <v>819</v>
       </c>
       <c r="D274" s="1"/>
     </row>
     <row r="275" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="B275" t="s">
+        <v>821</v>
+      </c>
+      <c r="C275" t="s">
         <v>820</v>
-      </c>
-      <c r="B275" t="s">
-        <v>822</v>
-      </c>
-      <c r="C275" t="s">
-        <v>821</v>
       </c>
       <c r="D275" s="1"/>
     </row>
     <row r="276" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
+        <v>822</v>
+      </c>
+      <c r="B276" t="s">
+        <v>824</v>
+      </c>
+      <c r="C276" t="s">
         <v>823</v>
-      </c>
-      <c r="B276" t="s">
-        <v>825</v>
-      </c>
-      <c r="C276" t="s">
-        <v>824</v>
       </c>
       <c r="D276" s="1"/>
     </row>
     <row r="277" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B277" t="s">
         <v>826</v>
       </c>
-      <c r="B277" t="s">
+      <c r="C277" t="s">
         <v>827</v>
-      </c>
-      <c r="C277" t="s">
-        <v>828</v>
       </c>
       <c r="D277" s="1"/>
     </row>
     <row r="278" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="B278" t="s">
         <v>829</v>
       </c>
-      <c r="B278" t="s">
+      <c r="C278" t="s">
         <v>830</v>
-      </c>
-      <c r="C278" t="s">
-        <v>831</v>
       </c>
       <c r="D278" s="1"/>
     </row>
     <row r="279" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="B279" t="s">
         <v>832</v>
-      </c>
-      <c r="B279" t="s">
-        <v>833</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -9965,10 +9962,10 @@
     </row>
     <row r="280" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="B280" t="s">
         <v>834</v>
-      </c>
-      <c r="B280" t="s">
-        <v>835</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -9977,22 +9974,22 @@
     </row>
     <row r="281" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="B281" t="s">
+        <v>837</v>
+      </c>
+      <c r="C281" t="s">
         <v>836</v>
-      </c>
-      <c r="B281" t="s">
-        <v>838</v>
-      </c>
-      <c r="C281" t="s">
-        <v>837</v>
       </c>
       <c r="D281" s="1"/>
     </row>
     <row r="282" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="B282" t="s">
         <v>839</v>
-      </c>
-      <c r="B282" t="s">
-        <v>840</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -10001,10 +9998,10 @@
     </row>
     <row r="283" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="8" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B283" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -10013,34 +10010,34 @@
     </row>
     <row r="284" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B284" t="s">
         <v>842</v>
       </c>
-      <c r="B284" t="s">
+      <c r="C284" t="s">
         <v>843</v>
-      </c>
-      <c r="C284" t="s">
-        <v>844</v>
       </c>
       <c r="D284" s="1"/>
     </row>
     <row r="285" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="B285" t="s">
         <v>845</v>
       </c>
-      <c r="B285" t="s">
+      <c r="C285" t="s">
         <v>846</v>
-      </c>
-      <c r="C285" t="s">
-        <v>847</v>
       </c>
       <c r="D285" s="1"/>
     </row>
     <row r="286" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="B286" t="s">
         <v>848</v>
-      </c>
-      <c r="B286" t="s">
-        <v>849</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -10049,10 +10046,10 @@
     </row>
     <row r="287" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="B287" t="s">
         <v>850</v>
-      </c>
-      <c r="B287" t="s">
-        <v>851</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -10061,58 +10058,58 @@
     </row>
     <row r="288" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
-        <v>852</v>
-      </c>
-      <c r="B288" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C288" t="s">
         <v>1589</v>
-      </c>
-      <c r="C288" s="9" t="s">
-        <v>1590</v>
       </c>
       <c r="D288" s="1"/>
     </row>
     <row r="289" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="B289" t="s">
         <v>854</v>
       </c>
-      <c r="B289" t="s">
+      <c r="C289" t="s">
         <v>855</v>
-      </c>
-      <c r="C289" t="s">
-        <v>856</v>
       </c>
       <c r="D289" s="1"/>
     </row>
     <row r="290" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="B290" t="s">
         <v>857</v>
       </c>
-      <c r="B290" t="s">
+      <c r="C290" t="s">
         <v>858</v>
-      </c>
-      <c r="C290" t="s">
-        <v>859</v>
       </c>
       <c r="D290" s="1"/>
     </row>
     <row r="291" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B291" t="s">
         <v>860</v>
       </c>
-      <c r="B291" t="s">
+      <c r="C291" t="s">
         <v>861</v>
-      </c>
-      <c r="C291" t="s">
-        <v>862</v>
       </c>
       <c r="D291" s="1"/>
     </row>
     <row r="292" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="B292" t="s">
         <v>863</v>
-      </c>
-      <c r="B292" t="s">
-        <v>864</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -10121,82 +10118,82 @@
     </row>
     <row r="293" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="8" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B293" t="s">
+        <v>866</v>
+      </c>
+      <c r="C293" t="s">
         <v>867</v>
-      </c>
-      <c r="C293" t="s">
-        <v>868</v>
       </c>
       <c r="D293" s="1"/>
     </row>
     <row r="294" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="B294" t="s">
         <v>869</v>
       </c>
-      <c r="B294" t="s">
+      <c r="C294" t="s">
         <v>870</v>
-      </c>
-      <c r="C294" t="s">
-        <v>871</v>
       </c>
       <c r="D294" s="1"/>
     </row>
     <row r="295" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="B295" t="s">
         <v>872</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" t="s">
         <v>873</v>
-      </c>
-      <c r="C295" t="s">
-        <v>874</v>
       </c>
       <c r="D295" s="1"/>
     </row>
     <row r="296" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296" t="s">
         <v>875</v>
-      </c>
-      <c r="B296">
-        <v>0</v>
-      </c>
-      <c r="C296" t="s">
-        <v>876</v>
       </c>
       <c r="D296" s="1"/>
     </row>
     <row r="297" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="B297" t="s">
+        <v>878</v>
+      </c>
+      <c r="C297" t="s">
         <v>877</v>
-      </c>
-      <c r="B297" t="s">
-        <v>879</v>
-      </c>
-      <c r="C297" t="s">
-        <v>878</v>
       </c>
       <c r="D297" s="1"/>
     </row>
     <row r="298" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
+        <v>879</v>
+      </c>
+      <c r="B298" t="s">
         <v>880</v>
       </c>
-      <c r="B298" t="s">
+      <c r="C298" t="s">
         <v>881</v>
-      </c>
-      <c r="C298" t="s">
-        <v>882</v>
       </c>
       <c r="D298" s="1"/>
     </row>
     <row r="299" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="B299" t="s">
         <v>883</v>
-      </c>
-      <c r="B299" t="s">
-        <v>884</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -10205,34 +10202,34 @@
     </row>
     <row r="300" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="B300" t="s">
         <v>885</v>
       </c>
-      <c r="B300" t="s">
+      <c r="C300" t="s">
         <v>886</v>
-      </c>
-      <c r="C300" t="s">
-        <v>887</v>
       </c>
       <c r="D300" s="1"/>
     </row>
     <row r="301" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="8" t="s">
+        <v>887</v>
+      </c>
+      <c r="B301" t="s">
         <v>888</v>
       </c>
-      <c r="B301" t="s">
+      <c r="C301" t="s">
         <v>889</v>
-      </c>
-      <c r="C301" t="s">
-        <v>890</v>
       </c>
       <c r="D301" s="1"/>
     </row>
     <row r="302" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="B302" t="s">
         <v>891</v>
-      </c>
-      <c r="B302" t="s">
-        <v>892</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -10241,22 +10238,22 @@
     </row>
     <row r="303" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="B303" t="s">
+        <v>894</v>
+      </c>
+      <c r="C303" t="s">
         <v>893</v>
-      </c>
-      <c r="B303" t="s">
-        <v>895</v>
-      </c>
-      <c r="C303" t="s">
-        <v>894</v>
       </c>
       <c r="D303" s="1"/>
     </row>
     <row r="304" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="B304" t="s">
         <v>896</v>
-      </c>
-      <c r="B304" t="s">
-        <v>897</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -10265,10 +10262,10 @@
     </row>
     <row r="305" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="B305" t="s">
         <v>898</v>
-      </c>
-      <c r="B305" t="s">
-        <v>899</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -10277,22 +10274,22 @@
     </row>
     <row r="306" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="B306" t="s">
+        <v>902</v>
+      </c>
+      <c r="C306" t="s">
         <v>900</v>
-      </c>
-      <c r="B306" t="s">
-        <v>903</v>
-      </c>
-      <c r="C306" t="s">
-        <v>901</v>
       </c>
       <c r="D306" s="1"/>
     </row>
     <row r="307" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="8" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B307" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -10301,10 +10298,10 @@
     </row>
     <row r="308" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="B308" t="s">
         <v>905</v>
-      </c>
-      <c r="B308" t="s">
-        <v>906</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -10313,10 +10310,10 @@
     </row>
     <row r="309" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="B309" t="s">
         <v>907</v>
-      </c>
-      <c r="B309" t="s">
-        <v>908</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -10325,10 +10322,10 @@
     </row>
     <row r="310" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8" t="s">
+        <v>908</v>
+      </c>
+      <c r="B310" t="s">
         <v>909</v>
-      </c>
-      <c r="B310" t="s">
-        <v>910</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -10337,10 +10334,10 @@
     </row>
     <row r="311" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="B311" t="s">
         <v>911</v>
-      </c>
-      <c r="B311" t="s">
-        <v>912</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -10349,10 +10346,10 @@
     </row>
     <row r="312" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="8" t="s">
+        <v>912</v>
+      </c>
+      <c r="B312" t="s">
         <v>913</v>
-      </c>
-      <c r="B312" t="s">
-        <v>914</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -10361,10 +10358,10 @@
     </row>
     <row r="313" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="B313" t="s">
         <v>915</v>
-      </c>
-      <c r="B313" t="s">
-        <v>916</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -10373,10 +10370,10 @@
     </row>
     <row r="314" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
+        <v>916</v>
+      </c>
+      <c r="B314" t="s">
         <v>917</v>
-      </c>
-      <c r="B314" t="s">
-        <v>918</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -10385,10 +10382,10 @@
     </row>
     <row r="315" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
+        <v>918</v>
+      </c>
+      <c r="B315" t="s">
         <v>919</v>
-      </c>
-      <c r="B315" t="s">
-        <v>920</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -10397,10 +10394,10 @@
     </row>
     <row r="316" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="B316" t="s">
         <v>921</v>
-      </c>
-      <c r="B316" t="s">
-        <v>922</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -10409,10 +10406,10 @@
     </row>
     <row r="317" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="B317" t="s">
         <v>923</v>
-      </c>
-      <c r="B317" t="s">
-        <v>924</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -10421,10 +10418,10 @@
     </row>
     <row r="318" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="B318" t="s">
         <v>925</v>
-      </c>
-      <c r="B318" t="s">
-        <v>926</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -10433,10 +10430,10 @@
     </row>
     <row r="319" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="B319" t="s">
         <v>927</v>
-      </c>
-      <c r="B319" t="s">
-        <v>928</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -10445,10 +10442,10 @@
     </row>
     <row r="320" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="B320" t="s">
         <v>929</v>
-      </c>
-      <c r="B320" t="s">
-        <v>930</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -10457,10 +10454,10 @@
     </row>
     <row r="321" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="B321" t="s">
         <v>931</v>
-      </c>
-      <c r="B321" t="s">
-        <v>932</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -10469,10 +10466,10 @@
     </row>
     <row r="322" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
+        <v>932</v>
+      </c>
+      <c r="B322" t="s">
         <v>933</v>
-      </c>
-      <c r="B322" t="s">
-        <v>934</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -10481,10 +10478,10 @@
     </row>
     <row r="323" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="B323" t="s">
         <v>935</v>
-      </c>
-      <c r="B323" t="s">
-        <v>936</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -10493,10 +10490,10 @@
     </row>
     <row r="324" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="B324" t="s">
         <v>937</v>
-      </c>
-      <c r="B324" t="s">
-        <v>938</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -10505,10 +10502,10 @@
     </row>
     <row r="325" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="B325" t="s">
         <v>939</v>
-      </c>
-      <c r="B325" t="s">
-        <v>940</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -10517,10 +10514,10 @@
     </row>
     <row r="326" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
+        <v>940</v>
+      </c>
+      <c r="B326" t="s">
         <v>941</v>
-      </c>
-      <c r="B326" t="s">
-        <v>942</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -10529,10 +10526,10 @@
     </row>
     <row r="327" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="B327" t="s">
         <v>943</v>
-      </c>
-      <c r="B327" t="s">
-        <v>944</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -10541,142 +10538,142 @@
     </row>
     <row r="328" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="B328" t="s">
+        <v>946</v>
+      </c>
+      <c r="C328" t="s">
         <v>945</v>
-      </c>
-      <c r="B328" t="s">
-        <v>947</v>
-      </c>
-      <c r="C328" t="s">
-        <v>946</v>
       </c>
       <c r="D328" s="1"/>
     </row>
     <row r="329" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="B329" t="s">
         <v>948</v>
       </c>
-      <c r="B329" t="s">
+      <c r="C329" t="s">
         <v>949</v>
-      </c>
-      <c r="C329" t="s">
-        <v>950</v>
       </c>
       <c r="D329" s="1"/>
     </row>
     <row r="330" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="B330" t="s">
         <v>951</v>
       </c>
-      <c r="B330" t="s">
+      <c r="C330" t="s">
         <v>952</v>
-      </c>
-      <c r="C330" t="s">
-        <v>953</v>
       </c>
       <c r="D330" s="1"/>
     </row>
     <row r="331" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="8" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B331" t="s">
+        <v>953</v>
+      </c>
+      <c r="C331" t="s">
         <v>954</v>
-      </c>
-      <c r="C331" t="s">
-        <v>955</v>
       </c>
       <c r="D331" s="1"/>
     </row>
     <row r="332" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="B332" t="s">
+        <v>958</v>
+      </c>
+      <c r="C332" t="s">
         <v>957</v>
-      </c>
-      <c r="B332" t="s">
-        <v>959</v>
-      </c>
-      <c r="C332" t="s">
-        <v>958</v>
       </c>
       <c r="D332" s="1"/>
     </row>
     <row r="333" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="B333" t="s">
+        <v>961</v>
+      </c>
+      <c r="C333" t="s">
         <v>960</v>
-      </c>
-      <c r="B333" t="s">
-        <v>962</v>
-      </c>
-      <c r="C333" t="s">
-        <v>961</v>
       </c>
       <c r="D333" s="1"/>
     </row>
     <row r="334" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334" t="s">
         <v>963</v>
-      </c>
-      <c r="B334">
-        <v>0</v>
-      </c>
-      <c r="C334" t="s">
-        <v>964</v>
       </c>
       <c r="D334" s="1"/>
     </row>
     <row r="335" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="B335" t="s">
+        <v>966</v>
+      </c>
+      <c r="C335" t="s">
         <v>965</v>
-      </c>
-      <c r="B335" t="s">
-        <v>967</v>
-      </c>
-      <c r="C335" t="s">
-        <v>966</v>
       </c>
       <c r="D335" s="1"/>
     </row>
     <row r="336" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="B336" t="s">
         <v>968</v>
       </c>
-      <c r="B336" t="s">
+      <c r="C336" t="s">
         <v>969</v>
-      </c>
-      <c r="C336" t="s">
-        <v>970</v>
       </c>
       <c r="D336" s="1"/>
     </row>
     <row r="337" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="B337" t="s">
+        <v>972</v>
+      </c>
+      <c r="C337" t="s">
         <v>971</v>
-      </c>
-      <c r="B337" t="s">
-        <v>973</v>
-      </c>
-      <c r="C337" t="s">
-        <v>972</v>
       </c>
       <c r="D337" s="1"/>
     </row>
     <row r="338" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="B338" t="s">
+        <v>975</v>
+      </c>
+      <c r="C338" t="s">
         <v>974</v>
-      </c>
-      <c r="B338" t="s">
-        <v>976</v>
-      </c>
-      <c r="C338" t="s">
-        <v>975</v>
       </c>
       <c r="D338" s="1"/>
     </row>
     <row r="339" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="B339" t="s">
         <v>977</v>
-      </c>
-      <c r="B339" t="s">
-        <v>978</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -10685,10 +10682,10 @@
     </row>
     <row r="340" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="B340" t="s">
         <v>979</v>
-      </c>
-      <c r="B340" t="s">
-        <v>980</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -10697,130 +10694,130 @@
     </row>
     <row r="341" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="B341" t="s">
         <v>981</v>
       </c>
-      <c r="B341" t="s">
+      <c r="C341" t="s">
         <v>982</v>
-      </c>
-      <c r="C341" t="s">
-        <v>983</v>
       </c>
       <c r="D341" s="1"/>
     </row>
     <row r="342" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="B342" t="s">
         <v>984</v>
       </c>
-      <c r="B342" t="s">
+      <c r="C342" t="s">
         <v>985</v>
-      </c>
-      <c r="C342" t="s">
-        <v>986</v>
       </c>
       <c r="D342" s="1"/>
     </row>
     <row r="343" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="B343" t="s">
+        <v>988</v>
+      </c>
+      <c r="C343" t="s">
         <v>987</v>
-      </c>
-      <c r="B343" t="s">
-        <v>989</v>
-      </c>
-      <c r="C343" t="s">
-        <v>988</v>
       </c>
       <c r="D343" s="1"/>
     </row>
     <row r="344" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="B344" t="s">
+        <v>991</v>
+      </c>
+      <c r="C344" t="s">
         <v>990</v>
-      </c>
-      <c r="B344" t="s">
-        <v>992</v>
-      </c>
-      <c r="C344" t="s">
-        <v>991</v>
       </c>
       <c r="D344" s="1"/>
     </row>
     <row r="345" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="B345" t="s">
         <v>993</v>
       </c>
-      <c r="B345" t="s">
+      <c r="C345" t="s">
         <v>994</v>
-      </c>
-      <c r="C345" t="s">
-        <v>995</v>
       </c>
       <c r="D345" s="1"/>
     </row>
     <row r="346" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="B346" t="s">
         <v>996</v>
       </c>
-      <c r="B346" t="s">
+      <c r="C346" t="s">
         <v>997</v>
-      </c>
-      <c r="C346" t="s">
-        <v>998</v>
       </c>
       <c r="D346" s="1"/>
     </row>
     <row r="347" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="B347" t="s">
         <v>999</v>
       </c>
-      <c r="B347" t="s">
+      <c r="C347" t="s">
         <v>1000</v>
-      </c>
-      <c r="C347" t="s">
-        <v>1001</v>
       </c>
       <c r="D347" s="1"/>
     </row>
     <row r="348" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B348" t="s">
         <v>1002</v>
       </c>
-      <c r="B348" t="s">
+      <c r="C348" t="s">
         <v>1003</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1004</v>
       </c>
       <c r="D348" s="1"/>
     </row>
     <row r="349" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C349" t="s">
         <v>1005</v>
-      </c>
-      <c r="B349" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1006</v>
       </c>
       <c r="D349" s="1"/>
     </row>
     <row r="350" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C350" t="s">
         <v>1008</v>
-      </c>
-      <c r="B350" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1009</v>
       </c>
       <c r="D350" s="1"/>
     </row>
     <row r="351" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B351" t="s">
         <v>1011</v>
-      </c>
-      <c r="B351" t="s">
-        <v>1012</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -10829,10 +10826,10 @@
     </row>
     <row r="352" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B352" t="s">
         <v>1014</v>
-      </c>
-      <c r="B352" t="s">
-        <v>1015</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -10841,10 +10838,10 @@
     </row>
     <row r="353" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B353" t="s">
         <v>1016</v>
-      </c>
-      <c r="B353" t="s">
-        <v>1017</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -10853,10 +10850,10 @@
     </row>
     <row r="354" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B354" t="s">
         <v>1018</v>
-      </c>
-      <c r="B354" t="s">
-        <v>1019</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -10865,22 +10862,22 @@
     </row>
     <row r="355" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B355" t="s">
         <v>1020</v>
       </c>
-      <c r="B355" t="s">
+      <c r="C355" t="s">
         <v>1021</v>
-      </c>
-      <c r="C355" t="s">
-        <v>1022</v>
       </c>
       <c r="D355" s="1"/>
     </row>
     <row r="356" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B356" t="s">
         <v>1023</v>
-      </c>
-      <c r="B356" t="s">
-        <v>1024</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -10889,10 +10886,10 @@
     </row>
     <row r="357" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B357" t="s">
         <v>1025</v>
-      </c>
-      <c r="B357" t="s">
-        <v>1026</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -10901,10 +10898,10 @@
     </row>
     <row r="358" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B358" t="s">
         <v>1027</v>
-      </c>
-      <c r="B358" t="s">
-        <v>1028</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -10913,31 +10910,31 @@
     </row>
     <row r="359" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C359" t="s">
         <v>1029</v>
-      </c>
-      <c r="B359" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C359" t="s">
-        <v>1030</v>
       </c>
       <c r="D359" s="1"/>
     </row>
     <row r="360" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C360" t="s">
         <v>1032</v>
-      </c>
-      <c r="B360" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C360" t="s">
-        <v>1033</v>
       </c>
       <c r="D360" s="1"/>
     </row>
     <row r="361" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="8" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -10949,10 +10946,10 @@
     </row>
     <row r="362" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B362" t="s">
         <v>1036</v>
-      </c>
-      <c r="B362" t="s">
-        <v>1037</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -10961,142 +10958,142 @@
     </row>
     <row r="363" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B363" t="s">
         <v>1038</v>
       </c>
-      <c r="B363" t="s">
+      <c r="C363" t="s">
         <v>1039</v>
-      </c>
-      <c r="C363" t="s">
-        <v>1040</v>
       </c>
       <c r="D363" s="1"/>
     </row>
     <row r="364" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B364" t="s">
         <v>1041</v>
       </c>
-      <c r="B364" t="s">
+      <c r="C364" t="s">
         <v>1042</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1043</v>
       </c>
       <c r="D364" s="1"/>
     </row>
     <row r="365" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B365" t="s">
         <v>1044</v>
       </c>
-      <c r="B365" t="s">
+      <c r="C365" t="s">
         <v>1045</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1046</v>
       </c>
       <c r="D365" s="1"/>
     </row>
     <row r="366" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B366" t="s">
         <v>1047</v>
       </c>
-      <c r="B366" t="s">
+      <c r="C366" t="s">
         <v>1048</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1049</v>
       </c>
       <c r="D366" s="1"/>
     </row>
     <row r="367" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="8" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B367" t="s">
         <v>1050</v>
       </c>
-      <c r="B367" t="s">
+      <c r="C367" t="s">
         <v>1051</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1052</v>
       </c>
       <c r="D367" s="1"/>
     </row>
     <row r="368" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B368" t="s">
         <v>1053</v>
       </c>
-      <c r="B368" t="s">
+      <c r="C368" t="s">
         <v>1054</v>
-      </c>
-      <c r="C368" t="s">
-        <v>1055</v>
       </c>
       <c r="D368" s="1"/>
     </row>
     <row r="369" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C369" t="s">
         <v>1056</v>
-      </c>
-      <c r="B369" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C369" t="s">
-        <v>1057</v>
       </c>
       <c r="D369" s="1"/>
     </row>
     <row r="370" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B370" t="s">
         <v>1059</v>
       </c>
-      <c r="B370" t="s">
+      <c r="C370" t="s">
         <v>1060</v>
-      </c>
-      <c r="C370" t="s">
-        <v>1061</v>
       </c>
       <c r="D370" s="1"/>
     </row>
     <row r="371" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B371" t="s">
         <v>1062</v>
       </c>
-      <c r="B371" t="s">
+      <c r="C371" t="s">
         <v>1063</v>
-      </c>
-      <c r="C371" t="s">
-        <v>1064</v>
       </c>
       <c r="D371" s="1"/>
     </row>
     <row r="372" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B372" t="s">
         <v>1065</v>
       </c>
-      <c r="B372" t="s">
+      <c r="C372" t="s">
         <v>1066</v>
-      </c>
-      <c r="C372" t="s">
-        <v>1067</v>
       </c>
       <c r="D372" s="1"/>
     </row>
     <row r="373" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B373" t="s">
         <v>1068</v>
       </c>
-      <c r="B373" t="s">
+      <c r="C373" t="s">
         <v>1069</v>
-      </c>
-      <c r="C373" t="s">
-        <v>1070</v>
       </c>
       <c r="D373" s="1"/>
     </row>
     <row r="374" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B374" t="s">
         <v>1071</v>
-      </c>
-      <c r="B374" t="s">
-        <v>1072</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -11105,22 +11102,22 @@
     </row>
     <row r="375" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B375" t="s">
         <v>1073</v>
       </c>
-      <c r="B375" t="s">
+      <c r="C375" t="s">
         <v>1074</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1075</v>
       </c>
       <c r="D375" s="1"/>
     </row>
     <row r="376" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="8" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B376" t="s">
         <v>1076</v>
-      </c>
-      <c r="B376" t="s">
-        <v>1077</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -11129,10 +11126,10 @@
     </row>
     <row r="377" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B377" t="s">
         <v>1078</v>
-      </c>
-      <c r="B377" t="s">
-        <v>1079</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -11141,22 +11138,22 @@
     </row>
     <row r="378" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B378" t="s">
         <v>1080</v>
       </c>
-      <c r="B378" t="s">
+      <c r="C378" t="s">
         <v>1081</v>
-      </c>
-      <c r="C378" t="s">
-        <v>1082</v>
       </c>
       <c r="D378" s="1"/>
     </row>
     <row r="379" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B379" t="s">
         <v>1083</v>
-      </c>
-      <c r="B379" t="s">
-        <v>1084</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -11165,22 +11162,22 @@
     </row>
     <row r="380" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380" t="s">
         <v>1085</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380" t="s">
-        <v>1086</v>
       </c>
       <c r="D380" s="1"/>
     </row>
     <row r="381" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B381" t="s">
         <v>1087</v>
-      </c>
-      <c r="B381" t="s">
-        <v>1088</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -11189,43 +11186,43 @@
     </row>
     <row r="382" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="8" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B382" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C382" t="s">
         <v>1091</v>
-      </c>
-      <c r="C382" t="s">
-        <v>1092</v>
       </c>
       <c r="D382" s="1"/>
     </row>
     <row r="383" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="8" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B383">
         <v>0</v>
       </c>
       <c r="C383" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D383" s="1"/>
     </row>
     <row r="384" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="8" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384" t="s">
         <v>1094</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384" t="s">
-        <v>1095</v>
       </c>
       <c r="D384" s="1"/>
     </row>
     <row r="385" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="8" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -11237,22 +11234,22 @@
     </row>
     <row r="386" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="8" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B386" t="s">
         <v>1097</v>
       </c>
-      <c r="B386" t="s">
+      <c r="C386" t="s">
         <v>1098</v>
-      </c>
-      <c r="C386" t="s">
-        <v>1099</v>
       </c>
       <c r="D386" s="1"/>
     </row>
     <row r="387" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="8" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B387" t="s">
         <v>1100</v>
-      </c>
-      <c r="B387" t="s">
-        <v>1101</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -11261,70 +11258,70 @@
     </row>
     <row r="388" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388" t="s">
         <v>1102</v>
-      </c>
-      <c r="B388">
-        <v>0</v>
-      </c>
-      <c r="C388" t="s">
-        <v>1103</v>
       </c>
       <c r="D388" s="1"/>
     </row>
     <row r="389" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B389" t="s">
         <v>1104</v>
       </c>
-      <c r="B389" t="s">
+      <c r="C389" t="s">
         <v>1105</v>
-      </c>
-      <c r="C389" t="s">
-        <v>1106</v>
       </c>
       <c r="D389" s="1"/>
     </row>
     <row r="390" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390" t="s">
         <v>1107</v>
-      </c>
-      <c r="B390">
-        <v>0</v>
-      </c>
-      <c r="C390" t="s">
-        <v>1108</v>
       </c>
       <c r="D390" s="1"/>
     </row>
     <row r="391" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B391" t="s">
         <v>1109</v>
       </c>
-      <c r="B391" t="s">
+      <c r="C391" t="s">
         <v>1110</v>
-      </c>
-      <c r="C391" t="s">
-        <v>1111</v>
       </c>
       <c r="D391" s="1"/>
     </row>
     <row r="392" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B392" t="s">
         <v>1112</v>
       </c>
-      <c r="B392" t="s">
+      <c r="C392" t="s">
         <v>1113</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1114</v>
       </c>
       <c r="D392" s="1"/>
     </row>
     <row r="393" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="8" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B393" t="s">
         <v>1115</v>
-      </c>
-      <c r="B393" t="s">
-        <v>1116</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -11333,46 +11330,46 @@
     </row>
     <row r="394" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="8" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B394" t="s">
         <v>1117</v>
       </c>
-      <c r="B394" t="s">
+      <c r="C394" t="s">
         <v>1118</v>
-      </c>
-      <c r="C394" t="s">
-        <v>1119</v>
       </c>
       <c r="D394" s="1"/>
     </row>
     <row r="395" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B395" t="s">
         <v>1120</v>
       </c>
-      <c r="B395" t="s">
+      <c r="C395" t="s">
         <v>1121</v>
-      </c>
-      <c r="C395" t="s">
-        <v>1122</v>
       </c>
       <c r="D395" s="1"/>
     </row>
     <row r="396" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C396" t="s">
         <v>1123</v>
-      </c>
-      <c r="B396" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C396" t="s">
-        <v>1124</v>
       </c>
       <c r="D396" s="1"/>
     </row>
     <row r="397" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B397" t="s">
         <v>1126</v>
-      </c>
-      <c r="B397" t="s">
-        <v>1127</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -11381,10 +11378,10 @@
     </row>
     <row r="398" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="8" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B398" t="s">
         <v>1128</v>
-      </c>
-      <c r="B398" t="s">
-        <v>1129</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -11393,34 +11390,34 @@
     </row>
     <row r="399" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C399" t="s">
         <v>1130</v>
-      </c>
-      <c r="B399" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C399" t="s">
-        <v>1131</v>
       </c>
       <c r="D399" s="1"/>
     </row>
     <row r="400" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B400" t="s">
         <v>1133</v>
       </c>
-      <c r="B400" t="s">
+      <c r="C400" t="s">
         <v>1134</v>
-      </c>
-      <c r="C400" t="s">
-        <v>1135</v>
       </c>
       <c r="D400" s="1"/>
     </row>
     <row r="401" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="8" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B401" t="s">
         <v>1136</v>
-      </c>
-      <c r="B401" t="s">
-        <v>1137</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -11429,190 +11426,190 @@
     </row>
     <row r="402" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="8" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B402" t="s">
         <v>1138</v>
       </c>
-      <c r="B402" t="s">
+      <c r="C402" t="s">
         <v>1139</v>
-      </c>
-      <c r="C402" t="s">
-        <v>1140</v>
       </c>
       <c r="D402" s="1"/>
     </row>
     <row r="403" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="8" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B403" t="s">
         <v>1141</v>
       </c>
-      <c r="B403" t="s">
+      <c r="C403" t="s">
         <v>1142</v>
-      </c>
-      <c r="C403" t="s">
-        <v>1143</v>
       </c>
       <c r="D403" s="1"/>
     </row>
     <row r="404" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B404" t="s">
         <v>1144</v>
       </c>
-      <c r="B404" t="s">
+      <c r="C404" t="s">
         <v>1145</v>
-      </c>
-      <c r="C404" t="s">
-        <v>1146</v>
       </c>
       <c r="D404" s="1"/>
     </row>
     <row r="405" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="8" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B405" t="s">
         <v>1147</v>
       </c>
-      <c r="B405" t="s">
+      <c r="C405" t="s">
         <v>1148</v>
-      </c>
-      <c r="C405" t="s">
-        <v>1149</v>
       </c>
       <c r="D405" s="1"/>
     </row>
     <row r="406" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C406" t="s">
         <v>1150</v>
-      </c>
-      <c r="B406" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1151</v>
       </c>
       <c r="D406" s="1"/>
     </row>
     <row r="407" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="8" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B407" t="s">
         <v>1153</v>
       </c>
-      <c r="B407" t="s">
+      <c r="C407" t="s">
         <v>1154</v>
-      </c>
-      <c r="C407" t="s">
-        <v>1155</v>
       </c>
       <c r="D407" s="1"/>
     </row>
     <row r="408" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="8" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B408" t="s">
         <v>1156</v>
       </c>
-      <c r="B408" t="s">
+      <c r="C408" t="s">
         <v>1157</v>
-      </c>
-      <c r="C408" t="s">
-        <v>1158</v>
       </c>
       <c r="D408" s="1"/>
     </row>
     <row r="409" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="8" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B409" t="s">
         <v>1159</v>
       </c>
-      <c r="B409" t="s">
-        <v>1160</v>
-      </c>
       <c r="C409" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D409" s="1"/>
     </row>
     <row r="410" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="8" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B410" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C410" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D410" s="1"/>
     </row>
     <row r="411" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="8" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C411" t="s">
         <v>1162</v>
-      </c>
-      <c r="B411" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C411" t="s">
-        <v>1163</v>
       </c>
       <c r="D411" s="1"/>
     </row>
     <row r="412" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="8" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C412" t="s">
         <v>1165</v>
-      </c>
-      <c r="B412" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C412" t="s">
-        <v>1166</v>
       </c>
       <c r="D412" s="1"/>
     </row>
     <row r="413" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B413" t="s">
         <v>1168</v>
       </c>
-      <c r="B413" t="s">
+      <c r="C413" t="s">
         <v>1169</v>
-      </c>
-      <c r="C413" t="s">
-        <v>1170</v>
       </c>
       <c r="D413" s="1"/>
     </row>
     <row r="414" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B414" t="s">
         <v>1171</v>
       </c>
-      <c r="B414" t="s">
+      <c r="C414" t="s">
         <v>1172</v>
-      </c>
-      <c r="C414" t="s">
-        <v>1173</v>
       </c>
       <c r="D414" s="1"/>
     </row>
     <row r="415" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B415" t="s">
         <v>1174</v>
       </c>
-      <c r="B415" t="s">
+      <c r="C415" t="s">
         <v>1175</v>
-      </c>
-      <c r="C415" t="s">
-        <v>1176</v>
       </c>
       <c r="D415" s="1"/>
     </row>
     <row r="416" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B416" t="s">
         <v>1177</v>
       </c>
-      <c r="B416" t="s">
+      <c r="C416" t="s">
         <v>1178</v>
-      </c>
-      <c r="C416" t="s">
-        <v>1179</v>
       </c>
       <c r="D416" s="1"/>
     </row>
     <row r="417" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="8" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B417" t="s">
         <v>1180</v>
-      </c>
-      <c r="B417" t="s">
-        <v>1181</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -11621,10 +11618,10 @@
     </row>
     <row r="418" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B418" t="s">
         <v>1182</v>
-      </c>
-      <c r="B418" t="s">
-        <v>1183</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -11633,10 +11630,10 @@
     </row>
     <row r="419" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="8" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B419" t="s">
         <v>1184</v>
-      </c>
-      <c r="B419" t="s">
-        <v>1185</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -11645,82 +11642,82 @@
     </row>
     <row r="420" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C420" t="s">
         <v>1186</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C420" t="s">
-        <v>1187</v>
       </c>
       <c r="D420" s="1"/>
     </row>
     <row r="421" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C421" t="s">
         <v>1188</v>
-      </c>
-      <c r="B421" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C421" t="s">
-        <v>1189</v>
       </c>
       <c r="D421" s="1"/>
     </row>
     <row r="422" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B422" t="s">
         <v>1190</v>
       </c>
-      <c r="B422" t="s">
+      <c r="C422" t="s">
         <v>1191</v>
-      </c>
-      <c r="C422" t="s">
-        <v>1192</v>
       </c>
       <c r="D422" s="1"/>
     </row>
     <row r="423" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B423" t="s">
         <v>1193</v>
       </c>
-      <c r="B423" t="s">
+      <c r="C423" t="s">
         <v>1194</v>
-      </c>
-      <c r="C423" t="s">
-        <v>1195</v>
       </c>
       <c r="D423" s="1"/>
     </row>
     <row r="424" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="8" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B424" t="s">
         <v>1196</v>
       </c>
-      <c r="B424" t="s">
+      <c r="C424" t="s">
         <v>1197</v>
-      </c>
-      <c r="C424" t="s">
-        <v>1198</v>
       </c>
       <c r="D424" s="1"/>
     </row>
     <row r="425" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="8" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B425" t="s">
         <v>1199</v>
       </c>
-      <c r="B425" t="s">
+      <c r="C425" t="s">
         <v>1200</v>
-      </c>
-      <c r="C425" t="s">
-        <v>1201</v>
       </c>
       <c r="D425" s="1"/>
     </row>
     <row r="426" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="8" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B426" t="s">
         <v>1202</v>
-      </c>
-      <c r="B426" t="s">
-        <v>1203</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -11729,10 +11726,10 @@
     </row>
     <row r="427" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="8" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B427" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -11741,82 +11738,82 @@
     </row>
     <row r="428" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="8" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B428" s="9" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C428" s="9" t="s">
-        <v>1585</v>
+        <v>1204</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C428" t="s">
+        <v>1584</v>
       </c>
       <c r="D428" s="1"/>
     </row>
     <row r="429" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="8" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B429" t="s">
         <v>1206</v>
       </c>
-      <c r="B429" t="s">
+      <c r="C429" t="s">
         <v>1207</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1208</v>
       </c>
       <c r="D429" s="1"/>
     </row>
     <row r="430" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C430" t="s">
         <v>1209</v>
-      </c>
-      <c r="B430" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C430" t="s">
-        <v>1210</v>
       </c>
       <c r="D430" s="1"/>
     </row>
     <row r="431" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B431" t="s">
         <v>1212</v>
       </c>
-      <c r="B431" t="s">
+      <c r="C431" t="s">
         <v>1213</v>
-      </c>
-      <c r="C431" t="s">
-        <v>1214</v>
       </c>
       <c r="D431" s="1"/>
     </row>
     <row r="432" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="8" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C432" t="s">
         <v>1215</v>
-      </c>
-      <c r="B432" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C432" t="s">
-        <v>1216</v>
       </c>
       <c r="D432" s="1"/>
     </row>
     <row r="433" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B433" t="s">
         <v>1218</v>
       </c>
-      <c r="B433" t="s">
+      <c r="C433" t="s">
         <v>1219</v>
-      </c>
-      <c r="C433" t="s">
-        <v>1220</v>
       </c>
       <c r="D433" s="1"/>
     </row>
     <row r="434" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B434" t="s">
         <v>1221</v>
-      </c>
-      <c r="B434" t="s">
-        <v>1222</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -11825,10 +11822,10 @@
     </row>
     <row r="435" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="8" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B435" t="s">
         <v>1223</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1224</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -11837,10 +11834,10 @@
     </row>
     <row r="436" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B436" t="s">
         <v>1225</v>
-      </c>
-      <c r="B436" t="s">
-        <v>1226</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -11849,22 +11846,22 @@
     </row>
     <row r="437" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="8" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B437" t="s">
         <v>1227</v>
       </c>
-      <c r="B437" t="s">
+      <c r="C437" t="s">
         <v>1228</v>
-      </c>
-      <c r="C437" t="s">
-        <v>1229</v>
       </c>
       <c r="D437" s="1"/>
     </row>
     <row r="438" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B438" t="s">
         <v>1230</v>
-      </c>
-      <c r="B438" t="s">
-        <v>1231</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -11873,34 +11870,34 @@
     </row>
     <row r="439" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="8" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B439" t="s">
         <v>1232</v>
       </c>
-      <c r="B439" t="s">
+      <c r="C439" s="1" t="s">
         <v>1233</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>1234</v>
       </c>
       <c r="D439" s="1"/>
     </row>
     <row r="440" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="8" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B440" t="s">
         <v>1235</v>
       </c>
-      <c r="B440" t="s">
+      <c r="C440" t="s">
         <v>1236</v>
-      </c>
-      <c r="C440" t="s">
-        <v>1237</v>
       </c>
       <c r="D440" s="1"/>
     </row>
     <row r="441" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B441" t="s">
         <v>1238</v>
-      </c>
-      <c r="B441" t="s">
-        <v>1239</v>
       </c>
       <c r="C441">
         <v>0</v>
@@ -11909,70 +11906,70 @@
     </row>
     <row r="442" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B442" t="s">
         <v>1240</v>
       </c>
-      <c r="B442" t="s">
+      <c r="C442" t="s">
         <v>1241</v>
-      </c>
-      <c r="C442" t="s">
-        <v>1242</v>
       </c>
       <c r="D442" s="1"/>
     </row>
     <row r="443" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="8" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B443" t="s">
         <v>1243</v>
       </c>
-      <c r="B443" t="s">
+      <c r="C443" t="s">
         <v>1244</v>
-      </c>
-      <c r="C443" t="s">
-        <v>1245</v>
       </c>
       <c r="D443" s="1"/>
     </row>
     <row r="444" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B444" t="s">
         <v>1246</v>
       </c>
-      <c r="B444" t="s">
+      <c r="C444" t="s">
         <v>1247</v>
-      </c>
-      <c r="C444" t="s">
-        <v>1248</v>
       </c>
       <c r="D444" s="1"/>
     </row>
     <row r="445" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B445" t="s">
         <v>1249</v>
       </c>
-      <c r="B445" t="s">
+      <c r="C445" t="s">
         <v>1250</v>
-      </c>
-      <c r="C445" t="s">
-        <v>1251</v>
       </c>
       <c r="D445" s="1"/>
     </row>
     <row r="446" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C446" t="s">
         <v>1252</v>
-      </c>
-      <c r="B446" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C446" t="s">
-        <v>1253</v>
       </c>
       <c r="D446" s="1"/>
     </row>
     <row r="447" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B447" t="s">
         <v>1255</v>
-      </c>
-      <c r="B447" t="s">
-        <v>1256</v>
       </c>
       <c r="C447">
         <v>0</v>
@@ -11981,10 +11978,10 @@
     </row>
     <row r="448" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="8" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B448" t="s">
         <v>1257</v>
-      </c>
-      <c r="B448" t="s">
-        <v>1258</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -11993,10 +11990,10 @@
     </row>
     <row r="449" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B449" t="s">
         <v>1259</v>
-      </c>
-      <c r="B449" t="s">
-        <v>1260</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -12005,166 +12002,166 @@
     </row>
     <row r="450" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C450" t="s">
         <v>1261</v>
-      </c>
-      <c r="B450" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C450" t="s">
-        <v>1262</v>
       </c>
       <c r="D450" s="1"/>
     </row>
     <row r="451" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C451" t="s">
         <v>1263</v>
-      </c>
-      <c r="B451" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C451" t="s">
-        <v>1264</v>
       </c>
       <c r="D451" s="1"/>
     </row>
     <row r="452" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C452" t="s">
         <v>1266</v>
-      </c>
-      <c r="B452" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C452" t="s">
-        <v>1267</v>
       </c>
       <c r="D452" s="1"/>
     </row>
     <row r="453" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C453" t="s">
         <v>1269</v>
-      </c>
-      <c r="B453" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C453" t="s">
-        <v>1270</v>
       </c>
       <c r="D453" s="1"/>
     </row>
     <row r="454" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B454" t="s">
         <v>1272</v>
       </c>
-      <c r="B454" t="s">
+      <c r="C454" t="s">
         <v>1273</v>
-      </c>
-      <c r="C454" t="s">
-        <v>1274</v>
       </c>
       <c r="D454" s="1"/>
     </row>
     <row r="455" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B455" t="s">
         <v>1275</v>
       </c>
-      <c r="B455" t="s">
+      <c r="C455" t="s">
         <v>1276</v>
-      </c>
-      <c r="C455" t="s">
-        <v>1277</v>
       </c>
       <c r="D455" s="1"/>
     </row>
     <row r="456" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B456" t="s">
         <v>1278</v>
       </c>
-      <c r="B456" t="s">
+      <c r="C456" t="s">
         <v>1279</v>
-      </c>
-      <c r="C456" t="s">
-        <v>1280</v>
       </c>
       <c r="D456" s="1"/>
     </row>
     <row r="457" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B457" t="s">
         <v>1281</v>
       </c>
-      <c r="B457" t="s">
+      <c r="C457" t="s">
         <v>1282</v>
-      </c>
-      <c r="C457" t="s">
-        <v>1283</v>
       </c>
       <c r="D457" s="1"/>
     </row>
     <row r="458" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B458" t="s">
         <v>1284</v>
       </c>
-      <c r="B458" t="s">
+      <c r="C458" t="s">
         <v>1285</v>
-      </c>
-      <c r="C458" t="s">
-        <v>1286</v>
       </c>
       <c r="D458" s="1"/>
     </row>
     <row r="459" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B459" t="s">
         <v>1287</v>
       </c>
-      <c r="B459" t="s">
+      <c r="C459" t="s">
         <v>1288</v>
-      </c>
-      <c r="C459" t="s">
-        <v>1289</v>
       </c>
       <c r="D459" s="1"/>
     </row>
     <row r="460" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="8" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B460" t="s">
         <v>1290</v>
       </c>
-      <c r="B460" t="s">
+      <c r="C460" t="s">
         <v>1291</v>
-      </c>
-      <c r="C460" t="s">
-        <v>1292</v>
       </c>
       <c r="D460" s="1"/>
     </row>
     <row r="461" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="8" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C461" t="s">
         <v>1293</v>
-      </c>
-      <c r="B461" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C461" t="s">
-        <v>1294</v>
       </c>
       <c r="D461" s="1"/>
     </row>
     <row r="462" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B462" t="s">
         <v>1296</v>
       </c>
-      <c r="B462" t="s">
+      <c r="C462" t="s">
         <v>1297</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1298</v>
       </c>
       <c r="D462" s="1"/>
     </row>
     <row r="463" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="8" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B463" t="s">
         <v>1299</v>
-      </c>
-      <c r="B463" t="s">
-        <v>1300</v>
       </c>
       <c r="C463">
         <v>0</v>
@@ -12173,22 +12170,22 @@
     </row>
     <row r="464" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B464" t="s">
         <v>1301</v>
       </c>
-      <c r="B464" t="s">
-        <v>1302</v>
-      </c>
       <c r="C464" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D464" s="1"/>
     </row>
     <row r="465" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B465" t="s">
         <v>1303</v>
-      </c>
-      <c r="B465" t="s">
-        <v>1304</v>
       </c>
       <c r="C465">
         <v>0</v>
@@ -12197,118 +12194,118 @@
     </row>
     <row r="466" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B466" t="s">
         <v>1305</v>
       </c>
-      <c r="B466" t="s">
+      <c r="C466" t="s">
         <v>1306</v>
-      </c>
-      <c r="C466" t="s">
-        <v>1307</v>
       </c>
       <c r="D466" s="1"/>
     </row>
     <row r="467" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="8" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B467" t="s">
         <v>1308</v>
       </c>
-      <c r="B467" t="s">
+      <c r="C467" t="s">
         <v>1309</v>
-      </c>
-      <c r="C467" t="s">
-        <v>1310</v>
       </c>
       <c r="D467" s="1"/>
     </row>
     <row r="468" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="8" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B468" t="s">
         <v>1311</v>
       </c>
-      <c r="B468" t="s">
+      <c r="C468" t="s">
         <v>1312</v>
-      </c>
-      <c r="C468" t="s">
-        <v>1313</v>
       </c>
       <c r="D468" s="1"/>
     </row>
     <row r="469" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="8" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B469" t="s">
         <v>1314</v>
       </c>
-      <c r="B469" t="s">
+      <c r="C469" t="s">
         <v>1315</v>
-      </c>
-      <c r="C469" t="s">
-        <v>1316</v>
       </c>
       <c r="D469" s="1"/>
     </row>
     <row r="470" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B470" t="s">
         <v>1317</v>
       </c>
-      <c r="B470" t="s">
+      <c r="C470" t="s">
         <v>1318</v>
-      </c>
-      <c r="C470" t="s">
-        <v>1319</v>
       </c>
       <c r="D470" s="1"/>
     </row>
     <row r="471" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B471" t="s">
         <v>1320</v>
       </c>
-      <c r="B471" t="s">
+      <c r="C471" t="s">
         <v>1321</v>
-      </c>
-      <c r="C471" t="s">
-        <v>1322</v>
       </c>
       <c r="D471" s="1"/>
     </row>
     <row r="472" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B472" t="s">
         <v>1323</v>
       </c>
-      <c r="B472" t="s">
+      <c r="C472" t="s">
         <v>1324</v>
-      </c>
-      <c r="C472" t="s">
-        <v>1325</v>
       </c>
       <c r="D472" s="1"/>
     </row>
     <row r="473" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B473" t="s">
         <v>1326</v>
       </c>
-      <c r="B473" t="s">
+      <c r="C473" t="s">
         <v>1327</v>
-      </c>
-      <c r="C473" t="s">
-        <v>1328</v>
       </c>
       <c r="D473" s="1"/>
     </row>
     <row r="474" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="8" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B474" t="s">
         <v>1329</v>
       </c>
-      <c r="B474" t="s">
+      <c r="C474" t="s">
         <v>1330</v>
-      </c>
-      <c r="C474" t="s">
-        <v>1331</v>
       </c>
       <c r="D474" s="1"/>
     </row>
     <row r="475" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="8" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B475" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C475">
         <v>0</v>
@@ -12317,10 +12314,10 @@
     </row>
     <row r="476" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="8" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B476" t="s">
         <v>1334</v>
-      </c>
-      <c r="B476" t="s">
-        <v>1335</v>
       </c>
       <c r="C476">
         <v>0</v>
@@ -12329,34 +12326,34 @@
     </row>
     <row r="477" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B477" t="s">
         <v>1336</v>
       </c>
-      <c r="B477" t="s">
+      <c r="C477" t="s">
         <v>1337</v>
-      </c>
-      <c r="C477" t="s">
-        <v>1338</v>
       </c>
       <c r="D477" s="1"/>
     </row>
     <row r="478" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="8" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C478" t="s">
         <v>1339</v>
-      </c>
-      <c r="B478" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C478" t="s">
-        <v>1340</v>
       </c>
       <c r="D478" s="1"/>
     </row>
     <row r="479" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B479" t="s">
         <v>1342</v>
-      </c>
-      <c r="B479" t="s">
-        <v>1343</v>
       </c>
       <c r="C479" s="7">
         <v>0</v>
@@ -12365,142 +12362,142 @@
     </row>
     <row r="480" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="8" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C480" t="s">
         <v>1344</v>
-      </c>
-      <c r="B480" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C480" t="s">
-        <v>1345</v>
       </c>
       <c r="D480" s="1"/>
     </row>
     <row r="481" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="8" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B481" t="s">
         <v>1347</v>
       </c>
-      <c r="B481" t="s">
+      <c r="C481" t="s">
         <v>1348</v>
-      </c>
-      <c r="C481" t="s">
-        <v>1349</v>
       </c>
       <c r="D481" s="1"/>
     </row>
     <row r="482" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="8" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B482" t="s">
         <v>1350</v>
       </c>
-      <c r="B482" t="s">
+      <c r="C482" t="s">
         <v>1351</v>
-      </c>
-      <c r="C482" t="s">
-        <v>1352</v>
       </c>
       <c r="D482" s="1"/>
     </row>
     <row r="483" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="8" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C483" t="s">
         <v>1353</v>
-      </c>
-      <c r="B483" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C483" t="s">
-        <v>1354</v>
       </c>
       <c r="D483" s="1"/>
     </row>
     <row r="484" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="8" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B484" t="s">
         <v>1355</v>
       </c>
-      <c r="B484" t="s">
+      <c r="C484" t="s">
         <v>1356</v>
-      </c>
-      <c r="C484" t="s">
-        <v>1357</v>
       </c>
       <c r="D484" s="1"/>
     </row>
     <row r="485" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="8" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B485" t="s">
         <v>1358</v>
       </c>
-      <c r="B485" t="s">
+      <c r="C485" t="s">
         <v>1359</v>
-      </c>
-      <c r="C485" t="s">
-        <v>1360</v>
       </c>
       <c r="D485" s="1"/>
     </row>
     <row r="486" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="8" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B486" t="s">
+        <v>678</v>
+      </c>
+      <c r="C486" t="s">
         <v>1361</v>
-      </c>
-      <c r="B486" t="s">
-        <v>679</v>
-      </c>
-      <c r="C486" t="s">
-        <v>1362</v>
       </c>
       <c r="D486" s="1"/>
     </row>
     <row r="487" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="8" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B487" t="s">
         <v>1363</v>
       </c>
-      <c r="B487" t="s">
+      <c r="C487" t="s">
         <v>1364</v>
-      </c>
-      <c r="C487" t="s">
-        <v>1365</v>
       </c>
       <c r="D487" s="1"/>
     </row>
     <row r="488" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B488" t="s">
         <v>1366</v>
       </c>
-      <c r="B488" t="s">
+      <c r="C488" t="s">
         <v>1367</v>
-      </c>
-      <c r="C488" t="s">
-        <v>1368</v>
       </c>
       <c r="D488" s="1"/>
     </row>
     <row r="489" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B489" t="s">
         <v>1369</v>
       </c>
-      <c r="B489" t="s">
+      <c r="C489" t="s">
         <v>1370</v>
-      </c>
-      <c r="C489" t="s">
-        <v>1371</v>
       </c>
       <c r="D489" s="1"/>
     </row>
     <row r="490" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="8" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B490" t="s">
         <v>1372</v>
       </c>
-      <c r="B490" t="s">
+      <c r="C490" t="s">
         <v>1373</v>
-      </c>
-      <c r="C490" t="s">
-        <v>1374</v>
       </c>
       <c r="D490" s="1"/>
     </row>
     <row r="491" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B491" t="s">
         <v>1375</v>
-      </c>
-      <c r="B491" t="s">
-        <v>1376</v>
       </c>
       <c r="C491">
         <v>0</v>
@@ -12509,22 +12506,22 @@
     </row>
     <row r="492" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="8" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B492" t="s">
         <v>1377</v>
       </c>
-      <c r="B492" t="s">
+      <c r="C492" t="s">
         <v>1378</v>
-      </c>
-      <c r="C492" t="s">
-        <v>1379</v>
       </c>
       <c r="D492" s="1"/>
     </row>
     <row r="493" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="8" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B493" t="s">
         <v>1380</v>
-      </c>
-      <c r="B493" t="s">
-        <v>1381</v>
       </c>
       <c r="C493">
         <v>0</v>
@@ -12533,58 +12530,58 @@
     </row>
     <row r="494" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="8" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B494" t="s">
         <v>1382</v>
       </c>
-      <c r="B494" t="s">
+      <c r="C494" t="s">
         <v>1383</v>
-      </c>
-      <c r="C494" t="s">
-        <v>1384</v>
       </c>
       <c r="D494" s="1"/>
     </row>
     <row r="495" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="8" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B495" t="s">
         <v>1385</v>
       </c>
-      <c r="B495" t="s">
+      <c r="C495" t="s">
         <v>1386</v>
-      </c>
-      <c r="C495" t="s">
-        <v>1387</v>
       </c>
       <c r="D495" s="1"/>
     </row>
     <row r="496" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="8" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+      <c r="C496" t="s">
         <v>1388</v>
-      </c>
-      <c r="B496">
-        <v>0</v>
-      </c>
-      <c r="C496" t="s">
-        <v>1389</v>
       </c>
       <c r="D496" s="1"/>
     </row>
     <row r="497" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="8" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B497" t="s">
         <v>1390</v>
       </c>
-      <c r="B497" t="s">
+      <c r="C497" t="s">
         <v>1391</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1392</v>
       </c>
       <c r="D497" s="1"/>
     </row>
     <row r="498" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="8" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B498" t="s">
         <v>1393</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1394</v>
       </c>
       <c r="C498">
         <v>0</v>
@@ -12593,10 +12590,10 @@
     </row>
     <row r="499" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="8" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B499" t="s">
         <v>1395</v>
-      </c>
-      <c r="B499" t="s">
-        <v>1396</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -12605,34 +12602,34 @@
     </row>
     <row r="500" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="8" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C500" t="s">
         <v>1397</v>
-      </c>
-      <c r="B500" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C500" t="s">
-        <v>1398</v>
       </c>
       <c r="D500" s="1"/>
     </row>
     <row r="501" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="8" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C501" t="s">
         <v>1400</v>
-      </c>
-      <c r="B501" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C501" t="s">
-        <v>1401</v>
       </c>
       <c r="D501" s="1"/>
     </row>
     <row r="502" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="8" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B502" t="s">
         <v>1403</v>
-      </c>
-      <c r="B502" t="s">
-        <v>1404</v>
       </c>
       <c r="C502">
         <v>0</v>
@@ -12641,10 +12638,10 @@
     </row>
     <row r="503" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B503" t="s">
         <v>1405</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1406</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -12653,10 +12650,10 @@
     </row>
     <row r="504" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="8" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B504" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -12665,22 +12662,22 @@
     </row>
     <row r="505" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="8" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B505" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C505" t="s">
         <v>1410</v>
-      </c>
-      <c r="C505" t="s">
-        <v>1411</v>
       </c>
       <c r="D505" s="1"/>
     </row>
     <row r="506" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B506" t="s">
         <v>1412</v>
-      </c>
-      <c r="B506" t="s">
-        <v>1413</v>
       </c>
       <c r="C506">
         <v>0</v>
@@ -12689,202 +12686,202 @@
     </row>
     <row r="507" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="8" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B507" t="s">
         <v>1414</v>
       </c>
-      <c r="B507" t="s">
+      <c r="C507" t="s">
         <v>1415</v>
-      </c>
-      <c r="C507" t="s">
-        <v>1416</v>
       </c>
       <c r="D507" s="1"/>
     </row>
     <row r="508" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="8" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C508" t="s">
         <v>1417</v>
-      </c>
-      <c r="B508" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1418</v>
       </c>
       <c r="D508" s="1"/>
     </row>
     <row r="509" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B509" t="s">
         <v>1420</v>
       </c>
-      <c r="B509" t="s">
+      <c r="C509" t="s">
         <v>1421</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1422</v>
       </c>
       <c r="D509" s="1"/>
     </row>
     <row r="510" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="8" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B510" t="s">
         <v>1423</v>
       </c>
-      <c r="B510" t="s">
+      <c r="C510" t="s">
         <v>1424</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1425</v>
       </c>
       <c r="D510" s="1"/>
     </row>
     <row r="511" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="8" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B511" t="s">
         <v>1426</v>
       </c>
-      <c r="B511" t="s">
+      <c r="C511" t="s">
         <v>1427</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1428</v>
       </c>
       <c r="D511" s="1"/>
     </row>
     <row r="512" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B512" t="s">
         <v>1429</v>
       </c>
-      <c r="B512" t="s">
+      <c r="C512" t="s">
         <v>1430</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1431</v>
       </c>
       <c r="D512" s="1"/>
     </row>
     <row r="513" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B513" t="s">
         <v>1432</v>
       </c>
-      <c r="B513" t="s">
+      <c r="C513" t="s">
         <v>1433</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1434</v>
       </c>
       <c r="D513" s="1"/>
     </row>
     <row r="514" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="8" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B514" t="s">
         <v>1435</v>
       </c>
-      <c r="B514" t="s">
+      <c r="C514" t="s">
         <v>1436</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1437</v>
       </c>
       <c r="D514" s="1"/>
     </row>
     <row r="515" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="8" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B515" t="s">
         <v>1438</v>
       </c>
-      <c r="B515" t="s">
+      <c r="C515" t="s">
         <v>1439</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1440</v>
       </c>
       <c r="D515" s="1"/>
     </row>
     <row r="516" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="8" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C516" t="s">
         <v>1441</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1443</v>
-      </c>
-      <c r="C516" t="s">
-        <v>1442</v>
       </c>
       <c r="D516" s="1"/>
     </row>
     <row r="517" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="8" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B517" t="s">
         <v>1444</v>
       </c>
-      <c r="B517" t="s">
+      <c r="C517" t="s">
         <v>1445</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1446</v>
       </c>
       <c r="D517" s="1"/>
     </row>
     <row r="518" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B518" t="s">
         <v>1447</v>
       </c>
-      <c r="B518" t="s">
+      <c r="C518" t="s">
         <v>1448</v>
-      </c>
-      <c r="C518" t="s">
-        <v>1449</v>
       </c>
       <c r="D518" s="1"/>
     </row>
     <row r="519" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="8" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B519" t="s">
         <v>1450</v>
       </c>
-      <c r="B519" t="s">
+      <c r="C519" t="s">
         <v>1451</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1452</v>
       </c>
       <c r="D519" s="1"/>
     </row>
     <row r="520" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B520" t="s">
         <v>1453</v>
       </c>
-      <c r="B520" t="s">
+      <c r="C520" t="s">
         <v>1454</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1455</v>
       </c>
       <c r="D520" s="1"/>
     </row>
     <row r="521" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B521" t="s">
         <v>1456</v>
       </c>
-      <c r="B521" t="s">
+      <c r="C521" t="s">
         <v>1457</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1458</v>
       </c>
       <c r="D521" s="1"/>
     </row>
     <row r="522" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="8" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B522" t="s">
         <v>1459</v>
       </c>
-      <c r="B522" t="s">
+      <c r="C522" t="s">
         <v>1460</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1461</v>
       </c>
       <c r="D522" s="1"/>
     </row>
     <row r="523" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B523" t="s">
         <v>1462</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1463</v>
       </c>
       <c r="C523">
         <v>0</v>
@@ -12893,10 +12890,10 @@
     </row>
     <row r="524" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="8" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B524" t="s">
         <v>1464</v>
-      </c>
-      <c r="B524" t="s">
-        <v>1465</v>
       </c>
       <c r="C524">
         <v>0</v>
@@ -12905,10 +12902,10 @@
     </row>
     <row r="525" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B525" t="s">
         <v>1466</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1467</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -12917,34 +12914,34 @@
     </row>
     <row r="526" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="8" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B526" s="7">
+        <v>0</v>
+      </c>
+      <c r="C526" t="s">
         <v>1468</v>
-      </c>
-      <c r="B526" s="7">
-        <v>0</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1469</v>
       </c>
       <c r="D526" s="1"/>
     </row>
     <row r="527" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="8" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C527" t="s">
         <v>1470</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1471</v>
       </c>
       <c r="D527" s="1"/>
     </row>
     <row r="528" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="8" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B528" t="s">
         <v>1473</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1474</v>
       </c>
       <c r="C528">
         <v>0</v>
@@ -12953,10 +12950,10 @@
     </row>
     <row r="529" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="8" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B529" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -12965,82 +12962,82 @@
     </row>
     <row r="530" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="8" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B530" t="s">
         <v>1477</v>
       </c>
-      <c r="B530" t="s">
+      <c r="C530" t="s">
         <v>1478</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1479</v>
       </c>
       <c r="D530" s="1"/>
     </row>
     <row r="531" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+      <c r="C531" t="s">
         <v>1480</v>
-      </c>
-      <c r="B531">
-        <v>0</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1481</v>
       </c>
       <c r="D531" s="1"/>
     </row>
     <row r="532" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="8" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C532" t="s">
         <v>1482</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1484</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1483</v>
       </c>
       <c r="D532" s="1"/>
     </row>
     <row r="533" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="8" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B533" t="s">
         <v>1485</v>
       </c>
-      <c r="B533" t="s">
+      <c r="C533" t="s">
         <v>1486</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1487</v>
       </c>
       <c r="D533" s="1"/>
     </row>
     <row r="534" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="8" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C534" t="s">
         <v>1488</v>
-      </c>
-      <c r="B534" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1489</v>
       </c>
       <c r="D534" s="1"/>
     </row>
     <row r="535" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C535" t="s">
         <v>1491</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1493</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1492</v>
       </c>
       <c r="D535" s="1"/>
     </row>
     <row r="536" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B536" t="s">
         <v>1494</v>
-      </c>
-      <c r="B536" t="s">
-        <v>1495</v>
       </c>
       <c r="C536">
         <v>0</v>
@@ -13049,10 +13046,10 @@
     </row>
     <row r="537" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B537" t="s">
         <v>1496</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1497</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -13061,10 +13058,10 @@
     </row>
     <row r="538" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="8" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B538" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -13073,34 +13070,34 @@
     </row>
     <row r="539" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="8" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B539" t="s">
         <v>1499</v>
       </c>
-      <c r="B539" t="s">
+      <c r="C539" t="s">
         <v>1500</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1501</v>
       </c>
       <c r="D539" s="1"/>
     </row>
     <row r="540" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+      <c r="C540" t="s">
         <v>1502</v>
-      </c>
-      <c r="B540">
-        <v>0</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1503</v>
       </c>
       <c r="D540" s="1"/>
     </row>
     <row r="541" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="8" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B541" t="s">
         <v>1504</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1505</v>
       </c>
       <c r="C541">
         <v>0</v>
@@ -13109,22 +13106,22 @@
     </row>
     <row r="542" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="8" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B542" t="s">
         <v>1506</v>
       </c>
-      <c r="B542" t="s">
+      <c r="C542" t="s">
         <v>1507</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1508</v>
       </c>
       <c r="D542" s="1"/>
     </row>
     <row r="543" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B543" t="s">
         <v>1509</v>
-      </c>
-      <c r="B543" t="s">
-        <v>1510</v>
       </c>
       <c r="C543">
         <v>0</v>
@@ -13133,10 +13130,10 @@
     </row>
     <row r="544" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="8" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B544" t="s">
         <v>1511</v>
-      </c>
-      <c r="B544" t="s">
-        <v>1512</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -13145,22 +13142,22 @@
     </row>
     <row r="545" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="8" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B545" t="s">
         <v>1513</v>
       </c>
-      <c r="B545" t="s">
+      <c r="C545" t="s">
         <v>1514</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1515</v>
       </c>
       <c r="D545" s="1"/>
     </row>
     <row r="546" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="8" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B546" t="s">
         <v>1516</v>
-      </c>
-      <c r="B546" t="s">
-        <v>1517</v>
       </c>
       <c r="C546">
         <v>0</v>
@@ -13169,10 +13166,10 @@
     </row>
     <row r="547" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="8" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B547" t="s">
         <v>1518</v>
-      </c>
-      <c r="B547" t="s">
-        <v>1519</v>
       </c>
       <c r="C547">
         <v>0</v>
@@ -13181,10 +13178,10 @@
     </row>
     <row r="548" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="8" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B548" t="s">
         <v>1520</v>
-      </c>
-      <c r="B548" t="s">
-        <v>1521</v>
       </c>
       <c r="C548">
         <v>0</v>
@@ -13193,10 +13190,10 @@
     </row>
     <row r="549" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="8" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B549" t="s">
         <v>1538</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1539</v>
       </c>
       <c r="C549">
         <v>0</v>
@@ -13205,10 +13202,10 @@
     </row>
     <row r="550" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="8" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B550" t="s">
         <v>1541</v>
-      </c>
-      <c r="B550" t="s">
-        <v>1542</v>
       </c>
       <c r="C550">
         <v>0</v>
@@ -13217,10 +13214,10 @@
     </row>
     <row r="551" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="8" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B551" t="s">
         <v>1543</v>
-      </c>
-      <c r="B551" t="s">
-        <v>1544</v>
       </c>
       <c r="C551">
         <v>0</v>
@@ -13229,10 +13226,10 @@
     </row>
     <row r="552" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B552" t="s">
         <v>1570</v>
-      </c>
-      <c r="B552" t="s">
-        <v>1571</v>
       </c>
       <c r="C552">
         <v>0</v>
@@ -13241,13 +13238,13 @@
     </row>
     <row r="553" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B553" t="s">
+        <v>187</v>
+      </c>
+      <c r="C553" t="s">
         <v>186</v>
-      </c>
-      <c r="B553" t="s">
-        <v>188</v>
-      </c>
-      <c r="C553" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -13266,7 +13263,7 @@
         <v>10</v>
       </c>
       <c r="B555" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C555" s="1">
         <v>0</v>
@@ -13274,24 +13271,24 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B556" t="s">
         <v>273</v>
       </c>
-      <c r="B556" t="s">
+      <c r="C556" t="s">
         <v>274</v>
-      </c>
-      <c r="C556" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C557" t="s">
         <v>182</v>
-      </c>
-      <c r="B557" t="s">
-        <v>1561</v>
-      </c>
-      <c r="C557" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -13307,10 +13304,10 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B559" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>43</v>
@@ -13319,13 +13316,13 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C560" t="s">
         <v>1556</v>
-      </c>
-      <c r="B560" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1557</v>
       </c>
       <c r="E560" s="1"/>
     </row>
@@ -13334,22 +13331,22 @@
         <v>160</v>
       </c>
       <c r="B561" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C561" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E561" s="1"/>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B562" t="s">
         <v>193</v>
       </c>
-      <c r="B562" t="s">
+      <c r="C562" t="s">
         <v>194</v>
-      </c>
-      <c r="C562" t="s">
-        <v>195</v>
       </c>
       <c r="E562" s="1"/>
     </row>
@@ -13366,21 +13363,21 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B564" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C564" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B565" t="s">
         <v>434</v>
-      </c>
-      <c r="B565" t="s">
-        <v>435</v>
       </c>
       <c r="C565">
         <v>0</v>
@@ -13402,7 +13399,7 @@
         <v>77</v>
       </c>
       <c r="B567" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C567" s="1" t="s">
         <v>31</v>
@@ -13413,7 +13410,7 @@
         <v>104</v>
       </c>
       <c r="B568" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C568">
         <v>0</v>
@@ -13446,7 +13443,7 @@
         <v>102</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="C571" t="s">
         <v>138</v>
@@ -13454,32 +13451,32 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+      <c r="C572" t="s">
         <v>266</v>
-      </c>
-      <c r="B572">
-        <v>0</v>
-      </c>
-      <c r="C572" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B573" t="s">
         <v>445</v>
       </c>
-      <c r="B573" t="s">
+      <c r="C573" t="s">
         <v>446</v>
-      </c>
-      <c r="C573" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B574" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C574" t="s">
         <v>145</v>
@@ -13490,7 +13487,7 @@
         <v>147</v>
       </c>
       <c r="B575" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="C575">
         <v>0</v>
@@ -13509,7 +13506,7 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B577" t="s">
         <v>151</v>
@@ -13523,10 +13520,10 @@
         <v>154</v>
       </c>
       <c r="B578" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="C578" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
@@ -13542,13 +13539,13 @@
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="B580" t="s">
+        <v>420</v>
+      </c>
+      <c r="C580" t="s">
         <v>419</v>
-      </c>
-      <c r="B580" t="s">
-        <v>421</v>
-      </c>
-      <c r="C580" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -13567,10 +13564,10 @@
         <v>98</v>
       </c>
       <c r="B582" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C582" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -13578,7 +13575,7 @@
         <v>97</v>
       </c>
       <c r="B583" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C583" t="s">
         <v>140</v>
@@ -13622,7 +13619,7 @@
         <v>119</v>
       </c>
       <c r="B587" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="C587" t="s">
         <v>120</v>
@@ -13633,10 +13630,10 @@
         <v>163</v>
       </c>
       <c r="B588" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C588" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="E588" s="1"/>
     </row>
@@ -13676,10 +13673,10 @@
     </row>
     <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B592" t="s">
         <v>184</v>
-      </c>
-      <c r="B592" t="s">
-        <v>185</v>
       </c>
       <c r="C592">
         <v>0</v>
@@ -13688,10 +13685,10 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B593" t="s">
         <v>413</v>
-      </c>
-      <c r="B593" t="s">
-        <v>414</v>
       </c>
       <c r="C593">
         <v>0</v>
@@ -13699,21 +13696,21 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B594" t="s">
+        <v>589</v>
+      </c>
+      <c r="C594" t="s">
         <v>588</v>
-      </c>
-      <c r="B594" t="s">
-        <v>590</v>
-      </c>
-      <c r="C594" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B595" t="s">
         <v>627</v>
-      </c>
-      <c r="B595" t="s">
-        <v>628</v>
       </c>
       <c r="C595">
         <v>0</v>
@@ -13721,48 +13718,48 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B596" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="C596" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="597" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="8" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B597" t="s">
         <v>1587</v>
       </c>
-      <c r="B597" s="9" t="s">
-        <v>1588</v>
-      </c>
-      <c r="C597" s="9" t="s">
-        <v>853</v>
+      <c r="C597" t="s">
+        <v>852</v>
       </c>
       <c r="D597" s="1"/>
     </row>
     <row r="598" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="8" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B598" s="9" t="s">
         <v>1583</v>
       </c>
-      <c r="C598" s="9" t="s">
-        <v>1586</v>
+      <c r="B598" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C598" t="s">
+        <v>1585</v>
       </c>
       <c r="D598" s="1"/>
     </row>
     <row r="599" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="8" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C599" t="s">
         <v>1580</v>
-      </c>
-      <c r="B599" s="9" t="s">
-        <v>1579</v>
-      </c>
-      <c r="C599" s="9" t="s">
-        <v>1581</v>
       </c>
       <c r="D599" s="1"/>
     </row>
@@ -13790,24 +13787,24 @@
     </row>
     <row r="602" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B602" t="s">
+        <v>305</v>
+      </c>
+      <c r="C602" t="s">
         <v>307</v>
-      </c>
-      <c r="B602" t="s">
-        <v>306</v>
-      </c>
-      <c r="C602" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B603" t="s">
+        <v>270</v>
+      </c>
+      <c r="C603" t="s">
         <v>271</v>
-      </c>
-      <c r="C603" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
@@ -13837,18 +13834,18 @@
         <v>157</v>
       </c>
       <c r="B606" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="C606" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B607" t="s">
         <v>169</v>
-      </c>
-      <c r="B607" t="s">
-        <v>170</v>
       </c>
       <c r="C607">
         <v>0</v>
@@ -13859,7 +13856,7 @@
         <v>161</v>
       </c>
       <c r="B608" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C608">
         <v>0</v>
@@ -13867,22 +13864,22 @@
     </row>
     <row r="609" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B609" t="s">
         <v>1568</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1569</v>
       </c>
       <c r="D609" s="1"/>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B610" t="s">
         <v>268</v>
       </c>
-      <c r="B610" t="s">
+      <c r="C610" t="s">
         <v>269</v>
-      </c>
-      <c r="C610" t="s">
-        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/前缀.xlsx
+++ b/前缀.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lazy\Desktop\Research-on-the-Identification-Mechanism-of-Altmetrics-Data-for-Sina-Weibo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C368AF-94B8-4169-BDD2-4D4122095254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F240FBD5-6C25-4332-B019-3FD95D428F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -609,10 +609,6 @@
     <t>https://lbezone.hkust.edu.hk/pdfviewer/web/viewer.php?</t>
   </si>
   <si>
-    <t>http://dx.doi.org/;https://doi.org/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>APS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -637,10 +633,6 @@
   </si>
   <si>
     <t>pnas</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hans</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -6373,12 +6365,20 @@
     <t>百度学术</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>hans/汉斯出版社</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://dx.doi.org/;https://doi.org/;http://dx.chinadoi.cn/10.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6438,6 +6438,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -6464,7 +6472,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6490,6 +6498,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6781,7 +6795,7 @@
       </c>
       <c r="D1" s="1"/>
       <c r="F1" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6789,27 +6803,27 @@
         <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="C2" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="C3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -6820,11 +6834,11 @@
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -6832,14 +6846,14 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D5" s="3"/>
       <c r="F5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -6854,7 +6868,7 @@
       </c>
       <c r="D6" s="2"/>
       <c r="F6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,13 +6876,13 @@
         <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>317</v>
+      <c r="F7" s="9" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6876,7 +6890,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="C8" t="s">
         <v>133</v>
@@ -6887,7 +6901,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -6898,18 +6912,18 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="C10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -6931,10 +6945,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -6942,10 +6956,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6964,10 +6978,10 @@
         <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C16" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -7008,10 +7022,10 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -7022,7 +7036,7 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -7041,10 +7055,10 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -7063,7 +7077,7 @@
         <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C25" t="s">
         <v>135</v>
@@ -7121,7 +7135,7 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -7132,7 +7146,7 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7162,7 +7176,7 @@
         <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C34" t="s">
         <v>136</v>
@@ -7173,7 +7187,7 @@
         <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="C35" t="s">
         <v>65</v>
@@ -7181,10 +7195,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B36" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -7195,10 +7209,10 @@
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="C37" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -7228,7 +7242,7 @@
         <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C40" t="s">
         <v>79</v>
@@ -7236,32 +7250,32 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B41" t="s">
+        <v>434</v>
+      </c>
+      <c r="C41" t="s">
         <v>435</v>
-      </c>
-      <c r="B41" t="s">
-        <v>436</v>
-      </c>
-      <c r="C41" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B42" t="s">
+        <v>437</v>
+      </c>
+      <c r="C42" t="s">
         <v>438</v>
-      </c>
-      <c r="B42" t="s">
-        <v>439</v>
-      </c>
-      <c r="C42" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B43" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -7269,13 +7283,13 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" t="s">
+        <v>219</v>
+      </c>
+      <c r="C44" t="s">
         <v>220</v>
-      </c>
-      <c r="B44" t="s">
-        <v>221</v>
-      </c>
-      <c r="C44" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -7291,90 +7305,90 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C49" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C52" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B53" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -7401,57 +7415,57 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B56" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C56" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" t="s">
         <v>242</v>
       </c>
-      <c r="B57" t="s">
-        <v>244</v>
-      </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B58" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B59" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" t="s">
         <v>247</v>
-      </c>
-      <c r="B59" t="s">
-        <v>248</v>
-      </c>
-      <c r="C59" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" t="s">
+        <v>175</v>
+      </c>
+      <c r="C60" t="s">
         <v>176</v>
-      </c>
-      <c r="B60" t="s">
-        <v>177</v>
-      </c>
-      <c r="C60" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="6" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -7459,54 +7473,54 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="C61" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B62" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="C62" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B63" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="C63" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B64" t="s">
         <v>201</v>
       </c>
-      <c r="B64" t="s">
-        <v>203</v>
-      </c>
       <c r="C64" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B65" t="s">
         <v>207</v>
       </c>
-      <c r="B65" t="s">
-        <v>209</v>
-      </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -7525,10 +7539,10 @@
         <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C67" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -7572,7 +7586,7 @@
         <v>126</v>
       </c>
       <c r="C71" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7588,21 +7602,21 @@
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B74" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -7610,10 +7624,10 @@
     </row>
     <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -7621,32 +7635,32 @@
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B76" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C76" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B77" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="C77" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B78" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7654,120 +7668,120 @@
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" t="s">
+        <v>249</v>
+      </c>
+      <c r="C79" t="s">
         <v>250</v>
-      </c>
-      <c r="B79" t="s">
-        <v>251</v>
-      </c>
-      <c r="C79" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B80" t="s">
+        <v>255</v>
+      </c>
+      <c r="C80" t="s">
         <v>256</v>
-      </c>
-      <c r="B80" t="s">
-        <v>257</v>
-      </c>
-      <c r="C80" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B83" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C83" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B84" t="s">
+        <v>252</v>
+      </c>
+      <c r="C84" t="s">
         <v>253</v>
-      </c>
-      <c r="B84" t="s">
-        <v>254</v>
-      </c>
-      <c r="C84" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B85" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C85" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B86" t="s">
+        <v>276</v>
+      </c>
+      <c r="C86" t="s">
         <v>277</v>
-      </c>
-      <c r="B86" t="s">
-        <v>278</v>
-      </c>
-      <c r="C86" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B87" t="s">
+        <v>279</v>
+      </c>
+      <c r="C87" t="s">
         <v>280</v>
-      </c>
-      <c r="B87" t="s">
-        <v>281</v>
-      </c>
-      <c r="C87" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B88" t="s">
         <v>283</v>
       </c>
-      <c r="B88" t="s">
-        <v>285</v>
-      </c>
       <c r="C88" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B89" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7775,54 +7789,54 @@
     </row>
     <row r="90" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B90" t="s">
+        <v>287</v>
+      </c>
+      <c r="C90" t="s">
         <v>288</v>
-      </c>
-      <c r="B90" t="s">
-        <v>289</v>
-      </c>
-      <c r="C90" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B91" t="s">
+        <v>290</v>
+      </c>
+      <c r="C91" t="s">
         <v>291</v>
-      </c>
-      <c r="B91" t="s">
-        <v>292</v>
-      </c>
-      <c r="C91" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B92" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" t="s">
         <v>294</v>
-      </c>
-      <c r="B92" t="s">
-        <v>295</v>
-      </c>
-      <c r="C92" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C93" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -7830,10 +7844,10 @@
     </row>
     <row r="95" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B95" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -7841,131 +7855,131 @@
     </row>
     <row r="96" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="B96" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C96" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B97" t="s">
+        <v>307</v>
+      </c>
+      <c r="C97" t="s">
         <v>308</v>
-      </c>
-      <c r="B97" t="s">
-        <v>309</v>
-      </c>
-      <c r="C97" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B98" t="s">
+        <v>310</v>
+      </c>
+      <c r="C98" t="s">
         <v>311</v>
-      </c>
-      <c r="B98" t="s">
-        <v>312</v>
-      </c>
-      <c r="C98" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B99" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C99" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B100" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C100" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B101" t="s">
+        <v>320</v>
+      </c>
+      <c r="C101" t="s">
         <v>321</v>
-      </c>
-      <c r="B101" t="s">
-        <v>322</v>
-      </c>
-      <c r="C101" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B102" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C102" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B103" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C103" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B104" t="s">
+        <v>325</v>
+      </c>
+      <c r="C104" t="s">
         <v>326</v>
-      </c>
-      <c r="B104" t="s">
-        <v>327</v>
-      </c>
-      <c r="C104" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B105" t="s">
+        <v>328</v>
+      </c>
+      <c r="C105" t="s">
         <v>329</v>
-      </c>
-      <c r="B105" t="s">
-        <v>330</v>
-      </c>
-      <c r="C105" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C106" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -7973,10 +7987,10 @@
     </row>
     <row r="108" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B108" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -7984,252 +7998,252 @@
     </row>
     <row r="109" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B109" t="s">
+        <v>335</v>
+      </c>
+      <c r="C109" t="s">
         <v>336</v>
-      </c>
-      <c r="B109" t="s">
-        <v>337</v>
-      </c>
-      <c r="C109" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B110" t="s">
         <v>339</v>
       </c>
-      <c r="B110" t="s">
-        <v>341</v>
-      </c>
       <c r="C110" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C111" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B112" t="s">
+        <v>342</v>
+      </c>
+      <c r="C112" t="s">
         <v>344</v>
-      </c>
-      <c r="C112" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B113" t="s">
+        <v>346</v>
+      </c>
+      <c r="C113" t="s">
         <v>347</v>
-      </c>
-      <c r="B113" t="s">
-        <v>348</v>
-      </c>
-      <c r="C113" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="C114" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B115" t="s">
         <v>352</v>
       </c>
-      <c r="B115" t="s">
-        <v>354</v>
-      </c>
       <c r="C115" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C116" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B117" t="s">
+        <v>357</v>
+      </c>
+      <c r="C117" t="s">
         <v>358</v>
-      </c>
-      <c r="B117" t="s">
-        <v>359</v>
-      </c>
-      <c r="C117" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B118" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C118" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B119" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C119" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B120" t="s">
         <v>365</v>
       </c>
-      <c r="B120" t="s">
-        <v>367</v>
-      </c>
       <c r="C120" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B121" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C121" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B122" t="s">
+        <v>370</v>
+      </c>
+      <c r="C122" t="s">
         <v>371</v>
-      </c>
-      <c r="B122" t="s">
-        <v>372</v>
-      </c>
-      <c r="C122" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B123" t="s">
+        <v>373</v>
+      </c>
+      <c r="C123" t="s">
         <v>374</v>
-      </c>
-      <c r="B123" t="s">
-        <v>375</v>
-      </c>
-      <c r="C123" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B124" t="s">
         <v>377</v>
       </c>
-      <c r="B124" t="s">
-        <v>379</v>
-      </c>
       <c r="C124" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B125" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C125" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B126" t="s">
+        <v>429</v>
+      </c>
+      <c r="C126" t="s">
         <v>430</v>
-      </c>
-      <c r="B126" t="s">
-        <v>431</v>
-      </c>
-      <c r="C126" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B127" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C127" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B128" t="s">
+        <v>383</v>
+      </c>
+      <c r="C128" t="s">
         <v>384</v>
-      </c>
-      <c r="B128" t="s">
-        <v>385</v>
-      </c>
-      <c r="C128" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B129" t="s">
+        <v>386</v>
+      </c>
+      <c r="C129" t="s">
         <v>387</v>
-      </c>
-      <c r="B129" t="s">
-        <v>388</v>
-      </c>
-      <c r="C129" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B130" t="s">
+        <v>389</v>
+      </c>
+      <c r="C130" t="s">
         <v>390</v>
-      </c>
-      <c r="B130" t="s">
-        <v>391</v>
-      </c>
-      <c r="C130" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B131" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -8237,153 +8251,153 @@
     </row>
     <row r="132" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B132" t="s">
+        <v>394</v>
+      </c>
+      <c r="C132" t="s">
         <v>395</v>
-      </c>
-      <c r="B132" t="s">
-        <v>396</v>
-      </c>
-      <c r="C132" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B133" t="s">
+        <v>397</v>
+      </c>
+      <c r="C133" t="s">
         <v>398</v>
-      </c>
-      <c r="B133" t="s">
-        <v>399</v>
-      </c>
-      <c r="C133" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B134" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C134" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B135" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C135" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B136" t="s">
+        <v>402</v>
+      </c>
+      <c r="C136" t="s">
         <v>403</v>
-      </c>
-      <c r="B136" t="s">
-        <v>404</v>
-      </c>
-      <c r="C136" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B137" t="s">
+        <v>446</v>
+      </c>
+      <c r="C137" t="s">
         <v>447</v>
-      </c>
-      <c r="B137" t="s">
-        <v>448</v>
-      </c>
-      <c r="C137" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B138" t="s">
+        <v>449</v>
+      </c>
+      <c r="C138" t="s">
         <v>450</v>
-      </c>
-      <c r="B138" t="s">
-        <v>451</v>
-      </c>
-      <c r="C138" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B139" t="s">
+        <v>405</v>
+      </c>
+      <c r="C139" t="s">
         <v>406</v>
-      </c>
-      <c r="B139" t="s">
-        <v>407</v>
-      </c>
-      <c r="C139" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B140" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C140" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B141" t="s">
+        <v>455</v>
+      </c>
+      <c r="C141" t="s">
         <v>456</v>
-      </c>
-      <c r="B141" t="s">
-        <v>457</v>
-      </c>
-      <c r="C141" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B142" t="s">
+        <v>458</v>
+      </c>
+      <c r="C142" t="s">
         <v>459</v>
-      </c>
-      <c r="B142" t="s">
-        <v>460</v>
-      </c>
-      <c r="C142" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B143" t="s">
         <v>462</v>
       </c>
-      <c r="B143" t="s">
-        <v>464</v>
-      </c>
       <c r="C143" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B144" t="s">
         <v>465</v>
       </c>
-      <c r="B144" t="s">
-        <v>467</v>
-      </c>
       <c r="C144" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B145" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -8391,43 +8405,43 @@
     </row>
     <row r="146" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B146" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C146" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B147" t="s">
+        <v>471</v>
+      </c>
+      <c r="C147" t="s">
         <v>472</v>
-      </c>
-      <c r="B147" t="s">
-        <v>473</v>
-      </c>
-      <c r="C147" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B148" t="s">
+        <v>474</v>
+      </c>
+      <c r="C148" t="s">
         <v>475</v>
-      </c>
-      <c r="B148" t="s">
-        <v>476</v>
-      </c>
-      <c r="C148" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B149" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -8435,32 +8449,32 @@
     </row>
     <row r="150" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B150" t="s">
+        <v>478</v>
+      </c>
+      <c r="C150" t="s">
         <v>479</v>
-      </c>
-      <c r="B150" t="s">
-        <v>480</v>
-      </c>
-      <c r="C150" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B151" t="s">
+        <v>481</v>
+      </c>
+      <c r="C151" t="s">
         <v>482</v>
-      </c>
-      <c r="B151" t="s">
-        <v>483</v>
-      </c>
-      <c r="C151" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B152" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -8468,32 +8482,32 @@
     </row>
     <row r="153" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B153" t="s">
         <v>486</v>
       </c>
-      <c r="B153" t="s">
-        <v>488</v>
-      </c>
       <c r="C153" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B154" t="s">
+        <v>488</v>
+      </c>
+      <c r="C154" t="s">
         <v>489</v>
-      </c>
-      <c r="B154" t="s">
-        <v>490</v>
-      </c>
-      <c r="C154" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B155" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -8501,43 +8515,43 @@
     </row>
     <row r="156" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B156" t="s">
+        <v>493</v>
+      </c>
+      <c r="C156" t="s">
         <v>494</v>
-      </c>
-      <c r="B156" t="s">
-        <v>495</v>
-      </c>
-      <c r="C156" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B157" t="s">
+        <v>496</v>
+      </c>
+      <c r="C157" t="s">
         <v>497</v>
-      </c>
-      <c r="B157" t="s">
-        <v>498</v>
-      </c>
-      <c r="C157" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B158" t="s">
         <v>500</v>
       </c>
-      <c r="B158" t="s">
-        <v>502</v>
-      </c>
       <c r="C158" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B159" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C159" s="7">
         <v>0</v>
@@ -8545,10 +8559,10 @@
     </row>
     <row r="160" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B160" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C160" s="7">
         <v>0</v>
@@ -8556,21 +8570,21 @@
     </row>
     <row r="161" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B161" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C161" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B162" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -8578,76 +8592,76 @@
     </row>
     <row r="163" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B163" t="s">
+        <v>508</v>
+      </c>
+      <c r="C163" t="s">
         <v>509</v>
-      </c>
-      <c r="B163" t="s">
-        <v>510</v>
-      </c>
-      <c r="C163" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B164" t="s">
         <v>512</v>
       </c>
-      <c r="B164" t="s">
-        <v>514</v>
-      </c>
       <c r="C164" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B165" t="s">
+        <v>514</v>
+      </c>
+      <c r="C165" t="s">
         <v>515</v>
-      </c>
-      <c r="B165" t="s">
-        <v>516</v>
-      </c>
-      <c r="C165" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="B166" t="s">
+        <v>517</v>
+      </c>
+      <c r="C166" t="s">
         <v>518</v>
-      </c>
-      <c r="B166" t="s">
-        <v>519</v>
-      </c>
-      <c r="C166" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="B167" t="s">
         <v>521</v>
       </c>
-      <c r="B167" t="s">
-        <v>523</v>
-      </c>
       <c r="C167" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="B168" t="s">
         <v>524</v>
       </c>
-      <c r="B168" t="s">
-        <v>526</v>
-      </c>
       <c r="C168" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B169" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -8655,10 +8669,10 @@
     </row>
     <row r="170" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B170" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -8666,21 +8680,21 @@
     </row>
     <row r="171" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B171" t="s">
+        <v>555</v>
+      </c>
+      <c r="C171" t="s">
         <v>556</v>
-      </c>
-      <c r="B171" t="s">
-        <v>557</v>
-      </c>
-      <c r="C171" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B172" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -8688,43 +8702,43 @@
     </row>
     <row r="173" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B173" t="s">
         <v>561</v>
       </c>
-      <c r="B173" t="s">
-        <v>563</v>
-      </c>
       <c r="C173" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="B174" t="s">
         <v>564</v>
       </c>
-      <c r="B174" t="s">
-        <v>566</v>
-      </c>
       <c r="C174" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="B175" t="s">
+        <v>566</v>
+      </c>
+      <c r="C175" t="s">
         <v>567</v>
-      </c>
-      <c r="B175" t="s">
-        <v>568</v>
-      </c>
-      <c r="C175" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B176" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -8732,10 +8746,10 @@
     </row>
     <row r="177" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B177" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -8743,10 +8757,10 @@
     </row>
     <row r="178" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B178" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -8754,10 +8768,10 @@
     </row>
     <row r="179" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B179" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -8765,21 +8779,21 @@
     </row>
     <row r="180" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="B180" t="s">
+        <v>577</v>
+      </c>
+      <c r="C180" t="s">
         <v>578</v>
-      </c>
-      <c r="B180" t="s">
-        <v>579</v>
-      </c>
-      <c r="C180" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B181" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -8787,21 +8801,21 @@
     </row>
     <row r="182" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B182" t="s">
+        <v>582</v>
+      </c>
+      <c r="C182" t="s">
         <v>583</v>
-      </c>
-      <c r="B182" t="s">
-        <v>584</v>
-      </c>
-      <c r="C182" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B183" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -8810,82 +8824,82 @@
     </row>
     <row r="184" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="B184" t="s">
         <v>590</v>
       </c>
-      <c r="B184" t="s">
-        <v>592</v>
-      </c>
       <c r="C184" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D184" s="1"/>
     </row>
     <row r="185" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="B185" t="s">
+        <v>593</v>
+      </c>
+      <c r="C185" t="s">
         <v>594</v>
-      </c>
-      <c r="B185" t="s">
-        <v>595</v>
-      </c>
-      <c r="C185" t="s">
-        <v>596</v>
       </c>
       <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C186" t="s">
         <v>597</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C186" t="s">
-        <v>599</v>
       </c>
       <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="8" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B187" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C187" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="B188" t="s">
+        <v>602</v>
+      </c>
+      <c r="C188" t="s">
         <v>603</v>
-      </c>
-      <c r="B188" t="s">
-        <v>604</v>
-      </c>
-      <c r="C188" t="s">
-        <v>605</v>
       </c>
       <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="B189" t="s">
+        <v>605</v>
+      </c>
+      <c r="C189" t="s">
         <v>606</v>
-      </c>
-      <c r="B189" t="s">
-        <v>607</v>
-      </c>
-      <c r="C189" t="s">
-        <v>608</v>
       </c>
       <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B190" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -8894,22 +8908,22 @@
     </row>
     <row r="191" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B191" t="s">
+        <v>610</v>
+      </c>
+      <c r="C191" t="s">
         <v>611</v>
-      </c>
-      <c r="B191" t="s">
-        <v>612</v>
-      </c>
-      <c r="C191" t="s">
-        <v>613</v>
       </c>
       <c r="D191" s="1"/>
     </row>
     <row r="192" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B192" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -8918,34 +8932,34 @@
     </row>
     <row r="193" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="B193" t="s">
+        <v>615</v>
+      </c>
+      <c r="C193" t="s">
         <v>616</v>
-      </c>
-      <c r="B193" t="s">
-        <v>617</v>
-      </c>
-      <c r="C193" t="s">
-        <v>618</v>
       </c>
       <c r="D193" s="1"/>
     </row>
     <row r="194" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B194" t="s">
+        <v>618</v>
+      </c>
+      <c r="C194" t="s">
         <v>619</v>
-      </c>
-      <c r="B194" t="s">
-        <v>620</v>
-      </c>
-      <c r="C194" t="s">
-        <v>621</v>
       </c>
       <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B195" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -8954,10 +8968,10 @@
     </row>
     <row r="196" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B196" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -8966,10 +8980,10 @@
     </row>
     <row r="197" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B197" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8978,22 +8992,22 @@
     </row>
     <row r="198" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B198" t="s">
+        <v>630</v>
+      </c>
+      <c r="C198" t="s">
         <v>631</v>
-      </c>
-      <c r="B198" t="s">
-        <v>632</v>
-      </c>
-      <c r="C198" t="s">
-        <v>633</v>
       </c>
       <c r="D198" s="1"/>
     </row>
     <row r="199" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="8" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B199" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -9002,10 +9016,10 @@
     </row>
     <row r="200" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="8" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B200" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -9014,34 +9028,34 @@
     </row>
     <row r="201" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="B201" t="s">
         <v>638</v>
       </c>
-      <c r="B201" t="s">
-        <v>640</v>
-      </c>
       <c r="C201" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D201" s="1"/>
     </row>
     <row r="202" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B202" t="s">
         <v>641</v>
       </c>
-      <c r="B202" t="s">
-        <v>643</v>
-      </c>
       <c r="C202" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B203" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -9050,10 +9064,10 @@
     </row>
     <row r="204" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B204" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -9062,10 +9076,10 @@
     </row>
     <row r="205" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B205" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -9074,10 +9088,10 @@
     </row>
     <row r="206" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B206" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -9086,10 +9100,10 @@
     </row>
     <row r="207" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B207" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -9098,58 +9112,58 @@
     </row>
     <row r="208" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="B208" t="s">
         <v>654</v>
       </c>
-      <c r="B208" t="s">
-        <v>656</v>
-      </c>
       <c r="C208" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D208" s="1"/>
     </row>
     <row r="209" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B209" t="s">
+        <v>656</v>
+      </c>
+      <c r="C209" t="s">
         <v>657</v>
-      </c>
-      <c r="B209" t="s">
-        <v>658</v>
-      </c>
-      <c r="C209" t="s">
-        <v>659</v>
       </c>
       <c r="D209" s="1"/>
     </row>
     <row r="210" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="B210" t="s">
+        <v>659</v>
+      </c>
+      <c r="C210" t="s">
         <v>660</v>
-      </c>
-      <c r="B210" t="s">
-        <v>661</v>
-      </c>
-      <c r="C210" t="s">
-        <v>662</v>
       </c>
       <c r="D210" s="1"/>
     </row>
     <row r="211" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B211" t="s">
         <v>663</v>
       </c>
-      <c r="B211" t="s">
-        <v>665</v>
-      </c>
       <c r="C211" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D211" s="1"/>
     </row>
     <row r="212" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B212" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -9158,34 +9172,34 @@
     </row>
     <row r="213" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="B213" t="s">
         <v>668</v>
       </c>
-      <c r="B213" t="s">
-        <v>670</v>
-      </c>
       <c r="C213" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D213" s="1"/>
     </row>
     <row r="214" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B214" t="s">
+        <v>670</v>
+      </c>
+      <c r="C214" t="s">
         <v>671</v>
-      </c>
-      <c r="B214" t="s">
-        <v>672</v>
-      </c>
-      <c r="C214" t="s">
-        <v>673</v>
       </c>
       <c r="D214" s="1"/>
     </row>
     <row r="215" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B215" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -9194,58 +9208,58 @@
     </row>
     <row r="216" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="B216" t="s">
         <v>676</v>
       </c>
-      <c r="B216" t="s">
-        <v>678</v>
-      </c>
       <c r="C216" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D216" s="1"/>
     </row>
     <row r="217" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B217" t="s">
         <v>679</v>
       </c>
-      <c r="B217" t="s">
-        <v>681</v>
-      </c>
       <c r="C217" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="B218" t="s">
+        <v>681</v>
+      </c>
+      <c r="C218" t="s">
         <v>682</v>
-      </c>
-      <c r="B218" t="s">
-        <v>683</v>
-      </c>
-      <c r="C218" t="s">
-        <v>684</v>
       </c>
       <c r="D218" s="1"/>
     </row>
     <row r="219" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B219" t="s">
+        <v>684</v>
+      </c>
+      <c r="C219" t="s">
         <v>685</v>
-      </c>
-      <c r="B219" t="s">
-        <v>686</v>
-      </c>
-      <c r="C219" t="s">
-        <v>687</v>
       </c>
       <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="8" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B220" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -9254,58 +9268,58 @@
     </row>
     <row r="221" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="B221" t="s">
+        <v>689</v>
+      </c>
+      <c r="C221" t="s">
         <v>690</v>
-      </c>
-      <c r="B221" t="s">
-        <v>691</v>
-      </c>
-      <c r="C221" t="s">
-        <v>692</v>
       </c>
       <c r="D221" s="1"/>
     </row>
     <row r="222" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B222" t="s">
+        <v>692</v>
+      </c>
+      <c r="C222" t="s">
         <v>693</v>
-      </c>
-      <c r="B222" t="s">
-        <v>694</v>
-      </c>
-      <c r="C222" t="s">
-        <v>695</v>
       </c>
       <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="B223" t="s">
         <v>696</v>
       </c>
-      <c r="B223" t="s">
-        <v>698</v>
-      </c>
       <c r="C223" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D223" s="1"/>
     </row>
     <row r="224" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="B224" t="s">
         <v>699</v>
       </c>
-      <c r="B224" t="s">
-        <v>701</v>
-      </c>
       <c r="C224" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D224" s="1"/>
     </row>
     <row r="225" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B225" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -9314,58 +9328,58 @@
     </row>
     <row r="226" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B226" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C226" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D226" s="1"/>
     </row>
     <row r="227" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="B227" t="s">
+        <v>704</v>
+      </c>
+      <c r="C227" t="s">
         <v>705</v>
-      </c>
-      <c r="B227" t="s">
-        <v>706</v>
-      </c>
-      <c r="C227" t="s">
-        <v>707</v>
       </c>
       <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="B228" t="s">
+        <v>707</v>
+      </c>
+      <c r="C228" t="s">
         <v>708</v>
-      </c>
-      <c r="B228" t="s">
-        <v>709</v>
-      </c>
-      <c r="C228" t="s">
-        <v>710</v>
       </c>
       <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="B229" t="s">
+        <v>710</v>
+      </c>
+      <c r="C229" t="s">
         <v>711</v>
-      </c>
-      <c r="B229" t="s">
-        <v>712</v>
-      </c>
-      <c r="C229" t="s">
-        <v>713</v>
       </c>
       <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B230" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -9374,22 +9388,22 @@
     </row>
     <row r="231" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="B231" t="s">
         <v>716</v>
       </c>
-      <c r="B231" t="s">
-        <v>718</v>
-      </c>
       <c r="C231" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D231" s="1"/>
     </row>
     <row r="232" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B232" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -9398,46 +9412,46 @@
     </row>
     <row r="233" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B233" t="s">
+        <v>719</v>
+      </c>
+      <c r="C233" t="s">
         <v>720</v>
-      </c>
-      <c r="B233" t="s">
-        <v>721</v>
-      </c>
-      <c r="C233" t="s">
-        <v>722</v>
       </c>
       <c r="D233" s="1"/>
     </row>
     <row r="234" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="B234" t="s">
         <v>723</v>
       </c>
-      <c r="B234" t="s">
-        <v>725</v>
-      </c>
       <c r="C234" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D234" s="1"/>
     </row>
     <row r="235" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="B235" t="s">
+        <v>725</v>
+      </c>
+      <c r="C235" t="s">
         <v>726</v>
-      </c>
-      <c r="B235" t="s">
-        <v>727</v>
-      </c>
-      <c r="C235" t="s">
-        <v>728</v>
       </c>
       <c r="D235" s="1"/>
     </row>
     <row r="236" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B236" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -9446,10 +9460,10 @@
     </row>
     <row r="237" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B237" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -9458,10 +9472,10 @@
     </row>
     <row r="238" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B238" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -9470,34 +9484,34 @@
     </row>
     <row r="239" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="B239" t="s">
+        <v>734</v>
+      </c>
+      <c r="C239" t="s">
         <v>735</v>
-      </c>
-      <c r="B239" t="s">
-        <v>736</v>
-      </c>
-      <c r="C239" t="s">
-        <v>737</v>
       </c>
       <c r="D239" s="1"/>
     </row>
     <row r="240" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B240" t="s">
+        <v>737</v>
+      </c>
+      <c r="C240" t="s">
         <v>738</v>
-      </c>
-      <c r="B240" t="s">
-        <v>739</v>
-      </c>
-      <c r="C240" t="s">
-        <v>740</v>
       </c>
       <c r="D240" s="1"/>
     </row>
     <row r="241" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B241" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -9506,10 +9520,10 @@
     </row>
     <row r="242" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="8" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B242" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -9518,10 +9532,10 @@
     </row>
     <row r="243" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="8" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B243" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -9530,10 +9544,10 @@
     </row>
     <row r="244" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="8" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B244" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -9542,10 +9556,10 @@
     </row>
     <row r="245" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B245" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -9554,10 +9568,10 @@
     </row>
     <row r="246" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B246" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9566,34 +9580,34 @@
     </row>
     <row r="247" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="B247" t="s">
+        <v>752</v>
+      </c>
+      <c r="C247" t="s">
         <v>753</v>
-      </c>
-      <c r="B247" t="s">
-        <v>754</v>
-      </c>
-      <c r="C247" t="s">
-        <v>755</v>
       </c>
       <c r="D247" s="1"/>
     </row>
     <row r="248" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="B248" t="s">
+        <v>755</v>
+      </c>
+      <c r="C248" t="s">
         <v>756</v>
-      </c>
-      <c r="B248" t="s">
-        <v>757</v>
-      </c>
-      <c r="C248" t="s">
-        <v>758</v>
       </c>
       <c r="D248" s="1"/>
     </row>
     <row r="249" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B249" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -9602,34 +9616,34 @@
     </row>
     <row r="250" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="B250" t="s">
         <v>761</v>
       </c>
-      <c r="B250" t="s">
-        <v>763</v>
-      </c>
       <c r="C250" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D250" s="1"/>
     </row>
     <row r="251" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="B251" t="s">
+        <v>763</v>
+      </c>
+      <c r="C251" t="s">
         <v>764</v>
-      </c>
-      <c r="B251" t="s">
-        <v>765</v>
-      </c>
-      <c r="C251" t="s">
-        <v>766</v>
       </c>
       <c r="D251" s="1"/>
     </row>
     <row r="252" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B252" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -9638,22 +9652,22 @@
     </row>
     <row r="253" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="8" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B253" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C253" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D253" s="1"/>
     </row>
     <row r="254" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="8" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B254" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -9662,34 +9676,34 @@
     </row>
     <row r="255" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="8" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B255" t="s">
+        <v>772</v>
+      </c>
+      <c r="C255" t="s">
         <v>774</v>
-      </c>
-      <c r="C255" t="s">
-        <v>776</v>
       </c>
       <c r="D255" s="1"/>
     </row>
     <row r="256" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="B256" t="s">
         <v>775</v>
       </c>
-      <c r="B256" t="s">
-        <v>777</v>
-      </c>
       <c r="C256" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D256" s="1"/>
     </row>
     <row r="257" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="8" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B257" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -9698,10 +9712,10 @@
     </row>
     <row r="258" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="8" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B258" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -9710,22 +9724,22 @@
     </row>
     <row r="259" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="B259" t="s">
+        <v>782</v>
+      </c>
+      <c r="C259" t="s">
         <v>783</v>
-      </c>
-      <c r="B259" t="s">
-        <v>784</v>
-      </c>
-      <c r="C259" t="s">
-        <v>785</v>
       </c>
       <c r="D259" s="1"/>
     </row>
     <row r="260" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="8" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B260" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -9734,22 +9748,22 @@
     </row>
     <row r="261" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="B261" t="s">
+        <v>787</v>
+      </c>
+      <c r="C261" t="s">
         <v>788</v>
-      </c>
-      <c r="B261" t="s">
-        <v>789</v>
-      </c>
-      <c r="C261" t="s">
-        <v>790</v>
       </c>
       <c r="D261" s="1"/>
     </row>
     <row r="262" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B262" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -9758,10 +9772,10 @@
     </row>
     <row r="263" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -9770,10 +9784,10 @@
     </row>
     <row r="264" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B264" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -9782,10 +9796,10 @@
     </row>
     <row r="265" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="8" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B265" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -9794,34 +9808,34 @@
     </row>
     <row r="266" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="8" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B266" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C266" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D266" s="1"/>
     </row>
     <row r="267" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B267" t="s">
+        <v>798</v>
+      </c>
+      <c r="C267" t="s">
         <v>799</v>
-      </c>
-      <c r="B267" t="s">
-        <v>800</v>
-      </c>
-      <c r="C267" t="s">
-        <v>801</v>
       </c>
       <c r="D267" s="1"/>
     </row>
     <row r="268" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="8" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B268" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -9830,22 +9844,22 @@
     </row>
     <row r="269" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="B269" t="s">
+        <v>803</v>
+      </c>
+      <c r="C269" t="s">
         <v>804</v>
-      </c>
-      <c r="B269" t="s">
-        <v>805</v>
-      </c>
-      <c r="C269" t="s">
-        <v>806</v>
       </c>
       <c r="D269" s="1"/>
     </row>
     <row r="270" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="8" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B270" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -9854,22 +9868,22 @@
     </row>
     <row r="271" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="B271" t="s">
+        <v>808</v>
+      </c>
+      <c r="C271" t="s">
         <v>809</v>
-      </c>
-      <c r="B271" t="s">
-        <v>810</v>
-      </c>
-      <c r="C271" t="s">
-        <v>811</v>
       </c>
       <c r="D271" s="1"/>
     </row>
     <row r="272" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B272" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -9878,82 +9892,82 @@
     </row>
     <row r="273" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="B273" t="s">
         <v>813</v>
       </c>
-      <c r="B273" t="s">
-        <v>815</v>
-      </c>
       <c r="C273" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D273" s="1"/>
     </row>
     <row r="274" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="8" t="s">
+        <v>814</v>
+      </c>
+      <c r="B274" t="s">
+        <v>815</v>
+      </c>
+      <c r="C274" t="s">
         <v>816</v>
-      </c>
-      <c r="B274" t="s">
-        <v>817</v>
-      </c>
-      <c r="C274" t="s">
-        <v>818</v>
       </c>
       <c r="D274" s="1"/>
     </row>
     <row r="275" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B275" t="s">
         <v>819</v>
       </c>
-      <c r="B275" t="s">
-        <v>821</v>
-      </c>
       <c r="C275" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D275" s="1"/>
     </row>
     <row r="276" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="8" t="s">
+        <v>820</v>
+      </c>
+      <c r="B276" t="s">
         <v>822</v>
       </c>
-      <c r="B276" t="s">
-        <v>824</v>
-      </c>
       <c r="C276" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D276" s="1"/>
     </row>
     <row r="277" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B277" t="s">
+        <v>824</v>
+      </c>
+      <c r="C277" t="s">
         <v>825</v>
-      </c>
-      <c r="B277" t="s">
-        <v>826</v>
-      </c>
-      <c r="C277" t="s">
-        <v>827</v>
       </c>
       <c r="D277" s="1"/>
     </row>
     <row r="278" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="B278" t="s">
+        <v>827</v>
+      </c>
+      <c r="C278" t="s">
         <v>828</v>
-      </c>
-      <c r="B278" t="s">
-        <v>829</v>
-      </c>
-      <c r="C278" t="s">
-        <v>830</v>
       </c>
       <c r="D278" s="1"/>
     </row>
     <row r="279" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="8" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B279" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -9962,10 +9976,10 @@
     </row>
     <row r="280" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="8" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B280" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -9974,22 +9988,22 @@
     </row>
     <row r="281" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="8" t="s">
+        <v>833</v>
+      </c>
+      <c r="B281" t="s">
         <v>835</v>
       </c>
-      <c r="B281" t="s">
-        <v>837</v>
-      </c>
       <c r="C281" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D281" s="1"/>
     </row>
     <row r="282" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="8" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B282" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -9998,10 +10012,10 @@
     </row>
     <row r="283" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="8" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B283" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -10010,34 +10024,34 @@
     </row>
     <row r="284" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B284" t="s">
+        <v>840</v>
+      </c>
+      <c r="C284" t="s">
         <v>841</v>
-      </c>
-      <c r="B284" t="s">
-        <v>842</v>
-      </c>
-      <c r="C284" t="s">
-        <v>843</v>
       </c>
       <c r="D284" s="1"/>
     </row>
     <row r="285" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="B285" t="s">
+        <v>843</v>
+      </c>
+      <c r="C285" t="s">
         <v>844</v>
-      </c>
-      <c r="B285" t="s">
-        <v>845</v>
-      </c>
-      <c r="C285" t="s">
-        <v>846</v>
       </c>
       <c r="D285" s="1"/>
     </row>
     <row r="286" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B286" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -10046,10 +10060,10 @@
     </row>
     <row r="287" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B287" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -10058,58 +10072,58 @@
     </row>
     <row r="288" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="8" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B288" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="C288" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="D288" s="1"/>
     </row>
     <row r="289" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="B289" t="s">
+        <v>852</v>
+      </c>
+      <c r="C289" t="s">
         <v>853</v>
-      </c>
-      <c r="B289" t="s">
-        <v>854</v>
-      </c>
-      <c r="C289" t="s">
-        <v>855</v>
       </c>
       <c r="D289" s="1"/>
     </row>
     <row r="290" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="B290" t="s">
+        <v>855</v>
+      </c>
+      <c r="C290" t="s">
         <v>856</v>
-      </c>
-      <c r="B290" t="s">
-        <v>857</v>
-      </c>
-      <c r="C290" t="s">
-        <v>858</v>
       </c>
       <c r="D290" s="1"/>
     </row>
     <row r="291" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="B291" t="s">
+        <v>858</v>
+      </c>
+      <c r="C291" t="s">
         <v>859</v>
-      </c>
-      <c r="B291" t="s">
-        <v>860</v>
-      </c>
-      <c r="C291" t="s">
-        <v>861</v>
       </c>
       <c r="D291" s="1"/>
     </row>
     <row r="292" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B292" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -10118,82 +10132,82 @@
     </row>
     <row r="293" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="B293" t="s">
         <v>864</v>
       </c>
-      <c r="B293" t="s">
-        <v>866</v>
-      </c>
       <c r="C293" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D293" s="1"/>
     </row>
     <row r="294" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B294" t="s">
+        <v>867</v>
+      </c>
+      <c r="C294" t="s">
         <v>868</v>
-      </c>
-      <c r="B294" t="s">
-        <v>869</v>
-      </c>
-      <c r="C294" t="s">
-        <v>870</v>
       </c>
       <c r="D294" s="1"/>
     </row>
     <row r="295" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B295" t="s">
+        <v>870</v>
+      </c>
+      <c r="C295" t="s">
         <v>871</v>
-      </c>
-      <c r="B295" t="s">
-        <v>872</v>
-      </c>
-      <c r="C295" t="s">
-        <v>873</v>
       </c>
       <c r="D295" s="1"/>
     </row>
     <row r="296" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="8" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B296">
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D296" s="1"/>
     </row>
     <row r="297" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="B297" t="s">
         <v>876</v>
       </c>
-      <c r="B297" t="s">
-        <v>878</v>
-      </c>
       <c r="C297" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D297" s="1"/>
     </row>
     <row r="298" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="B298" t="s">
+        <v>878</v>
+      </c>
+      <c r="C298" t="s">
         <v>879</v>
-      </c>
-      <c r="B298" t="s">
-        <v>880</v>
-      </c>
-      <c r="C298" t="s">
-        <v>881</v>
       </c>
       <c r="D298" s="1"/>
     </row>
     <row r="299" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B299" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -10202,34 +10216,34 @@
     </row>
     <row r="300" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="B300" t="s">
+        <v>883</v>
+      </c>
+      <c r="C300" t="s">
         <v>884</v>
-      </c>
-      <c r="B300" t="s">
-        <v>885</v>
-      </c>
-      <c r="C300" t="s">
-        <v>886</v>
       </c>
       <c r="D300" s="1"/>
     </row>
     <row r="301" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="B301" t="s">
+        <v>886</v>
+      </c>
+      <c r="C301" t="s">
         <v>887</v>
-      </c>
-      <c r="B301" t="s">
-        <v>888</v>
-      </c>
-      <c r="C301" t="s">
-        <v>889</v>
       </c>
       <c r="D301" s="1"/>
     </row>
     <row r="302" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="8" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B302" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -10238,22 +10252,22 @@
     </row>
     <row r="303" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="B303" t="s">
         <v>892</v>
       </c>
-      <c r="B303" t="s">
-        <v>894</v>
-      </c>
       <c r="C303" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D303" s="1"/>
     </row>
     <row r="304" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B304" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -10262,10 +10276,10 @@
     </row>
     <row r="305" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B305" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -10274,22 +10288,22 @@
     </row>
     <row r="306" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B306" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C306" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D306" s="1"/>
     </row>
     <row r="307" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="B307" t="s">
         <v>901</v>
-      </c>
-      <c r="B307" t="s">
-        <v>903</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -10298,10 +10312,10 @@
     </row>
     <row r="308" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B308" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -10310,10 +10324,10 @@
     </row>
     <row r="309" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B309" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -10322,10 +10336,10 @@
     </row>
     <row r="310" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="B310" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -10334,10 +10348,10 @@
     </row>
     <row r="311" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B311" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -10346,10 +10360,10 @@
     </row>
     <row r="312" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="8" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B312" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -10358,10 +10372,10 @@
     </row>
     <row r="313" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="8" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B313" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -10370,10 +10384,10 @@
     </row>
     <row r="314" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B314" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -10382,10 +10396,10 @@
     </row>
     <row r="315" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B315" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -10394,10 +10408,10 @@
     </row>
     <row r="316" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B316" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -10406,10 +10420,10 @@
     </row>
     <row r="317" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="8" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B317" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -10418,10 +10432,10 @@
     </row>
     <row r="318" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B318" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -10430,10 +10444,10 @@
     </row>
     <row r="319" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="8" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B319" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -10442,10 +10456,10 @@
     </row>
     <row r="320" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="8" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B320" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -10454,10 +10468,10 @@
     </row>
     <row r="321" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="8" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B321" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -10466,10 +10480,10 @@
     </row>
     <row r="322" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B322" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -10478,10 +10492,10 @@
     </row>
     <row r="323" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B323" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -10490,10 +10504,10 @@
     </row>
     <row r="324" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B324" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -10502,10 +10516,10 @@
     </row>
     <row r="325" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B325" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -10514,10 +10528,10 @@
     </row>
     <row r="326" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B326" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -10526,10 +10540,10 @@
     </row>
     <row r="327" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="8" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B327" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -10538,142 +10552,142 @@
     </row>
     <row r="328" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="B328" t="s">
         <v>944</v>
       </c>
-      <c r="B328" t="s">
-        <v>946</v>
-      </c>
       <c r="C328" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="D328" s="1"/>
     </row>
     <row r="329" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="B329" t="s">
+        <v>946</v>
+      </c>
+      <c r="C329" t="s">
         <v>947</v>
-      </c>
-      <c r="B329" t="s">
-        <v>948</v>
-      </c>
-      <c r="C329" t="s">
-        <v>949</v>
       </c>
       <c r="D329" s="1"/>
     </row>
     <row r="330" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="B330" t="s">
+        <v>949</v>
+      </c>
+      <c r="C330" t="s">
         <v>950</v>
-      </c>
-      <c r="B330" t="s">
-        <v>951</v>
-      </c>
-      <c r="C330" t="s">
-        <v>952</v>
       </c>
       <c r="D330" s="1"/>
     </row>
     <row r="331" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="8" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B331" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C331" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D331" s="1"/>
     </row>
     <row r="332" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="B332" t="s">
         <v>956</v>
       </c>
-      <c r="B332" t="s">
-        <v>958</v>
-      </c>
       <c r="C332" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D332" s="1"/>
     </row>
     <row r="333" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="B333" t="s">
         <v>959</v>
       </c>
-      <c r="B333" t="s">
-        <v>961</v>
-      </c>
       <c r="C333" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D333" s="1"/>
     </row>
     <row r="334" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="8" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B334">
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="D334" s="1"/>
     </row>
     <row r="335" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="B335" t="s">
         <v>964</v>
       </c>
-      <c r="B335" t="s">
-        <v>966</v>
-      </c>
       <c r="C335" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D335" s="1"/>
     </row>
     <row r="336" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="B336" t="s">
+        <v>966</v>
+      </c>
+      <c r="C336" t="s">
         <v>967</v>
-      </c>
-      <c r="B336" t="s">
-        <v>968</v>
-      </c>
-      <c r="C336" t="s">
-        <v>969</v>
       </c>
       <c r="D336" s="1"/>
     </row>
     <row r="337" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="B337" t="s">
         <v>970</v>
       </c>
-      <c r="B337" t="s">
-        <v>972</v>
-      </c>
       <c r="C337" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D337" s="1"/>
     </row>
     <row r="338" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="B338" t="s">
         <v>973</v>
       </c>
-      <c r="B338" t="s">
-        <v>975</v>
-      </c>
       <c r="C338" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D338" s="1"/>
     </row>
     <row r="339" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="8" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B339" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -10682,10 +10696,10 @@
     </row>
     <row r="340" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="8" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B340" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -10694,130 +10708,130 @@
     </row>
     <row r="341" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="B341" t="s">
+        <v>979</v>
+      </c>
+      <c r="C341" t="s">
         <v>980</v>
-      </c>
-      <c r="B341" t="s">
-        <v>981</v>
-      </c>
-      <c r="C341" t="s">
-        <v>982</v>
       </c>
       <c r="D341" s="1"/>
     </row>
     <row r="342" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="B342" t="s">
+        <v>982</v>
+      </c>
+      <c r="C342" t="s">
         <v>983</v>
-      </c>
-      <c r="B342" t="s">
-        <v>984</v>
-      </c>
-      <c r="C342" t="s">
-        <v>985</v>
       </c>
       <c r="D342" s="1"/>
     </row>
     <row r="343" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="B343" t="s">
         <v>986</v>
       </c>
-      <c r="B343" t="s">
-        <v>988</v>
-      </c>
       <c r="C343" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D343" s="1"/>
     </row>
     <row r="344" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="B344" t="s">
         <v>989</v>
       </c>
-      <c r="B344" t="s">
-        <v>991</v>
-      </c>
       <c r="C344" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="D344" s="1"/>
     </row>
     <row r="345" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="B345" t="s">
+        <v>991</v>
+      </c>
+      <c r="C345" t="s">
         <v>992</v>
-      </c>
-      <c r="B345" t="s">
-        <v>993</v>
-      </c>
-      <c r="C345" t="s">
-        <v>994</v>
       </c>
       <c r="D345" s="1"/>
     </row>
     <row r="346" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="B346" t="s">
+        <v>994</v>
+      </c>
+      <c r="C346" t="s">
         <v>995</v>
-      </c>
-      <c r="B346" t="s">
-        <v>996</v>
-      </c>
-      <c r="C346" t="s">
-        <v>997</v>
       </c>
       <c r="D346" s="1"/>
     </row>
     <row r="347" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="B347" t="s">
+        <v>997</v>
+      </c>
+      <c r="C347" t="s">
         <v>998</v>
-      </c>
-      <c r="B347" t="s">
-        <v>999</v>
-      </c>
-      <c r="C347" t="s">
-        <v>1000</v>
       </c>
       <c r="D347" s="1"/>
     </row>
     <row r="348" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C348" t="s">
         <v>1001</v>
-      </c>
-      <c r="B348" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1003</v>
       </c>
       <c r="D348" s="1"/>
     </row>
     <row r="349" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B349" t="s">
         <v>1004</v>
       </c>
-      <c r="B349" t="s">
-        <v>1006</v>
-      </c>
       <c r="C349" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="D349" s="1"/>
     </row>
     <row r="350" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B350" t="s">
         <v>1007</v>
       </c>
-      <c r="B350" t="s">
-        <v>1009</v>
-      </c>
       <c r="C350" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D350" s="1"/>
     </row>
     <row r="351" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="8" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B351" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -10826,10 +10840,10 @@
     </row>
     <row r="352" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="8" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B352" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -10838,10 +10852,10 @@
     </row>
     <row r="353" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="8" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B353" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -10850,10 +10864,10 @@
     </row>
     <row r="354" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="8" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B354" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -10862,22 +10876,22 @@
     </row>
     <row r="355" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C355" t="s">
         <v>1019</v>
-      </c>
-      <c r="B355" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C355" t="s">
-        <v>1021</v>
       </c>
       <c r="D355" s="1"/>
     </row>
     <row r="356" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="8" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B356" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -10886,10 +10900,10 @@
     </row>
     <row r="357" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="8" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B357" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -10898,10 +10912,10 @@
     </row>
     <row r="358" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="8" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B358" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -10910,31 +10924,31 @@
     </row>
     <row r="359" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B359" t="s">
         <v>1028</v>
       </c>
-      <c r="B359" t="s">
-        <v>1030</v>
-      </c>
       <c r="C359" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D359" s="1"/>
     </row>
     <row r="360" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B360" t="s">
         <v>1031</v>
       </c>
-      <c r="B360" t="s">
-        <v>1033</v>
-      </c>
       <c r="C360" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="D360" s="1"/>
     </row>
     <row r="361" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="8" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -10946,10 +10960,10 @@
     </row>
     <row r="362" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="8" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B362" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -10958,142 +10972,142 @@
     </row>
     <row r="363" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C363" t="s">
         <v>1037</v>
-      </c>
-      <c r="B363" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C363" t="s">
-        <v>1039</v>
       </c>
       <c r="D363" s="1"/>
     </row>
     <row r="364" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C364" t="s">
         <v>1040</v>
-      </c>
-      <c r="B364" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C364" t="s">
-        <v>1042</v>
       </c>
       <c r="D364" s="1"/>
     </row>
     <row r="365" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C365" t="s">
         <v>1043</v>
-      </c>
-      <c r="B365" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C365" t="s">
-        <v>1045</v>
       </c>
       <c r="D365" s="1"/>
     </row>
     <row r="366" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C366" t="s">
         <v>1046</v>
-      </c>
-      <c r="B366" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C366" t="s">
-        <v>1048</v>
       </c>
       <c r="D366" s="1"/>
     </row>
     <row r="367" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C367" t="s">
         <v>1049</v>
-      </c>
-      <c r="B367" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C367" t="s">
-        <v>1051</v>
       </c>
       <c r="D367" s="1"/>
     </row>
     <row r="368" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C368" t="s">
         <v>1052</v>
-      </c>
-      <c r="B368" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C368" t="s">
-        <v>1054</v>
       </c>
       <c r="D368" s="1"/>
     </row>
     <row r="369" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B369" t="s">
         <v>1055</v>
       </c>
-      <c r="B369" t="s">
-        <v>1057</v>
-      </c>
       <c r="C369" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="D369" s="1"/>
     </row>
     <row r="370" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C370" t="s">
         <v>1058</v>
-      </c>
-      <c r="B370" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C370" t="s">
-        <v>1060</v>
       </c>
       <c r="D370" s="1"/>
     </row>
     <row r="371" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C371" t="s">
         <v>1061</v>
-      </c>
-      <c r="B371" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C371" t="s">
-        <v>1063</v>
       </c>
       <c r="D371" s="1"/>
     </row>
     <row r="372" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C372" t="s">
         <v>1064</v>
-      </c>
-      <c r="B372" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C372" t="s">
-        <v>1066</v>
       </c>
       <c r="D372" s="1"/>
     </row>
     <row r="373" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="8" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C373" t="s">
         <v>1067</v>
-      </c>
-      <c r="B373" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C373" t="s">
-        <v>1069</v>
       </c>
       <c r="D373" s="1"/>
     </row>
     <row r="374" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="8" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B374" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -11102,22 +11116,22 @@
     </row>
     <row r="375" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C375" t="s">
         <v>1072</v>
-      </c>
-      <c r="B375" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1074</v>
       </c>
       <c r="D375" s="1"/>
     </row>
     <row r="376" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="8" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B376" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -11126,10 +11140,10 @@
     </row>
     <row r="377" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="8" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B377" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -11138,22 +11152,22 @@
     </row>
     <row r="378" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C378" t="s">
         <v>1079</v>
-      </c>
-      <c r="B378" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C378" t="s">
-        <v>1081</v>
       </c>
       <c r="D378" s="1"/>
     </row>
     <row r="379" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="8" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B379" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -11162,22 +11176,22 @@
     </row>
     <row r="380" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="8" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B380">
         <v>0</v>
       </c>
       <c r="C380" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D380" s="1"/>
     </row>
     <row r="381" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="8" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B381" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -11186,43 +11200,43 @@
     </row>
     <row r="382" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="8" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B382" t="s">
         <v>1088</v>
       </c>
-      <c r="B382" t="s">
-        <v>1090</v>
-      </c>
       <c r="C382" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D382" s="1"/>
     </row>
     <row r="383" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="8" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B383">
         <v>0</v>
       </c>
       <c r="C383" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="D383" s="1"/>
     </row>
     <row r="384" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="8" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B384">
         <v>0</v>
       </c>
       <c r="C384" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="D384" s="1"/>
     </row>
     <row r="385" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="8" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -11234,22 +11248,22 @@
     </row>
     <row r="386" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="8" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C386" t="s">
         <v>1096</v>
-      </c>
-      <c r="B386" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C386" t="s">
-        <v>1098</v>
       </c>
       <c r="D386" s="1"/>
     </row>
     <row r="387" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="8" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B387" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -11258,70 +11272,70 @@
     </row>
     <row r="388" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="8" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="B388">
         <v>0</v>
       </c>
       <c r="C388" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D388" s="1"/>
     </row>
     <row r="389" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C389" t="s">
         <v>1103</v>
-      </c>
-      <c r="B389" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C389" t="s">
-        <v>1105</v>
       </c>
       <c r="D389" s="1"/>
     </row>
     <row r="390" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="8" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B390">
         <v>0</v>
       </c>
       <c r="C390" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="D390" s="1"/>
     </row>
     <row r="391" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C391" t="s">
         <v>1108</v>
-      </c>
-      <c r="B391" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C391" t="s">
-        <v>1110</v>
       </c>
       <c r="D391" s="1"/>
     </row>
     <row r="392" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="8" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C392" t="s">
         <v>1111</v>
-      </c>
-      <c r="B392" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C392" t="s">
-        <v>1113</v>
       </c>
       <c r="D392" s="1"/>
     </row>
     <row r="393" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="8" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B393" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -11330,46 +11344,46 @@
     </row>
     <row r="394" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="8" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C394" t="s">
         <v>1116</v>
-      </c>
-      <c r="B394" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C394" t="s">
-        <v>1118</v>
       </c>
       <c r="D394" s="1"/>
     </row>
     <row r="395" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C395" t="s">
         <v>1119</v>
-      </c>
-      <c r="B395" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C395" t="s">
-        <v>1121</v>
       </c>
       <c r="D395" s="1"/>
     </row>
     <row r="396" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="8" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B396" t="s">
         <v>1122</v>
       </c>
-      <c r="B396" t="s">
-        <v>1124</v>
-      </c>
       <c r="C396" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D396" s="1"/>
     </row>
     <row r="397" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="8" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="B397" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -11378,10 +11392,10 @@
     </row>
     <row r="398" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="8" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="B398" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -11390,34 +11404,34 @@
     </row>
     <row r="399" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="8" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B399" t="s">
         <v>1129</v>
       </c>
-      <c r="B399" t="s">
-        <v>1131</v>
-      </c>
       <c r="C399" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D399" s="1"/>
     </row>
     <row r="400" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C400" t="s">
         <v>1132</v>
-      </c>
-      <c r="B400" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C400" t="s">
-        <v>1134</v>
       </c>
       <c r="D400" s="1"/>
     </row>
     <row r="401" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="8" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="B401" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -11426,190 +11440,190 @@
     </row>
     <row r="402" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="8" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C402" t="s">
         <v>1137</v>
-      </c>
-      <c r="B402" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C402" t="s">
-        <v>1139</v>
       </c>
       <c r="D402" s="1"/>
     </row>
     <row r="403" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C403" t="s">
         <v>1140</v>
-      </c>
-      <c r="B403" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C403" t="s">
-        <v>1142</v>
       </c>
       <c r="D403" s="1"/>
     </row>
     <row r="404" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C404" t="s">
         <v>1143</v>
-      </c>
-      <c r="B404" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C404" t="s">
-        <v>1145</v>
       </c>
       <c r="D404" s="1"/>
     </row>
     <row r="405" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="8" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C405" t="s">
         <v>1146</v>
-      </c>
-      <c r="B405" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C405" t="s">
-        <v>1148</v>
       </c>
       <c r="D405" s="1"/>
     </row>
     <row r="406" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="8" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B406" t="s">
         <v>1149</v>
       </c>
-      <c r="B406" t="s">
-        <v>1151</v>
-      </c>
       <c r="C406" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D406" s="1"/>
     </row>
     <row r="407" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C407" t="s">
         <v>1152</v>
-      </c>
-      <c r="B407" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C407" t="s">
-        <v>1154</v>
       </c>
       <c r="D407" s="1"/>
     </row>
     <row r="408" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="8" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C408" t="s">
         <v>1155</v>
-      </c>
-      <c r="B408" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C408" t="s">
-        <v>1157</v>
       </c>
       <c r="D408" s="1"/>
     </row>
     <row r="409" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="8" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B409" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C409" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D409" s="1"/>
     </row>
     <row r="410" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="8" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B410" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C410" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D410" s="1"/>
     </row>
     <row r="411" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="8" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B411" t="s">
         <v>1161</v>
       </c>
-      <c r="B411" t="s">
-        <v>1163</v>
-      </c>
       <c r="C411" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="D411" s="1"/>
     </row>
     <row r="412" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="8" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B412" t="s">
         <v>1164</v>
       </c>
-      <c r="B412" t="s">
-        <v>1166</v>
-      </c>
       <c r="C412" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="D412" s="1"/>
     </row>
     <row r="413" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="8" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C413" t="s">
         <v>1167</v>
-      </c>
-      <c r="B413" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C413" t="s">
-        <v>1169</v>
       </c>
       <c r="D413" s="1"/>
     </row>
     <row r="414" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="8" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C414" t="s">
         <v>1170</v>
-      </c>
-      <c r="B414" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C414" t="s">
-        <v>1172</v>
       </c>
       <c r="D414" s="1"/>
     </row>
     <row r="415" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C415" t="s">
         <v>1173</v>
-      </c>
-      <c r="B415" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C415" t="s">
-        <v>1175</v>
       </c>
       <c r="D415" s="1"/>
     </row>
     <row r="416" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C416" t="s">
         <v>1176</v>
-      </c>
-      <c r="B416" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C416" t="s">
-        <v>1178</v>
       </c>
       <c r="D416" s="1"/>
     </row>
     <row r="417" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="8" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B417" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -11618,10 +11632,10 @@
     </row>
     <row r="418" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="8" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B418" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -11630,10 +11644,10 @@
     </row>
     <row r="419" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="8" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B419" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -11642,82 +11656,82 @@
     </row>
     <row r="420" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="8" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B420" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C420" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="D420" s="1"/>
     </row>
     <row r="421" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="8" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B421" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C421" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D421" s="1"/>
     </row>
     <row r="422" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C422" t="s">
         <v>1189</v>
-      </c>
-      <c r="B422" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C422" t="s">
-        <v>1191</v>
       </c>
       <c r="D422" s="1"/>
     </row>
     <row r="423" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C423" t="s">
         <v>1192</v>
-      </c>
-      <c r="B423" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C423" t="s">
-        <v>1194</v>
       </c>
       <c r="D423" s="1"/>
     </row>
     <row r="424" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="8" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C424" t="s">
         <v>1195</v>
-      </c>
-      <c r="B424" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C424" t="s">
-        <v>1197</v>
       </c>
       <c r="D424" s="1"/>
     </row>
     <row r="425" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="8" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C425" t="s">
         <v>1198</v>
-      </c>
-      <c r="B425" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C425" t="s">
-        <v>1200</v>
       </c>
       <c r="D425" s="1"/>
     </row>
     <row r="426" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="8" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B426" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -11726,10 +11740,10 @@
     </row>
     <row r="427" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="8" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B427" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -11738,82 +11752,82 @@
     </row>
     <row r="428" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="8" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B428" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="C428" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="D428" s="1"/>
     </row>
     <row r="429" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="8" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C429" t="s">
         <v>1205</v>
-      </c>
-      <c r="B429" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1207</v>
       </c>
       <c r="D429" s="1"/>
     </row>
     <row r="430" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="8" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B430" t="s">
         <v>1208</v>
       </c>
-      <c r="B430" t="s">
-        <v>1210</v>
-      </c>
       <c r="C430" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="D430" s="1"/>
     </row>
     <row r="431" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C431" t="s">
         <v>1211</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C431" t="s">
-        <v>1213</v>
       </c>
       <c r="D431" s="1"/>
     </row>
     <row r="432" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="8" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B432" t="s">
         <v>1214</v>
       </c>
-      <c r="B432" t="s">
-        <v>1216</v>
-      </c>
       <c r="C432" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D432" s="1"/>
     </row>
     <row r="433" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="8" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C433" t="s">
         <v>1217</v>
-      </c>
-      <c r="B433" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C433" t="s">
-        <v>1219</v>
       </c>
       <c r="D433" s="1"/>
     </row>
     <row r="434" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="8" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B434" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -11822,10 +11836,10 @@
     </row>
     <row r="435" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="8" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B435" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -11834,10 +11848,10 @@
     </row>
     <row r="436" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="8" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B436" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -11846,22 +11860,22 @@
     </row>
     <row r="437" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C437" t="s">
         <v>1226</v>
-      </c>
-      <c r="B437" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C437" t="s">
-        <v>1228</v>
       </c>
       <c r="D437" s="1"/>
     </row>
     <row r="438" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="8" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B438" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -11870,34 +11884,34 @@
     </row>
     <row r="439" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C439" s="1" t="s">
         <v>1231</v>
-      </c>
-      <c r="B439" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>1233</v>
       </c>
       <c r="D439" s="1"/>
     </row>
     <row r="440" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="8" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C440" t="s">
         <v>1234</v>
-      </c>
-      <c r="B440" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C440" t="s">
-        <v>1236</v>
       </c>
       <c r="D440" s="1"/>
     </row>
     <row r="441" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="8" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B441" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C441">
         <v>0</v>
@@ -11906,70 +11920,70 @@
     </row>
     <row r="442" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C442" t="s">
         <v>1239</v>
-      </c>
-      <c r="B442" t="s">
-        <v>1240</v>
-      </c>
-      <c r="C442" t="s">
-        <v>1241</v>
       </c>
       <c r="D442" s="1"/>
     </row>
     <row r="443" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C443" t="s">
         <v>1242</v>
-      </c>
-      <c r="B443" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C443" t="s">
-        <v>1244</v>
       </c>
       <c r="D443" s="1"/>
     </row>
     <row r="444" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C444" t="s">
         <v>1245</v>
-      </c>
-      <c r="B444" t="s">
-        <v>1246</v>
-      </c>
-      <c r="C444" t="s">
-        <v>1247</v>
       </c>
       <c r="D444" s="1"/>
     </row>
     <row r="445" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C445" t="s">
         <v>1248</v>
-      </c>
-      <c r="B445" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C445" t="s">
-        <v>1250</v>
       </c>
       <c r="D445" s="1"/>
     </row>
     <row r="446" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B446" t="s">
         <v>1251</v>
       </c>
-      <c r="B446" t="s">
-        <v>1253</v>
-      </c>
       <c r="C446" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D446" s="1"/>
     </row>
     <row r="447" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="8" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B447" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C447">
         <v>0</v>
@@ -11978,10 +11992,10 @@
     </row>
     <row r="448" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="8" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B448" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -11990,10 +12004,10 @@
     </row>
     <row r="449" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="8" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B449" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -12002,166 +12016,166 @@
     </row>
     <row r="450" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="8" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B450" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="C450" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D450" s="1"/>
     </row>
     <row r="451" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="8" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B451" t="s">
         <v>1262</v>
       </c>
-      <c r="B451" t="s">
-        <v>1264</v>
-      </c>
       <c r="C451" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="D451" s="1"/>
     </row>
     <row r="452" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B452" t="s">
         <v>1265</v>
       </c>
-      <c r="B452" t="s">
-        <v>1267</v>
-      </c>
       <c r="C452" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="D452" s="1"/>
     </row>
     <row r="453" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B453" t="s">
         <v>1268</v>
       </c>
-      <c r="B453" t="s">
-        <v>1270</v>
-      </c>
       <c r="C453" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D453" s="1"/>
     </row>
     <row r="454" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C454" t="s">
         <v>1271</v>
-      </c>
-      <c r="B454" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C454" t="s">
-        <v>1273</v>
       </c>
       <c r="D454" s="1"/>
     </row>
     <row r="455" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="8" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C455" t="s">
         <v>1274</v>
-      </c>
-      <c r="B455" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C455" t="s">
-        <v>1276</v>
       </c>
       <c r="D455" s="1"/>
     </row>
     <row r="456" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C456" t="s">
         <v>1277</v>
-      </c>
-      <c r="B456" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C456" t="s">
-        <v>1279</v>
       </c>
       <c r="D456" s="1"/>
     </row>
     <row r="457" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C457" t="s">
         <v>1280</v>
-      </c>
-      <c r="B457" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C457" t="s">
-        <v>1282</v>
       </c>
       <c r="D457" s="1"/>
     </row>
     <row r="458" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C458" t="s">
         <v>1283</v>
-      </c>
-      <c r="B458" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C458" t="s">
-        <v>1285</v>
       </c>
       <c r="D458" s="1"/>
     </row>
     <row r="459" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="8" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C459" t="s">
         <v>1286</v>
-      </c>
-      <c r="B459" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C459" t="s">
-        <v>1288</v>
       </c>
       <c r="D459" s="1"/>
     </row>
     <row r="460" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C460" t="s">
         <v>1289</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C460" t="s">
-        <v>1291</v>
       </c>
       <c r="D460" s="1"/>
     </row>
     <row r="461" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="8" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B461" t="s">
         <v>1292</v>
       </c>
-      <c r="B461" t="s">
-        <v>1294</v>
-      </c>
       <c r="C461" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="D461" s="1"/>
     </row>
     <row r="462" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="8" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C462" t="s">
         <v>1295</v>
-      </c>
-      <c r="B462" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C462" t="s">
-        <v>1297</v>
       </c>
       <c r="D462" s="1"/>
     </row>
     <row r="463" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="8" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="B463" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C463">
         <v>0</v>
@@ -12170,22 +12184,22 @@
     </row>
     <row r="464" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="8" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B464" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C464" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D464" s="1"/>
     </row>
     <row r="465" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="8" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B465" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C465">
         <v>0</v>
@@ -12194,118 +12208,118 @@
     </row>
     <row r="466" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="8" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C466" t="s">
         <v>1304</v>
-      </c>
-      <c r="B466" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C466" t="s">
-        <v>1306</v>
       </c>
       <c r="D466" s="1"/>
     </row>
     <row r="467" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="8" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C467" t="s">
         <v>1307</v>
-      </c>
-      <c r="B467" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C467" t="s">
-        <v>1309</v>
       </c>
       <c r="D467" s="1"/>
     </row>
     <row r="468" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C468" t="s">
         <v>1310</v>
-      </c>
-      <c r="B468" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C468" t="s">
-        <v>1312</v>
       </c>
       <c r="D468" s="1"/>
     </row>
     <row r="469" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="8" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C469" t="s">
         <v>1313</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C469" t="s">
-        <v>1315</v>
       </c>
       <c r="D469" s="1"/>
     </row>
     <row r="470" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C470" t="s">
         <v>1316</v>
-      </c>
-      <c r="B470" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C470" t="s">
-        <v>1318</v>
       </c>
       <c r="D470" s="1"/>
     </row>
     <row r="471" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="8" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C471" t="s">
         <v>1319</v>
-      </c>
-      <c r="B471" t="s">
-        <v>1320</v>
-      </c>
-      <c r="C471" t="s">
-        <v>1321</v>
       </c>
       <c r="D471" s="1"/>
     </row>
     <row r="472" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="8" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C472" t="s">
         <v>1322</v>
-      </c>
-      <c r="B472" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C472" t="s">
-        <v>1324</v>
       </c>
       <c r="D472" s="1"/>
     </row>
     <row r="473" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="8" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C473" t="s">
         <v>1325</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C473" t="s">
-        <v>1327</v>
       </c>
       <c r="D473" s="1"/>
     </row>
     <row r="474" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="8" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C474" t="s">
         <v>1328</v>
-      </c>
-      <c r="B474" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C474" t="s">
-        <v>1330</v>
       </c>
       <c r="D474" s="1"/>
     </row>
     <row r="475" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="8" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B475" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C475">
         <v>0</v>
@@ -12314,10 +12328,10 @@
     </row>
     <row r="476" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="8" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="B476" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C476">
         <v>0</v>
@@ -12326,34 +12340,34 @@
     </row>
     <row r="477" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="8" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C477" t="s">
         <v>1335</v>
-      </c>
-      <c r="B477" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C477" t="s">
-        <v>1337</v>
       </c>
       <c r="D477" s="1"/>
     </row>
     <row r="478" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="8" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B478" t="s">
         <v>1338</v>
       </c>
-      <c r="B478" t="s">
-        <v>1340</v>
-      </c>
       <c r="C478" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="D478" s="1"/>
     </row>
     <row r="479" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="8" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="B479" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C479" s="7">
         <v>0</v>
@@ -12362,142 +12376,142 @@
     </row>
     <row r="480" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="8" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B480" t="s">
         <v>1343</v>
       </c>
-      <c r="B480" t="s">
-        <v>1345</v>
-      </c>
       <c r="C480" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="D480" s="1"/>
     </row>
     <row r="481" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C481" t="s">
         <v>1346</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C481" t="s">
-        <v>1348</v>
       </c>
       <c r="D481" s="1"/>
     </row>
     <row r="482" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="8" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C482" t="s">
         <v>1349</v>
-      </c>
-      <c r="B482" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C482" t="s">
-        <v>1351</v>
       </c>
       <c r="D482" s="1"/>
     </row>
     <row r="483" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="8" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="B483" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="C483" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="D483" s="1"/>
     </row>
     <row r="484" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="8" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C484" t="s">
         <v>1354</v>
-      </c>
-      <c r="B484" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C484" t="s">
-        <v>1356</v>
       </c>
       <c r="D484" s="1"/>
     </row>
     <row r="485" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="8" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C485" t="s">
         <v>1357</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C485" t="s">
-        <v>1359</v>
       </c>
       <c r="D485" s="1"/>
     </row>
     <row r="486" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="8" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B486" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C486" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D486" s="1"/>
     </row>
     <row r="487" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="8" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C487" t="s">
         <v>1362</v>
-      </c>
-      <c r="B487" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C487" t="s">
-        <v>1364</v>
       </c>
       <c r="D487" s="1"/>
     </row>
     <row r="488" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="8" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C488" t="s">
         <v>1365</v>
-      </c>
-      <c r="B488" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C488" t="s">
-        <v>1367</v>
       </c>
       <c r="D488" s="1"/>
     </row>
     <row r="489" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C489" t="s">
         <v>1368</v>
-      </c>
-      <c r="B489" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C489" t="s">
-        <v>1370</v>
       </c>
       <c r="D489" s="1"/>
     </row>
     <row r="490" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="8" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C490" t="s">
         <v>1371</v>
-      </c>
-      <c r="B490" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C490" t="s">
-        <v>1373</v>
       </c>
       <c r="D490" s="1"/>
     </row>
     <row r="491" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="8" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B491" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="C491">
         <v>0</v>
@@ -12506,22 +12520,22 @@
     </row>
     <row r="492" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C492" t="s">
         <v>1376</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C492" t="s">
-        <v>1378</v>
       </c>
       <c r="D492" s="1"/>
     </row>
     <row r="493" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="8" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B493" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C493">
         <v>0</v>
@@ -12530,58 +12544,58 @@
     </row>
     <row r="494" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="8" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C494" t="s">
         <v>1381</v>
-      </c>
-      <c r="B494" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C494" t="s">
-        <v>1383</v>
       </c>
       <c r="D494" s="1"/>
     </row>
     <row r="495" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="8" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C495" t="s">
         <v>1384</v>
-      </c>
-      <c r="B495" t="s">
-        <v>1385</v>
-      </c>
-      <c r="C495" t="s">
-        <v>1386</v>
       </c>
       <c r="D495" s="1"/>
     </row>
     <row r="496" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="8" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="B496">
         <v>0</v>
       </c>
       <c r="C496" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="D496" s="1"/>
     </row>
     <row r="497" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="8" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C497" t="s">
         <v>1389</v>
-      </c>
-      <c r="B497" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1391</v>
       </c>
       <c r="D497" s="1"/>
     </row>
     <row r="498" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="8" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B498" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C498">
         <v>0</v>
@@ -12590,10 +12604,10 @@
     </row>
     <row r="499" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="8" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B499" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C499">
         <v>0</v>
@@ -12602,34 +12616,34 @@
     </row>
     <row r="500" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="8" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B500" t="s">
         <v>1396</v>
       </c>
-      <c r="B500" t="s">
-        <v>1398</v>
-      </c>
       <c r="C500" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D500" s="1"/>
     </row>
     <row r="501" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="8" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B501" t="s">
         <v>1399</v>
       </c>
-      <c r="B501" t="s">
-        <v>1401</v>
-      </c>
       <c r="C501" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="D501" s="1"/>
     </row>
     <row r="502" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="8" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B502" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C502">
         <v>0</v>
@@ -12638,10 +12652,10 @@
     </row>
     <row r="503" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="8" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B503" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="C503">
         <v>0</v>
@@ -12650,10 +12664,10 @@
     </row>
     <row r="504" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B504" t="s">
         <v>1406</v>
-      </c>
-      <c r="B504" t="s">
-        <v>1408</v>
       </c>
       <c r="C504">
         <v>0</v>
@@ -12662,22 +12676,22 @@
     </row>
     <row r="505" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B505" t="s">
         <v>1407</v>
       </c>
-      <c r="B505" t="s">
-        <v>1409</v>
-      </c>
       <c r="C505" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="D505" s="1"/>
     </row>
     <row r="506" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="8" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B506" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="C506">
         <v>0</v>
@@ -12686,202 +12700,202 @@
     </row>
     <row r="507" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C507" t="s">
         <v>1413</v>
-      </c>
-      <c r="B507" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C507" t="s">
-        <v>1415</v>
       </c>
       <c r="D507" s="1"/>
     </row>
     <row r="508" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="8" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B508" t="s">
         <v>1416</v>
       </c>
-      <c r="B508" t="s">
-        <v>1418</v>
-      </c>
       <c r="C508" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="D508" s="1"/>
     </row>
     <row r="509" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C509" t="s">
         <v>1419</v>
-      </c>
-      <c r="B509" t="s">
-        <v>1420</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1421</v>
       </c>
       <c r="D509" s="1"/>
     </row>
     <row r="510" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="8" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C510" t="s">
         <v>1422</v>
-      </c>
-      <c r="B510" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1424</v>
       </c>
       <c r="D510" s="1"/>
     </row>
     <row r="511" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="8" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C511" t="s">
         <v>1425</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1426</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1427</v>
       </c>
       <c r="D511" s="1"/>
     </row>
     <row r="512" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C512" t="s">
         <v>1428</v>
-      </c>
-      <c r="B512" t="s">
-        <v>1429</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1430</v>
       </c>
       <c r="D512" s="1"/>
     </row>
     <row r="513" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C513" t="s">
         <v>1431</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1433</v>
       </c>
       <c r="D513" s="1"/>
     </row>
     <row r="514" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="8" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C514" t="s">
         <v>1434</v>
-      </c>
-      <c r="B514" t="s">
-        <v>1435</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1436</v>
       </c>
       <c r="D514" s="1"/>
     </row>
     <row r="515" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C515" t="s">
         <v>1437</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1438</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1439</v>
       </c>
       <c r="D515" s="1"/>
     </row>
     <row r="516" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="8" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B516" t="s">
         <v>1440</v>
       </c>
-      <c r="B516" t="s">
-        <v>1442</v>
-      </c>
       <c r="C516" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="D516" s="1"/>
     </row>
     <row r="517" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="8" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C517" t="s">
         <v>1443</v>
-      </c>
-      <c r="B517" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1445</v>
       </c>
       <c r="D517" s="1"/>
     </row>
     <row r="518" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C518" t="s">
         <v>1446</v>
-      </c>
-      <c r="B518" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C518" t="s">
-        <v>1448</v>
       </c>
       <c r="D518" s="1"/>
     </row>
     <row r="519" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="8" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C519" t="s">
         <v>1449</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1451</v>
       </c>
       <c r="D519" s="1"/>
     </row>
     <row r="520" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="8" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C520" t="s">
         <v>1452</v>
-      </c>
-      <c r="B520" t="s">
-        <v>1453</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1454</v>
       </c>
       <c r="D520" s="1"/>
     </row>
     <row r="521" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="8" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C521" t="s">
         <v>1455</v>
-      </c>
-      <c r="B521" t="s">
-        <v>1456</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1457</v>
       </c>
       <c r="D521" s="1"/>
     </row>
     <row r="522" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C522" t="s">
         <v>1458</v>
-      </c>
-      <c r="B522" t="s">
-        <v>1459</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1460</v>
       </c>
       <c r="D522" s="1"/>
     </row>
     <row r="523" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="8" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B523" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="C523">
         <v>0</v>
@@ -12890,10 +12904,10 @@
     </row>
     <row r="524" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="8" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B524" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="C524">
         <v>0</v>
@@ -12902,10 +12916,10 @@
     </row>
     <row r="525" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="8" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B525" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C525">
         <v>0</v>
@@ -12914,34 +12928,34 @@
     </row>
     <row r="526" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="8" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B526" s="7">
         <v>0</v>
       </c>
       <c r="C526" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="D526" s="1"/>
     </row>
     <row r="527" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="8" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B527" t="s">
         <v>1469</v>
       </c>
-      <c r="B527" t="s">
-        <v>1471</v>
-      </c>
       <c r="C527" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="D527" s="1"/>
     </row>
     <row r="528" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="8" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="B528" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C528">
         <v>0</v>
@@ -12950,10 +12964,10 @@
     </row>
     <row r="529" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="8" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="B529" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="C529">
         <v>0</v>
@@ -12962,82 +12976,82 @@
     </row>
     <row r="530" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="8" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C530" t="s">
         <v>1476</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1477</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1478</v>
       </c>
       <c r="D530" s="1"/>
     </row>
     <row r="531" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="8" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="B531">
         <v>0</v>
       </c>
       <c r="C531" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="D531" s="1"/>
     </row>
     <row r="532" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B532" t="s">
         <v>1481</v>
       </c>
-      <c r="B532" t="s">
-        <v>1483</v>
-      </c>
       <c r="C532" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D532" s="1"/>
     </row>
     <row r="533" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="8" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C533" t="s">
         <v>1484</v>
-      </c>
-      <c r="B533" t="s">
-        <v>1485</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1486</v>
       </c>
       <c r="D533" s="1"/>
     </row>
     <row r="534" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="8" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B534" t="s">
         <v>1487</v>
       </c>
-      <c r="B534" t="s">
-        <v>1489</v>
-      </c>
       <c r="C534" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D534" s="1"/>
     </row>
     <row r="535" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="8" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B535" t="s">
         <v>1490</v>
       </c>
-      <c r="B535" t="s">
-        <v>1492</v>
-      </c>
       <c r="C535" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D535" s="1"/>
     </row>
     <row r="536" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="8" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B536" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="C536">
         <v>0</v>
@@ -13046,10 +13060,10 @@
     </row>
     <row r="537" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="8" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="B537" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="C537">
         <v>0</v>
@@ -13058,10 +13072,10 @@
     </row>
     <row r="538" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="8" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="B538" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C538">
         <v>0</v>
@@ -13070,34 +13084,34 @@
     </row>
     <row r="539" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="8" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C539" t="s">
         <v>1498</v>
-      </c>
-      <c r="B539" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1500</v>
       </c>
       <c r="D539" s="1"/>
     </row>
     <row r="540" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="8" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B540">
         <v>0</v>
       </c>
       <c r="C540" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D540" s="1"/>
     </row>
     <row r="541" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="8" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B541" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="C541">
         <v>0</v>
@@ -13106,22 +13120,22 @@
     </row>
     <row r="542" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="8" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C542" t="s">
         <v>1505</v>
-      </c>
-      <c r="B542" t="s">
-        <v>1506</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1507</v>
       </c>
       <c r="D542" s="1"/>
     </row>
     <row r="543" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="8" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B543" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="C543">
         <v>0</v>
@@ -13130,10 +13144,10 @@
     </row>
     <row r="544" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="8" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B544" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C544">
         <v>0</v>
@@ -13142,22 +13156,22 @@
     </row>
     <row r="545" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="8" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C545" t="s">
         <v>1512</v>
-      </c>
-      <c r="B545" t="s">
-        <v>1513</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1514</v>
       </c>
       <c r="D545" s="1"/>
     </row>
     <row r="546" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="8" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B546" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="C546">
         <v>0</v>
@@ -13166,10 +13180,10 @@
     </row>
     <row r="547" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="8" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B547" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="C547">
         <v>0</v>
@@ -13178,10 +13192,10 @@
     </row>
     <row r="548" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="8" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B548" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="C548">
         <v>0</v>
@@ -13190,10 +13204,10 @@
     </row>
     <row r="549" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="8" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B549" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="C549">
         <v>0</v>
@@ -13202,10 +13216,10 @@
     </row>
     <row r="550" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="8" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B550" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="C550">
         <v>0</v>
@@ -13214,10 +13228,10 @@
     </row>
     <row r="551" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="8" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B551" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C551">
         <v>0</v>
@@ -13226,10 +13240,10 @@
     </row>
     <row r="552" spans="1:5" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="8" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="B552" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="C552">
         <v>0</v>
@@ -13238,13 +13252,13 @@
     </row>
     <row r="553" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B553" t="s">
         <v>185</v>
       </c>
-      <c r="B553" t="s">
-        <v>187</v>
-      </c>
       <c r="C553" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
@@ -13263,7 +13277,7 @@
         <v>10</v>
       </c>
       <c r="B555" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C555" s="1">
         <v>0</v>
@@ -13271,24 +13285,24 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B556" t="s">
+        <v>271</v>
+      </c>
+      <c r="C556" t="s">
         <v>272</v>
-      </c>
-      <c r="B556" t="s">
-        <v>273</v>
-      </c>
-      <c r="C556" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B557" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="C557" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
@@ -13304,10 +13318,10 @@
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B559" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>43</v>
@@ -13316,37 +13330,37 @@
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B560" t="s">
         <v>1555</v>
       </c>
-      <c r="B560" t="s">
-        <v>1557</v>
-      </c>
       <c r="C560" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="E560" s="1"/>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B561" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="C561" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E561" s="1"/>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B562" t="s">
+        <v>191</v>
+      </c>
+      <c r="C562" t="s">
         <v>192</v>
-      </c>
-      <c r="B562" t="s">
-        <v>193</v>
-      </c>
-      <c r="C562" t="s">
-        <v>194</v>
       </c>
       <c r="E562" s="1"/>
     </row>
@@ -13363,21 +13377,21 @@
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B564" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C564" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B565" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C565">
         <v>0</v>
@@ -13399,7 +13413,7 @@
         <v>77</v>
       </c>
       <c r="B567" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C567" s="1" t="s">
         <v>31</v>
@@ -13410,7 +13424,7 @@
         <v>104</v>
       </c>
       <c r="B568" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C568">
         <v>0</v>
@@ -13421,7 +13435,7 @@
         <v>106</v>
       </c>
       <c r="B569" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C569">
         <v>0</v>
@@ -13443,7 +13457,7 @@
         <v>102</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C571" t="s">
         <v>138</v>
@@ -13451,32 +13465,32 @@
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B572">
         <v>0</v>
       </c>
       <c r="C572" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B573" t="s">
+        <v>443</v>
+      </c>
+      <c r="C573" t="s">
         <v>444</v>
-      </c>
-      <c r="B573" t="s">
-        <v>445</v>
-      </c>
-      <c r="C573" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="B574" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C574" t="s">
         <v>145</v>
@@ -13487,7 +13501,7 @@
         <v>147</v>
       </c>
       <c r="B575" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C575">
         <v>0</v>
@@ -13506,7 +13520,7 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="B577" t="s">
         <v>151</v>
@@ -13517,35 +13531,35 @@
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B578" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="C578" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B579" t="s">
         <v>155</v>
       </c>
-      <c r="B579" t="s">
-        <v>156</v>
-      </c>
       <c r="C579" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B580" t="s">
         <v>418</v>
       </c>
-      <c r="B580" t="s">
-        <v>420</v>
-      </c>
       <c r="C580" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
@@ -13564,10 +13578,10 @@
         <v>98</v>
       </c>
       <c r="B582" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C582" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
@@ -13575,7 +13589,7 @@
         <v>97</v>
       </c>
       <c r="B583" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C583" t="s">
         <v>140</v>
@@ -13619,7 +13633,7 @@
         <v>119</v>
       </c>
       <c r="B587" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="C587" t="s">
         <v>120</v>
@@ -13627,13 +13641,13 @@
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B588" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="C588" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="E588" s="1"/>
     </row>
@@ -13641,8 +13655,8 @@
       <c r="A589" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B589" t="s">
-        <v>153</v>
+      <c r="B589" s="10" t="s">
+        <v>1591</v>
       </c>
       <c r="C589">
         <v>0</v>
@@ -13650,10 +13664,10 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B590" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C590">
         <v>0</v>
@@ -13661,10 +13675,10 @@
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B591" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C591">
         <v>0</v>
@@ -13673,10 +13687,10 @@
     </row>
     <row r="592" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B592" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C592">
         <v>0</v>
@@ -13685,10 +13699,10 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B593" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C593">
         <v>0</v>
@@ -13696,21 +13710,21 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B594" t="s">
         <v>587</v>
       </c>
-      <c r="B594" t="s">
-        <v>589</v>
-      </c>
       <c r="C594" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B595" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C595">
         <v>0</v>
@@ -13718,48 +13732,48 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B596" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="C596" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="597" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="8" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="B597" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="C597" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D597" s="1"/>
     </row>
     <row r="598" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="8" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C598" t="s">
         <v>1583</v>
-      </c>
-      <c r="B598" t="s">
-        <v>1582</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1585</v>
       </c>
       <c r="D598" s="1"/>
     </row>
     <row r="599" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="8" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="B599" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C599" t="s">
         <v>1578</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1580</v>
       </c>
       <c r="D599" s="1"/>
     </row>
@@ -13787,24 +13801,24 @@
     </row>
     <row r="602" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B602" t="s">
+        <v>303</v>
+      </c>
+      <c r="C602" t="s">
         <v>305</v>
-      </c>
-      <c r="C602" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="B603" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C603" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.25">
@@ -13812,7 +13826,7 @@
         <v>142</v>
       </c>
       <c r="B604" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C604">
         <v>0</v>
@@ -13831,21 +13845,21 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B606" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="C606" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="B607" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C607">
         <v>0</v>
@@ -13853,10 +13867,10 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
-        <v>161</v>
+        <v>1590</v>
       </c>
       <c r="B608" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C608">
         <v>0</v>
@@ -13864,22 +13878,22 @@
     </row>
     <row r="609" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="B609" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D609" s="1"/>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B610" t="s">
+        <v>266</v>
+      </c>
+      <c r="C610" t="s">
         <v>267</v>
-      </c>
-      <c r="B610" t="s">
-        <v>268</v>
-      </c>
-      <c r="C610" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
